--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,6 +792,6547 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130350885</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80285</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>649008</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6995802</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130350908</v>
+      </c>
+      <c r="B4" t="n">
+        <v>89124</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>510</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>649250</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6995605</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130350902</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>648702</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6995939</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130350873</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57016</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>649139</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6995673</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130350865</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>649028</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6995693</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130350904</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>649056</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6995686</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130350866</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>649049</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6995652</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130350860</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>648687</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6995932</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130350870</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>649039</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6995705</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130350857</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>648826</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6995407</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130350853</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>648941</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6995608</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130350861</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>648707</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6995954</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130350903</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>648792</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6995927</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130350899</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>648996</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6995647</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130350844</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>649036</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6995660</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130351125</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92147</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>648877</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6995565</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130351124</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92147</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>649116</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6995496</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130350847</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>649222</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6995657</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130350868</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>649093</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6995638</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130350863</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>649031</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6995803</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130350838</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>649074</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6995652</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130350905</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>649120</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6995740</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130350900</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>649027</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6995592</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130350878</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92181</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>649038</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6995626</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130350877</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92181</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>648991</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6995659</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130350850</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>649130</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6995565</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130350849</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>649171</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6995600</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130350891</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80245</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>649044</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6995628</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130350858</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>648826</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6995403</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130350846</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>649063</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6995635</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130350898</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>648849</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6995437</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130350869</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>649090</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6995641</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130350852</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>649032</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6995530</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130350855</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>648855</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6995417</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130350872</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>649146</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6995662</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130350911</v>
+      </c>
+      <c r="B38" t="n">
+        <v>89124</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>510</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>648698</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6995926</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130350897</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>648848</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6995528</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130350840</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>649262</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6995647</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130350871</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>649048</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6995714</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130350845</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>649059</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6995641</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130350859</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>648771</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6995688</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130350854</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>648853</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6995420</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130350896</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>648854</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6995532</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130350856</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>648835</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6995397</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130350892</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57007</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>649126</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6995764</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130350886</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80285</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>648997</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6995649</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130350837</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91915</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>649254</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6995609</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130350909</v>
+      </c>
+      <c r="B50" t="n">
+        <v>89124</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>510</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>648957</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6995579</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130350883</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80313</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>649094</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6995519</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130350839</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>649369</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6995531</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130350841</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>649195</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6995694</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130350864</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>648993</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6995756</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130350890</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80245</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>649374</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6995542</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130350867</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>649095</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6995637</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130350879</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92026</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>658</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>649062</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6995641</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130350901</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>648771</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6995702</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130350874</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>648811</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6995477</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130350876</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>649127</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6995704</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130350893</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57007</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>649144</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6995799</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130350875</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>648755</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6995792</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>130350842</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>649096</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6995501</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>130350889</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80245</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>649384</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6995514</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130350862</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>648830</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6995874</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>130350910</v>
+      </c>
+      <c r="B66" t="n">
+        <v>89124</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>510</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>648873</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6995569</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>130350881</v>
+      </c>
+      <c r="B67" t="n">
+        <v>97791</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>649111</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6995725</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>130350848</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>649190</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6995689</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350908</v>
+        <v>130350902</v>
       </c>
       <c r="B4" t="n">
-        <v>89124</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649250</v>
+        <v>648702</v>
       </c>
       <c r="R4" t="n">
-        <v>6995605</v>
+        <v>6995939</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,32 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350902</v>
+        <v>130350873</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648702</v>
+        <v>649139</v>
       </c>
       <c r="R5" t="n">
-        <v>6995939</v>
+        <v>6995673</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1060,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,32 +1091,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130350873</v>
+        <v>130350908</v>
       </c>
       <c r="B6" t="n">
-        <v>57016</v>
+        <v>89124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649139</v>
+        <v>649250</v>
       </c>
       <c r="R6" t="n">
-        <v>6995673</v>
+        <v>6995605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,11 +1162,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1489,7 +1489,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130350860</v>
+        <v>130350870</v>
       </c>
       <c r="B10" t="n">
         <v>57826</v>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>648687</v>
+        <v>649039</v>
       </c>
       <c r="R10" t="n">
-        <v>6995932</v>
+        <v>6995705</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130350870</v>
+        <v>130350860</v>
       </c>
       <c r="B11" t="n">
         <v>57826</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649039</v>
+        <v>648687</v>
       </c>
       <c r="R11" t="n">
-        <v>6995705</v>
+        <v>6995932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130350857</v>
+        <v>130350853</v>
       </c>
       <c r="B12" t="n">
         <v>57826</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648826</v>
+        <v>648941</v>
       </c>
       <c r="R12" t="n">
-        <v>6995407</v>
+        <v>6995608</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,7 +1795,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130350853</v>
+        <v>130350857</v>
       </c>
       <c r="B13" t="n">
         <v>57826</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648941</v>
+        <v>648826</v>
       </c>
       <c r="R13" t="n">
-        <v>6995608</v>
+        <v>6995407</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350861</v>
+        <v>130350844</v>
       </c>
       <c r="B14" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>648707</v>
+        <v>649036</v>
       </c>
       <c r="R14" t="n">
-        <v>6995954</v>
+        <v>6995660</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,11 +1968,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1999,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130350903</v>
+        <v>130350861</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2034,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648792</v>
+        <v>648707</v>
       </c>
       <c r="R15" t="n">
-        <v>6995927</v>
+        <v>6995954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,6 +2065,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2096,10 +2096,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130350899</v>
+        <v>130351125</v>
       </c>
       <c r="B16" t="n">
-        <v>91748</v>
+        <v>92147</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,19 +2107,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6040186</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2127,10 +2131,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648996</v>
+        <v>648877</v>
       </c>
       <c r="R16" t="n">
-        <v>6995647</v>
+        <v>6995565</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,10 +2193,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130350844</v>
+        <v>130350899</v>
       </c>
       <c r="B17" t="n">
-        <v>91728</v>
+        <v>91748</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,23 +2204,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>649036</v>
+        <v>648996</v>
       </c>
       <c r="R17" t="n">
-        <v>6995660</v>
+        <v>6995647</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,10 +2286,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130351125</v>
+        <v>130350903</v>
       </c>
       <c r="B18" t="n">
-        <v>92147</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,21 +2297,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648877</v>
+        <v>648792</v>
       </c>
       <c r="R18" t="n">
-        <v>6995565</v>
+        <v>6995927</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130351124</v>
+        <v>130350838</v>
       </c>
       <c r="B19" t="n">
-        <v>92147</v>
+        <v>91692</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040186</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649116</v>
+        <v>649074</v>
       </c>
       <c r="R19" t="n">
-        <v>6995496</v>
+        <v>6995652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,7 +2480,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130350847</v>
+        <v>130350868</v>
       </c>
       <c r="B20" t="n">
         <v>57826</v>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649222</v>
+        <v>649093</v>
       </c>
       <c r="R20" t="n">
-        <v>6995657</v>
+        <v>6995638</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2582,7 +2582,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130350868</v>
+        <v>130350863</v>
       </c>
       <c r="B21" t="n">
         <v>57826</v>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>649093</v>
+        <v>649031</v>
       </c>
       <c r="R21" t="n">
-        <v>6995638</v>
+        <v>6995803</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130350863</v>
+        <v>130350847</v>
       </c>
       <c r="B22" t="n">
         <v>57826</v>
@@ -2719,10 +2719,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>649031</v>
+        <v>649222</v>
       </c>
       <c r="R22" t="n">
-        <v>6995803</v>
+        <v>6995657</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2786,32 +2786,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130350838</v>
+        <v>130351124</v>
       </c>
       <c r="B23" t="n">
-        <v>91692</v>
+        <v>92147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6040186</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649074</v>
+        <v>649116</v>
       </c>
       <c r="R23" t="n">
-        <v>6995652</v>
+        <v>6995496</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2883,7 +2883,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350905</v>
+        <v>130350900</v>
       </c>
       <c r="B24" t="n">
         <v>79180</v>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>649120</v>
+        <v>649027</v>
       </c>
       <c r="R24" t="n">
-        <v>6995740</v>
+        <v>6995592</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350900</v>
+        <v>130350905</v>
       </c>
       <c r="B25" t="n">
         <v>79180</v>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>649027</v>
+        <v>649120</v>
       </c>
       <c r="R25" t="n">
-        <v>6995592</v>
+        <v>6995740</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130350850</v>
+        <v>130350849</v>
       </c>
       <c r="B28" t="n">
         <v>57826</v>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>649130</v>
+        <v>649171</v>
       </c>
       <c r="R28" t="n">
-        <v>6995565</v>
+        <v>6995600</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3373,7 +3373,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130350849</v>
+        <v>130350850</v>
       </c>
       <c r="B29" t="n">
         <v>57826</v>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>649171</v>
+        <v>649130</v>
       </c>
       <c r="R29" t="n">
-        <v>6995600</v>
+        <v>6995565</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3475,32 +3475,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350891</v>
+        <v>130350846</v>
       </c>
       <c r="B30" t="n">
-        <v>80245</v>
+        <v>91728</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>649044</v>
+        <v>649063</v>
       </c>
       <c r="R30" t="n">
-        <v>6995628</v>
+        <v>6995635</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3674,32 +3674,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350846</v>
+        <v>130350891</v>
       </c>
       <c r="B32" t="n">
-        <v>91728</v>
+        <v>80245</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>649063</v>
+        <v>649044</v>
       </c>
       <c r="R32" t="n">
-        <v>6995635</v>
+        <v>6995628</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130350869</v>
+        <v>130350852</v>
       </c>
       <c r="B34" t="n">
         <v>57826</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>649090</v>
+        <v>649032</v>
       </c>
       <c r="R34" t="n">
-        <v>6995641</v>
+        <v>6995530</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130350852</v>
+        <v>130350869</v>
       </c>
       <c r="B35" t="n">
         <v>57826</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>649032</v>
+        <v>649090</v>
       </c>
       <c r="R35" t="n">
-        <v>6995530</v>
+        <v>6995641</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130350872</v>
+        <v>130350911</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>89124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4181,21 +4181,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>649146</v>
+        <v>648698</v>
       </c>
       <c r="R37" t="n">
-        <v>6995662</v>
+        <v>6995926</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4241,11 +4241,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4272,10 +4267,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130350911</v>
+        <v>130350872</v>
       </c>
       <c r="B38" t="n">
-        <v>89124</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4283,21 +4278,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4307,10 +4302,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>648698</v>
+        <v>649146</v>
       </c>
       <c r="R38" t="n">
-        <v>6995926</v>
+        <v>6995662</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4343,6 +4338,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4369,10 +4369,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130350897</v>
+        <v>130350840</v>
       </c>
       <c r="B39" t="n">
-        <v>91748</v>
+        <v>91728</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4380,19 +4380,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4400,10 +4404,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>648848</v>
+        <v>649262</v>
       </c>
       <c r="R39" t="n">
-        <v>6995528</v>
+        <v>6995647</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4462,10 +4466,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130350840</v>
+        <v>130350897</v>
       </c>
       <c r="B40" t="n">
-        <v>91728</v>
+        <v>91748</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4473,23 +4477,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>649262</v>
+        <v>648848</v>
       </c>
       <c r="R40" t="n">
-        <v>6995647</v>
+        <v>6995528</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350859</v>
+        <v>130350896</v>
       </c>
       <c r="B43" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,23 +4769,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4793,10 +4789,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>648771</v>
+        <v>648854</v>
       </c>
       <c r="R43" t="n">
-        <v>6995688</v>
+        <v>6995532</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4829,11 +4825,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4860,10 +4851,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350854</v>
+        <v>130350886</v>
       </c>
       <c r="B44" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,21 +4862,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4895,10 +4886,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648853</v>
+        <v>648997</v>
       </c>
       <c r="R44" t="n">
-        <v>6995420</v>
+        <v>6995649</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4931,11 +4922,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4962,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350896</v>
+        <v>130350892</v>
       </c>
       <c r="B45" t="n">
-        <v>91748</v>
+        <v>57007</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4973,19 +4959,23 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -4993,10 +4983,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648854</v>
+        <v>649126</v>
       </c>
       <c r="R45" t="n">
-        <v>6995532</v>
+        <v>6995764</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5029,6 +5019,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5055,7 +5050,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350856</v>
+        <v>130350859</v>
       </c>
       <c r="B46" t="n">
         <v>57826</v>
@@ -5090,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648835</v>
+        <v>648771</v>
       </c>
       <c r="R46" t="n">
-        <v>6995397</v>
+        <v>6995688</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5130,7 +5125,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5157,10 +5152,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350892</v>
+        <v>130350856</v>
       </c>
       <c r="B47" t="n">
-        <v>57007</v>
+        <v>57826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5168,16 +5163,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5192,10 +5187,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>649126</v>
+        <v>648835</v>
       </c>
       <c r="R47" t="n">
-        <v>6995764</v>
+        <v>6995397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5232,7 +5227,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5259,10 +5254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350886</v>
+        <v>130350854</v>
       </c>
       <c r="B48" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5270,21 +5265,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5294,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648997</v>
+        <v>648853</v>
       </c>
       <c r="R48" t="n">
-        <v>6995649</v>
+        <v>6995420</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5330,6 +5325,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5453,10 +5453,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130350909</v>
+        <v>130350839</v>
       </c>
       <c r="B50" t="n">
-        <v>89124</v>
+        <v>91728</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5464,21 +5464,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>648957</v>
+        <v>649369</v>
       </c>
       <c r="R50" t="n">
-        <v>6995579</v>
+        <v>6995531</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5550,32 +5550,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130350883</v>
+        <v>130350909</v>
       </c>
       <c r="B51" t="n">
-        <v>80313</v>
+        <v>89124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>649094</v>
+        <v>648957</v>
       </c>
       <c r="R51" t="n">
-        <v>6995519</v>
+        <v>6995579</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,32 +5647,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350839</v>
+        <v>130350883</v>
       </c>
       <c r="B52" t="n">
-        <v>91728</v>
+        <v>80313</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>649369</v>
+        <v>649094</v>
       </c>
       <c r="R52" t="n">
-        <v>6995531</v>
+        <v>6995519</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5744,32 +5744,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350841</v>
+        <v>130350890</v>
       </c>
       <c r="B53" t="n">
-        <v>91728</v>
+        <v>80245</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649195</v>
+        <v>649374</v>
       </c>
       <c r="R53" t="n">
-        <v>6995694</v>
+        <v>6995542</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350864</v>
+        <v>130350841</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>648993</v>
+        <v>649195</v>
       </c>
       <c r="R54" t="n">
-        <v>6995756</v>
+        <v>6995694</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5912,11 +5912,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5943,32 +5938,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130350890</v>
+        <v>130350864</v>
       </c>
       <c r="B55" t="n">
-        <v>80245</v>
+        <v>57826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5978,10 +5973,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>649374</v>
+        <v>648993</v>
       </c>
       <c r="R55" t="n">
-        <v>6995542</v>
+        <v>6995756</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6014,6 +6009,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6336,7 +6336,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350874</v>
+        <v>130350876</v>
       </c>
       <c r="B59" t="n">
         <v>57823</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>648811</v>
+        <v>649127</v>
       </c>
       <c r="R59" t="n">
-        <v>6995477</v>
+        <v>6995704</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6438,7 +6438,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350876</v>
+        <v>130350874</v>
       </c>
       <c r="B60" t="n">
         <v>57823</v>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>649127</v>
+        <v>648811</v>
       </c>
       <c r="R60" t="n">
-        <v>6995704</v>
+        <v>6995477</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6540,32 +6540,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130350893</v>
+        <v>130350881</v>
       </c>
       <c r="B61" t="n">
-        <v>57007</v>
+        <v>97791</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>649144</v>
+        <v>649111</v>
       </c>
       <c r="R61" t="n">
-        <v>6995799</v>
+        <v>6995725</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6611,11 +6611,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6642,10 +6637,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130350875</v>
+        <v>130350862</v>
       </c>
       <c r="B62" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6653,16 +6648,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6677,10 +6672,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>648755</v>
+        <v>648830</v>
       </c>
       <c r="R62" t="n">
-        <v>6995792</v>
+        <v>6995874</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6717,7 +6712,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6744,10 +6739,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350842</v>
+        <v>130350875</v>
       </c>
       <c r="B63" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6755,21 +6750,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6779,10 +6774,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649096</v>
+        <v>648755</v>
       </c>
       <c r="R63" t="n">
-        <v>6995501</v>
+        <v>6995792</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6815,6 +6810,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6841,32 +6841,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350889</v>
+        <v>130350893</v>
       </c>
       <c r="B64" t="n">
-        <v>80245</v>
+        <v>57007</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229497</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>649384</v>
+        <v>649144</v>
       </c>
       <c r="R64" t="n">
-        <v>6995514</v>
+        <v>6995799</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6912,6 +6912,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6938,32 +6943,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350862</v>
+        <v>130350889</v>
       </c>
       <c r="B65" t="n">
-        <v>57826</v>
+        <v>80245</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6973,10 +6978,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>648830</v>
+        <v>649384</v>
       </c>
       <c r="R65" t="n">
-        <v>6995874</v>
+        <v>6995514</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7009,11 +7014,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7137,32 +7137,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130350881</v>
+        <v>130350842</v>
       </c>
       <c r="B67" t="n">
-        <v>97791</v>
+        <v>91728</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649111</v>
+        <v>649096</v>
       </c>
       <c r="R67" t="n">
-        <v>6995725</v>
+        <v>6995501</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7334,6 +7334,103 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>130350884</v>
+      </c>
+      <c r="B69" t="n">
+        <v>96146</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Skälsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>649142</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6995829</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Styrnäs</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -989,32 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350902</v>
+        <v>130350873</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648702</v>
+        <v>649139</v>
       </c>
       <c r="R5" t="n">
-        <v>6995939</v>
+        <v>6995673</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1060,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,32 +1091,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130350873</v>
+        <v>130350902</v>
       </c>
       <c r="B6" t="n">
-        <v>57016</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649139</v>
+        <v>648702</v>
       </c>
       <c r="R6" t="n">
-        <v>6995673</v>
+        <v>6995939</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,11 +1162,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130350904</v>
+        <v>130350860</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649056</v>
+        <v>648687</v>
       </c>
       <c r="R8" t="n">
-        <v>6995686</v>
+        <v>6995932</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,6 +1361,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130350860</v>
+        <v>130350904</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,21 +1403,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1422,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>648687</v>
+        <v>649056</v>
       </c>
       <c r="R9" t="n">
-        <v>6995932</v>
+        <v>6995686</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1458,11 +1463,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350892</v>
+        <v>130350837</v>
       </c>
       <c r="B43" t="n">
-        <v>57007</v>
+        <v>91915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>1588</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>649126</v>
+        <v>649254</v>
       </c>
       <c r="R43" t="n">
-        <v>6995764</v>
+        <v>6995609</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4829,11 +4829,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4953,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350886</v>
+        <v>130350859</v>
       </c>
       <c r="B45" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4964,21 +4959,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4988,10 +4983,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648997</v>
+        <v>648771</v>
       </c>
       <c r="R45" t="n">
-        <v>6995649</v>
+        <v>6995688</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5024,6 +5019,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5050,7 +5050,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350859</v>
+        <v>130350854</v>
       </c>
       <c r="B46" t="n">
         <v>57826</v>
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648771</v>
+        <v>648853</v>
       </c>
       <c r="R46" t="n">
-        <v>6995688</v>
+        <v>6995420</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5152,7 +5152,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350854</v>
+        <v>130350856</v>
       </c>
       <c r="B47" t="n">
         <v>57826</v>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648853</v>
+        <v>648835</v>
       </c>
       <c r="R47" t="n">
-        <v>6995420</v>
+        <v>6995397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350856</v>
+        <v>130350892</v>
       </c>
       <c r="B48" t="n">
-        <v>57826</v>
+        <v>57007</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,16 +5265,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648835</v>
+        <v>649126</v>
       </c>
       <c r="R48" t="n">
-        <v>6995397</v>
+        <v>6995764</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5356,10 +5356,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350837</v>
+        <v>130350886</v>
       </c>
       <c r="B49" t="n">
-        <v>91915</v>
+        <v>80285</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,21 +5367,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1588</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>649254</v>
+        <v>648997</v>
       </c>
       <c r="R49" t="n">
-        <v>6995609</v>
+        <v>6995649</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350901</v>
+        <v>130350874</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648771</v>
+        <v>648811</v>
       </c>
       <c r="R58" t="n">
-        <v>6995702</v>
+        <v>6995477</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,6 +6310,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6336,7 +6341,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350874</v>
+        <v>130350876</v>
       </c>
       <c r="B59" t="n">
         <v>57823</v>
@@ -6371,10 +6376,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>648811</v>
+        <v>649127</v>
       </c>
       <c r="R59" t="n">
-        <v>6995477</v>
+        <v>6995704</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,7 +6416,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6438,10 +6443,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350876</v>
+        <v>130350901</v>
       </c>
       <c r="B60" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6449,21 +6454,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6473,10 +6478,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>649127</v>
+        <v>648771</v>
       </c>
       <c r="R60" t="n">
-        <v>6995704</v>
+        <v>6995702</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6509,11 +6514,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130350838</v>
+        <v>130351124</v>
       </c>
       <c r="B19" t="n">
-        <v>91692</v>
+        <v>92147</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6040186</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649074</v>
+        <v>649116</v>
       </c>
       <c r="R19" t="n">
-        <v>6995652</v>
+        <v>6995496</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2786,32 +2786,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351124</v>
+        <v>130350838</v>
       </c>
       <c r="B23" t="n">
-        <v>92147</v>
+        <v>91692</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649116</v>
+        <v>649074</v>
       </c>
       <c r="R23" t="n">
-        <v>6995496</v>
+        <v>6995652</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3475,34 +3475,30 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350891</v>
+        <v>130350898</v>
       </c>
       <c r="B30" t="n">
-        <v>80245</v>
+        <v>91748</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3510,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>649044</v>
+        <v>648849</v>
       </c>
       <c r="R30" t="n">
-        <v>6995628</v>
+        <v>6995437</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3669,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350898</v>
+        <v>130350858</v>
       </c>
       <c r="B32" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3680,19 +3676,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>648849</v>
+        <v>648826</v>
       </c>
       <c r="R32" t="n">
-        <v>6995437</v>
+        <v>6995403</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,6 +3736,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3762,32 +3767,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130350858</v>
+        <v>130350891</v>
       </c>
       <c r="B33" t="n">
-        <v>57826</v>
+        <v>80245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3797,10 +3802,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>648826</v>
+        <v>649044</v>
       </c>
       <c r="R33" t="n">
-        <v>6995403</v>
+        <v>6995628</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3833,11 +3838,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350837</v>
+        <v>130350892</v>
       </c>
       <c r="B43" t="n">
-        <v>91915</v>
+        <v>57007</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1588</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>649254</v>
+        <v>649126</v>
       </c>
       <c r="R43" t="n">
-        <v>6995609</v>
+        <v>6995764</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4829,6 +4829,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4948,10 +4953,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350859</v>
+        <v>130350886</v>
       </c>
       <c r="B45" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4959,21 +4964,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4983,10 +4988,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648771</v>
+        <v>648997</v>
       </c>
       <c r="R45" t="n">
-        <v>6995688</v>
+        <v>6995649</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5019,11 +5024,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5050,7 +5050,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350854</v>
+        <v>130350859</v>
       </c>
       <c r="B46" t="n">
         <v>57826</v>
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648853</v>
+        <v>648771</v>
       </c>
       <c r="R46" t="n">
-        <v>6995420</v>
+        <v>6995688</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5152,7 +5152,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350856</v>
+        <v>130350854</v>
       </c>
       <c r="B47" t="n">
         <v>57826</v>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648835</v>
+        <v>648853</v>
       </c>
       <c r="R47" t="n">
-        <v>6995397</v>
+        <v>6995420</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350892</v>
+        <v>130350856</v>
       </c>
       <c r="B48" t="n">
-        <v>57007</v>
+        <v>57826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,16 +5265,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>649126</v>
+        <v>648835</v>
       </c>
       <c r="R48" t="n">
-        <v>6995764</v>
+        <v>6995397</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5356,10 +5356,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350886</v>
+        <v>130350837</v>
       </c>
       <c r="B49" t="n">
-        <v>80285</v>
+        <v>91915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,21 +5367,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>648997</v>
+        <v>649254</v>
       </c>
       <c r="R49" t="n">
-        <v>6995649</v>
+        <v>6995609</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350874</v>
+        <v>130350901</v>
       </c>
       <c r="B58" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648811</v>
+        <v>648771</v>
       </c>
       <c r="R58" t="n">
-        <v>6995477</v>
+        <v>6995702</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,11 +6310,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6341,7 +6336,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350876</v>
+        <v>130350874</v>
       </c>
       <c r="B59" t="n">
         <v>57823</v>
@@ -6376,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>649127</v>
+        <v>648811</v>
       </c>
       <c r="R59" t="n">
-        <v>6995704</v>
+        <v>6995477</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6416,7 +6411,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6443,10 +6438,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350901</v>
+        <v>130350876</v>
       </c>
       <c r="B60" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6454,21 +6449,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6478,10 +6473,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>648771</v>
+        <v>649127</v>
       </c>
       <c r="R60" t="n">
-        <v>6995702</v>
+        <v>6995704</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6514,6 +6509,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -989,32 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350873</v>
+        <v>130350902</v>
       </c>
       <c r="B5" t="n">
-        <v>57016</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649139</v>
+        <v>648702</v>
       </c>
       <c r="R5" t="n">
-        <v>6995673</v>
+        <v>6995939</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,11 +1060,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130350902</v>
+        <v>130350873</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>648702</v>
+        <v>649139</v>
       </c>
       <c r="R6" t="n">
-        <v>6995939</v>
+        <v>6995673</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1157,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130350860</v>
+        <v>130350904</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>648687</v>
+        <v>649056</v>
       </c>
       <c r="R8" t="n">
-        <v>6995932</v>
+        <v>6995686</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130350904</v>
+        <v>130350860</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,21 +1398,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649056</v>
+        <v>648687</v>
       </c>
       <c r="R9" t="n">
-        <v>6995686</v>
+        <v>6995932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,6 +1458,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130351124</v>
+        <v>130350838</v>
       </c>
       <c r="B19" t="n">
-        <v>92147</v>
+        <v>91692</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040186</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649116</v>
+        <v>649074</v>
       </c>
       <c r="R19" t="n">
-        <v>6995496</v>
+        <v>6995652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2786,32 +2786,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130350838</v>
+        <v>130351124</v>
       </c>
       <c r="B23" t="n">
-        <v>91692</v>
+        <v>92147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6040186</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649074</v>
+        <v>649116</v>
       </c>
       <c r="R23" t="n">
-        <v>6995652</v>
+        <v>6995496</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3475,30 +3475,34 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350898</v>
+        <v>130350891</v>
       </c>
       <c r="B30" t="n">
-        <v>91748</v>
+        <v>80245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3506,10 +3510,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>648849</v>
+        <v>649044</v>
       </c>
       <c r="R30" t="n">
-        <v>6995437</v>
+        <v>6995628</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3665,10 +3669,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350858</v>
+        <v>130350898</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,23 +3680,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>648826</v>
+        <v>648849</v>
       </c>
       <c r="R32" t="n">
-        <v>6995403</v>
+        <v>6995437</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,11 +3736,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3767,32 +3762,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130350891</v>
+        <v>130350858</v>
       </c>
       <c r="B33" t="n">
-        <v>80245</v>
+        <v>57826</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3802,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>649044</v>
+        <v>648826</v>
       </c>
       <c r="R33" t="n">
-        <v>6995628</v>
+        <v>6995403</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,6 +3833,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350892</v>
+        <v>130350837</v>
       </c>
       <c r="B43" t="n">
-        <v>57007</v>
+        <v>91915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>1588</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>649126</v>
+        <v>649254</v>
       </c>
       <c r="R43" t="n">
-        <v>6995764</v>
+        <v>6995609</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4829,11 +4829,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4953,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350886</v>
+        <v>130350859</v>
       </c>
       <c r="B45" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4964,21 +4959,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4988,10 +4983,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648997</v>
+        <v>648771</v>
       </c>
       <c r="R45" t="n">
-        <v>6995649</v>
+        <v>6995688</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5024,6 +5019,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5050,7 +5050,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350859</v>
+        <v>130350854</v>
       </c>
       <c r="B46" t="n">
         <v>57826</v>
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648771</v>
+        <v>648853</v>
       </c>
       <c r="R46" t="n">
-        <v>6995688</v>
+        <v>6995420</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5152,7 +5152,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350854</v>
+        <v>130350856</v>
       </c>
       <c r="B47" t="n">
         <v>57826</v>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648853</v>
+        <v>648835</v>
       </c>
       <c r="R47" t="n">
-        <v>6995420</v>
+        <v>6995397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350856</v>
+        <v>130350892</v>
       </c>
       <c r="B48" t="n">
-        <v>57826</v>
+        <v>57007</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,16 +5265,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648835</v>
+        <v>649126</v>
       </c>
       <c r="R48" t="n">
-        <v>6995397</v>
+        <v>6995764</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5356,10 +5356,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350837</v>
+        <v>130350886</v>
       </c>
       <c r="B49" t="n">
-        <v>91915</v>
+        <v>80285</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,21 +5367,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1588</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5391,10 +5391,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>649254</v>
+        <v>648997</v>
       </c>
       <c r="R49" t="n">
-        <v>6995609</v>
+        <v>6995649</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350901</v>
+        <v>130350874</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648771</v>
+        <v>648811</v>
       </c>
       <c r="R58" t="n">
-        <v>6995702</v>
+        <v>6995477</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,6 +6310,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6336,7 +6341,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350874</v>
+        <v>130350876</v>
       </c>
       <c r="B59" t="n">
         <v>57823</v>
@@ -6371,10 +6376,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>648811</v>
+        <v>649127</v>
       </c>
       <c r="R59" t="n">
-        <v>6995477</v>
+        <v>6995704</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,7 +6416,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6438,10 +6443,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350876</v>
+        <v>130350901</v>
       </c>
       <c r="B60" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6449,21 +6454,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6473,10 +6478,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>649127</v>
+        <v>648771</v>
       </c>
       <c r="R60" t="n">
-        <v>6995704</v>
+        <v>6995702</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6509,11 +6514,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130350885</v>
       </c>
       <c r="B3" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>130350908</v>
       </c>
       <c r="B4" t="n">
-        <v>89124</v>
+        <v>89125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>130350902</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>130350904</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130350860</v>
+        <v>130350866</v>
       </c>
       <c r="B9" t="n">
         <v>57826</v>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>648687</v>
+        <v>649049</v>
       </c>
       <c r="R9" t="n">
-        <v>6995932</v>
+        <v>6995652</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,7 +1591,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130350866</v>
+        <v>130350860</v>
       </c>
       <c r="B11" t="n">
         <v>57826</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649049</v>
+        <v>648687</v>
       </c>
       <c r="R11" t="n">
-        <v>6995652</v>
+        <v>6995932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,7 +1900,7 @@
         <v>130350844</v>
       </c>
       <c r="B14" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130350899</v>
+        <v>130350903</v>
       </c>
       <c r="B15" t="n">
-        <v>91748</v>
+        <v>79183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,19 +2005,23 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2025,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648996</v>
+        <v>648792</v>
       </c>
       <c r="R15" t="n">
-        <v>6995647</v>
+        <v>6995927</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130350903</v>
+        <v>130350899</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>91751</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2098,23 +2102,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648792</v>
+        <v>648996</v>
       </c>
       <c r="R16" t="n">
-        <v>6995927</v>
+        <v>6995647</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
         <v>130351125</v>
       </c>
       <c r="B18" t="n">
-        <v>92147</v>
+        <v>92150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130350838</v>
+        <v>130351124</v>
       </c>
       <c r="B19" t="n">
-        <v>91692</v>
+        <v>92150</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6040186</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649074</v>
+        <v>649116</v>
       </c>
       <c r="R19" t="n">
-        <v>6995652</v>
+        <v>6995496</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,32 +2480,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130350863</v>
+        <v>130350838</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>91695</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649031</v>
+        <v>649074</v>
       </c>
       <c r="R20" t="n">
-        <v>6995803</v>
+        <v>6995652</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,11 +2551,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2582,7 +2577,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130350847</v>
+        <v>130350868</v>
       </c>
       <c r="B21" t="n">
         <v>57826</v>
@@ -2617,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>649222</v>
+        <v>649093</v>
       </c>
       <c r="R21" t="n">
-        <v>6995657</v>
+        <v>6995638</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2657,7 +2652,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2684,7 +2679,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130350868</v>
+        <v>130350863</v>
       </c>
       <c r="B22" t="n">
         <v>57826</v>
@@ -2719,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>649093</v>
+        <v>649031</v>
       </c>
       <c r="R22" t="n">
-        <v>6995638</v>
+        <v>6995803</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2786,10 +2781,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351124</v>
+        <v>130350847</v>
       </c>
       <c r="B23" t="n">
-        <v>92147</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2797,21 +2792,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2821,10 +2816,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649116</v>
+        <v>649222</v>
       </c>
       <c r="R23" t="n">
-        <v>6995496</v>
+        <v>6995657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2857,6 +2852,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2886,7 +2886,7 @@
         <v>130350878</v>
       </c>
       <c r="B24" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>130350877</v>
       </c>
       <c r="B25" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>130350900</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>130350905</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130350850</v>
+        <v>130350849</v>
       </c>
       <c r="B28" t="n">
         <v>57826</v>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>649130</v>
+        <v>649171</v>
       </c>
       <c r="R28" t="n">
-        <v>6995565</v>
+        <v>6995600</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3373,7 +3373,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130350849</v>
+        <v>130350850</v>
       </c>
       <c r="B29" t="n">
         <v>57826</v>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>649171</v>
+        <v>649130</v>
       </c>
       <c r="R29" t="n">
-        <v>6995600</v>
+        <v>6995565</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3475,32 +3475,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350891</v>
+        <v>130350846</v>
       </c>
       <c r="B30" t="n">
-        <v>80245</v>
+        <v>91731</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>649044</v>
+        <v>649063</v>
       </c>
       <c r="R30" t="n">
-        <v>6995628</v>
+        <v>6995635</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130350846</v>
+        <v>130350898</v>
       </c>
       <c r="B31" t="n">
-        <v>91728</v>
+        <v>91751</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3583,23 +3583,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3607,10 +3603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>649063</v>
+        <v>648849</v>
       </c>
       <c r="R31" t="n">
-        <v>6995635</v>
+        <v>6995437</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3669,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350898</v>
+        <v>130350858</v>
       </c>
       <c r="B32" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3680,19 +3676,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>648849</v>
+        <v>648826</v>
       </c>
       <c r="R32" t="n">
-        <v>6995437</v>
+        <v>6995403</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,6 +3736,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3762,32 +3767,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130350858</v>
+        <v>130350891</v>
       </c>
       <c r="B33" t="n">
-        <v>57826</v>
+        <v>80248</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3797,10 +3802,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>648826</v>
+        <v>649044</v>
       </c>
       <c r="R33" t="n">
-        <v>6995403</v>
+        <v>6995628</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3833,11 +3838,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3966,7 +3966,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130350855</v>
+        <v>130350869</v>
       </c>
       <c r="B35" t="n">
         <v>57826</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>648855</v>
+        <v>649090</v>
       </c>
       <c r="R35" t="n">
-        <v>6995417</v>
+        <v>6995641</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4068,7 +4068,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130350869</v>
+        <v>130350855</v>
       </c>
       <c r="B36" t="n">
         <v>57826</v>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>649090</v>
+        <v>648855</v>
       </c>
       <c r="R36" t="n">
-        <v>6995641</v>
+        <v>6995417</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4173,7 +4173,7 @@
         <v>130350911</v>
       </c>
       <c r="B37" t="n">
-        <v>89124</v>
+        <v>89125</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>130350897</v>
       </c>
       <c r="B39" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>130350840</v>
       </c>
       <c r="B40" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>130350845</v>
       </c>
       <c r="B42" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>130350837</v>
       </c>
       <c r="B43" t="n">
-        <v>91915</v>
+        <v>91918</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350896</v>
+        <v>130350859</v>
       </c>
       <c r="B44" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,19 +4866,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4886,10 +4890,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648854</v>
+        <v>648771</v>
       </c>
       <c r="R44" t="n">
-        <v>6995532</v>
+        <v>6995688</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4922,6 +4926,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4948,7 +4957,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350859</v>
+        <v>130350856</v>
       </c>
       <c r="B45" t="n">
         <v>57826</v>
@@ -4983,10 +4992,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648771</v>
+        <v>648835</v>
       </c>
       <c r="R45" t="n">
-        <v>6995688</v>
+        <v>6995397</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5023,7 +5032,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5152,10 +5161,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350856</v>
+        <v>130350886</v>
       </c>
       <c r="B47" t="n">
-        <v>57826</v>
+        <v>80288</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5163,21 +5172,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5187,10 +5196,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648835</v>
+        <v>648997</v>
       </c>
       <c r="R47" t="n">
-        <v>6995397</v>
+        <v>6995649</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5223,11 +5232,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5254,10 +5258,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350892</v>
+        <v>130350896</v>
       </c>
       <c r="B48" t="n">
-        <v>57007</v>
+        <v>91751</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,23 +5269,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>649126</v>
+        <v>648854</v>
       </c>
       <c r="R48" t="n">
-        <v>6995764</v>
+        <v>6995532</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,11 +5325,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5356,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350886</v>
+        <v>130350892</v>
       </c>
       <c r="B49" t="n">
-        <v>80285</v>
+        <v>57007</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,21 +5362,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5391,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>648997</v>
+        <v>649126</v>
       </c>
       <c r="R49" t="n">
-        <v>6995649</v>
+        <v>6995764</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5427,6 +5422,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5453,32 +5453,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130350839</v>
+        <v>130350883</v>
       </c>
       <c r="B50" t="n">
-        <v>91728</v>
+        <v>80316</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>649369</v>
+        <v>649094</v>
       </c>
       <c r="R50" t="n">
-        <v>6995531</v>
+        <v>6995519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130350909</v>
+        <v>130350839</v>
       </c>
       <c r="B51" t="n">
-        <v>89124</v>
+        <v>91731</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>648957</v>
+        <v>649369</v>
       </c>
       <c r="R51" t="n">
-        <v>6995579</v>
+        <v>6995531</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,32 +5647,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350883</v>
+        <v>130350909</v>
       </c>
       <c r="B52" t="n">
-        <v>80313</v>
+        <v>89125</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>649094</v>
+        <v>648957</v>
       </c>
       <c r="R52" t="n">
-        <v>6995519</v>
+        <v>6995579</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5744,32 +5744,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350841</v>
+        <v>130350890</v>
       </c>
       <c r="B53" t="n">
-        <v>91728</v>
+        <v>80248</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649195</v>
+        <v>649374</v>
       </c>
       <c r="R53" t="n">
-        <v>6995694</v>
+        <v>6995542</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350879</v>
+        <v>130350841</v>
       </c>
       <c r="B54" t="n">
-        <v>92026</v>
+        <v>91731</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>649062</v>
+        <v>649195</v>
       </c>
       <c r="R54" t="n">
-        <v>6995641</v>
+        <v>6995694</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130350864</v>
+        <v>130350879</v>
       </c>
       <c r="B55" t="n">
-        <v>57826</v>
+        <v>92029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>648993</v>
+        <v>649062</v>
       </c>
       <c r="R55" t="n">
-        <v>6995756</v>
+        <v>6995641</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6009,11 +6009,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6040,7 +6035,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130350867</v>
+        <v>130350864</v>
       </c>
       <c r="B56" t="n">
         <v>57826</v>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>649095</v>
+        <v>648993</v>
       </c>
       <c r="R56" t="n">
-        <v>6995637</v>
+        <v>6995756</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6115,7 +6110,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6142,32 +6137,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130350890</v>
+        <v>130350867</v>
       </c>
       <c r="B57" t="n">
-        <v>80245</v>
+        <v>57826</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6177,10 +6172,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>649374</v>
+        <v>649095</v>
       </c>
       <c r="R57" t="n">
-        <v>6995542</v>
+        <v>6995637</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6213,6 +6208,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350874</v>
+        <v>130350901</v>
       </c>
       <c r="B58" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648811</v>
+        <v>648771</v>
       </c>
       <c r="R58" t="n">
-        <v>6995477</v>
+        <v>6995702</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,11 +6310,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6443,10 +6438,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350901</v>
+        <v>130350874</v>
       </c>
       <c r="B60" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6454,21 +6449,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6478,10 +6473,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>648771</v>
+        <v>648811</v>
       </c>
       <c r="R60" t="n">
-        <v>6995702</v>
+        <v>6995477</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6514,6 +6509,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6540,10 +6540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130350875</v>
+        <v>130350862</v>
       </c>
       <c r="B61" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6551,16 +6551,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>648755</v>
+        <v>648830</v>
       </c>
       <c r="R61" t="n">
-        <v>6995792</v>
+        <v>6995874</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6747,7 +6747,7 @@
         <v>130350881</v>
       </c>
       <c r="B63" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>130350910</v>
       </c>
       <c r="B64" t="n">
-        <v>89124</v>
+        <v>89125</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>130350842</v>
       </c>
       <c r="B65" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7035,10 +7035,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130350862</v>
+        <v>130350875</v>
       </c>
       <c r="B66" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7046,16 +7046,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>648830</v>
+        <v>648755</v>
       </c>
       <c r="R66" t="n">
-        <v>6995874</v>
+        <v>6995792</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7140,7 +7140,7 @@
         <v>130350889</v>
       </c>
       <c r="B67" t="n">
-        <v>80245</v>
+        <v>80248</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>130350884</v>
       </c>
       <c r="B69" t="n">
-        <v>96146</v>
+        <v>96149</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130350885</v>
       </c>
       <c r="B3" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>130350908</v>
       </c>
       <c r="B4" t="n">
-        <v>89125</v>
+        <v>89151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>130350902</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>130350873</v>
       </c>
       <c r="B6" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>130350865</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130350904</v>
+        <v>130350866</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>57852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649056</v>
+        <v>649049</v>
       </c>
       <c r="R8" t="n">
-        <v>6995686</v>
+        <v>6995652</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,6 +1361,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130350866</v>
+        <v>130350870</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1422,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649049</v>
+        <v>649039</v>
       </c>
       <c r="R9" t="n">
-        <v>6995652</v>
+        <v>6995705</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1467,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130350870</v>
+        <v>130350860</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649039</v>
+        <v>648687</v>
       </c>
       <c r="R10" t="n">
-        <v>6995705</v>
+        <v>6995932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130350860</v>
+        <v>130350904</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>79209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,21 +1607,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1626,10 +1631,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>648687</v>
+        <v>649056</v>
       </c>
       <c r="R11" t="n">
-        <v>6995932</v>
+        <v>6995686</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,11 +1667,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1696,7 +1696,7 @@
         <v>130350853</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130350857</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350844</v>
+        <v>130351125</v>
       </c>
       <c r="B14" t="n">
-        <v>91731</v>
+        <v>92176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6040186</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649036</v>
+        <v>648877</v>
       </c>
       <c r="R14" t="n">
-        <v>6995660</v>
+        <v>6995565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130350903</v>
+        <v>130350844</v>
       </c>
       <c r="B15" t="n">
-        <v>79183</v>
+        <v>91757</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648792</v>
+        <v>649036</v>
       </c>
       <c r="R15" t="n">
-        <v>6995927</v>
+        <v>6995660</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
         <v>130350899</v>
       </c>
       <c r="B16" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130350861</v>
+        <v>130350903</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>79209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648707</v>
+        <v>648792</v>
       </c>
       <c r="R17" t="n">
-        <v>6995954</v>
+        <v>6995927</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,11 +2255,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2286,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130351125</v>
+        <v>130350861</v>
       </c>
       <c r="B18" t="n">
-        <v>92150</v>
+        <v>57852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,21 +2292,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2316,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648877</v>
+        <v>648707</v>
       </c>
       <c r="R18" t="n">
-        <v>6995565</v>
+        <v>6995954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,6 +2352,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130351124</v>
+        <v>130350838</v>
       </c>
       <c r="B19" t="n">
-        <v>92150</v>
+        <v>91721</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040186</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649116</v>
+        <v>649074</v>
       </c>
       <c r="R19" t="n">
-        <v>6995496</v>
+        <v>6995652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,32 +2480,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130350838</v>
+        <v>130351124</v>
       </c>
       <c r="B20" t="n">
-        <v>91695</v>
+        <v>92176</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6040186</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649074</v>
+        <v>649116</v>
       </c>
       <c r="R20" t="n">
-        <v>6995652</v>
+        <v>6995496</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
         <v>130350868</v>
       </c>
       <c r="B21" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>130350863</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>130350847</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350878</v>
+        <v>130350900</v>
       </c>
       <c r="B24" t="n">
-        <v>92184</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>649038</v>
+        <v>649027</v>
       </c>
       <c r="R24" t="n">
-        <v>6995626</v>
+        <v>6995592</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350877</v>
+        <v>130350905</v>
       </c>
       <c r="B25" t="n">
-        <v>92184</v>
+        <v>79209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>648991</v>
+        <v>649120</v>
       </c>
       <c r="R25" t="n">
-        <v>6995659</v>
+        <v>6995740</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130350900</v>
+        <v>130350878</v>
       </c>
       <c r="B26" t="n">
-        <v>79183</v>
+        <v>92210</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>649027</v>
+        <v>649038</v>
       </c>
       <c r="R26" t="n">
-        <v>6995592</v>
+        <v>6995626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,32 +3174,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130350905</v>
+        <v>130350877</v>
       </c>
       <c r="B27" t="n">
-        <v>79183</v>
+        <v>92210</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>649120</v>
+        <v>648991</v>
       </c>
       <c r="R27" t="n">
-        <v>6995740</v>
+        <v>6995659</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3274,7 +3274,7 @@
         <v>130350849</v>
       </c>
       <c r="B28" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>130350850</v>
       </c>
       <c r="B29" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>130350846</v>
       </c>
       <c r="B30" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>130350898</v>
       </c>
       <c r="B31" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>130350858</v>
       </c>
       <c r="B32" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>130350891</v>
       </c>
       <c r="B33" t="n">
-        <v>80248</v>
+        <v>80274</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>130350852</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>130350869</v>
       </c>
       <c r="B35" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>130350855</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>130350911</v>
       </c>
       <c r="B37" t="n">
-        <v>89125</v>
+        <v>89151</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>130350872</v>
       </c>
       <c r="B38" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4369,10 +4369,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130350897</v>
+        <v>130350840</v>
       </c>
       <c r="B39" t="n">
-        <v>91751</v>
+        <v>91757</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4380,19 +4380,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4400,10 +4404,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>648848</v>
+        <v>649262</v>
       </c>
       <c r="R39" t="n">
-        <v>6995528</v>
+        <v>6995647</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4462,10 +4466,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130350840</v>
+        <v>130350897</v>
       </c>
       <c r="B40" t="n">
-        <v>91731</v>
+        <v>91777</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4473,23 +4477,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>649262</v>
+        <v>648848</v>
       </c>
       <c r="R40" t="n">
-        <v>6995647</v>
+        <v>6995528</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4562,7 +4562,7 @@
         <v>130350871</v>
       </c>
       <c r="B41" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>130350845</v>
       </c>
       <c r="B42" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>130350837</v>
       </c>
       <c r="B43" t="n">
-        <v>91918</v>
+        <v>91944</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350859</v>
+        <v>130350896</v>
       </c>
       <c r="B44" t="n">
-        <v>57826</v>
+        <v>91777</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,23 +4866,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4890,10 +4886,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648771</v>
+        <v>648854</v>
       </c>
       <c r="R44" t="n">
-        <v>6995688</v>
+        <v>6995532</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,11 +4922,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4957,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350856</v>
+        <v>130350886</v>
       </c>
       <c r="B45" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,21 +4959,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4992,10 +4983,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648835</v>
+        <v>648997</v>
       </c>
       <c r="R45" t="n">
-        <v>6995397</v>
+        <v>6995649</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5028,11 +5019,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5059,10 +5045,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350854</v>
+        <v>130350892</v>
       </c>
       <c r="B46" t="n">
-        <v>57826</v>
+        <v>57033</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5070,16 +5056,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5094,10 +5080,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648853</v>
+        <v>649126</v>
       </c>
       <c r="R46" t="n">
-        <v>6995420</v>
+        <v>6995764</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5134,7 +5120,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5161,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350886</v>
+        <v>130350859</v>
       </c>
       <c r="B47" t="n">
-        <v>80288</v>
+        <v>57852</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5172,21 +5158,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5196,10 +5182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648997</v>
+        <v>648771</v>
       </c>
       <c r="R47" t="n">
-        <v>6995649</v>
+        <v>6995688</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5232,6 +5218,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5258,10 +5249,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350896</v>
+        <v>130350856</v>
       </c>
       <c r="B48" t="n">
-        <v>91751</v>
+        <v>57852</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5269,19 +5260,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5289,10 +5284,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648854</v>
+        <v>648835</v>
       </c>
       <c r="R48" t="n">
-        <v>6995532</v>
+        <v>6995397</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,6 +5320,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5351,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350892</v>
+        <v>130350854</v>
       </c>
       <c r="B49" t="n">
-        <v>57007</v>
+        <v>57852</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>649126</v>
+        <v>648853</v>
       </c>
       <c r="R49" t="n">
-        <v>6995764</v>
+        <v>6995420</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5456,7 +5456,7 @@
         <v>130350883</v>
       </c>
       <c r="B50" t="n">
-        <v>80316</v>
+        <v>80342</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130350839</v>
+        <v>130350909</v>
       </c>
       <c r="B51" t="n">
-        <v>91731</v>
+        <v>89151</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>649369</v>
+        <v>648957</v>
       </c>
       <c r="R51" t="n">
-        <v>6995531</v>
+        <v>6995579</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,10 +5647,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350909</v>
+        <v>130350839</v>
       </c>
       <c r="B52" t="n">
-        <v>89125</v>
+        <v>91757</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5658,21 +5658,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>648957</v>
+        <v>649369</v>
       </c>
       <c r="R52" t="n">
-        <v>6995579</v>
+        <v>6995531</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5744,32 +5744,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350890</v>
+        <v>130350841</v>
       </c>
       <c r="B53" t="n">
-        <v>80248</v>
+        <v>91757</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649374</v>
+        <v>649195</v>
       </c>
       <c r="R53" t="n">
-        <v>6995542</v>
+        <v>6995694</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350841</v>
+        <v>130350864</v>
       </c>
       <c r="B54" t="n">
-        <v>91731</v>
+        <v>57852</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>649195</v>
+        <v>648993</v>
       </c>
       <c r="R54" t="n">
-        <v>6995694</v>
+        <v>6995756</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5912,6 +5912,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5938,10 +5943,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130350879</v>
+        <v>130350867</v>
       </c>
       <c r="B55" t="n">
-        <v>92029</v>
+        <v>57852</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5949,21 +5954,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5973,10 +5978,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>649062</v>
+        <v>649095</v>
       </c>
       <c r="R55" t="n">
-        <v>6995641</v>
+        <v>6995637</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6009,6 +6014,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6035,10 +6045,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130350864</v>
+        <v>130350879</v>
       </c>
       <c r="B56" t="n">
-        <v>57826</v>
+        <v>92055</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6046,21 +6056,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6070,10 +6080,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>648993</v>
+        <v>649062</v>
       </c>
       <c r="R56" t="n">
-        <v>6995756</v>
+        <v>6995641</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6106,11 +6116,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6137,32 +6142,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130350867</v>
+        <v>130350890</v>
       </c>
       <c r="B57" t="n">
-        <v>57826</v>
+        <v>80274</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6172,10 +6177,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>649095</v>
+        <v>649374</v>
       </c>
       <c r="R57" t="n">
-        <v>6995637</v>
+        <v>6995542</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6208,11 +6213,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6242,7 +6242,7 @@
         <v>130350901</v>
       </c>
       <c r="B58" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350876</v>
+        <v>130350874</v>
       </c>
       <c r="B59" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>649127</v>
+        <v>648811</v>
       </c>
       <c r="R59" t="n">
-        <v>6995704</v>
+        <v>6995477</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6438,10 +6438,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350874</v>
+        <v>130350876</v>
       </c>
       <c r="B60" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>648811</v>
+        <v>649127</v>
       </c>
       <c r="R60" t="n">
-        <v>6995477</v>
+        <v>6995704</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6540,10 +6540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130350862</v>
+        <v>130350910</v>
       </c>
       <c r="B61" t="n">
-        <v>57826</v>
+        <v>89151</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>648830</v>
+        <v>648873</v>
       </c>
       <c r="R61" t="n">
-        <v>6995874</v>
+        <v>6995569</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6611,11 +6611,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6642,10 +6637,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130350893</v>
+        <v>130350862</v>
       </c>
       <c r="B62" t="n">
-        <v>57007</v>
+        <v>57852</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6653,16 +6648,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6677,10 +6672,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>649144</v>
+        <v>648830</v>
       </c>
       <c r="R62" t="n">
-        <v>6995799</v>
+        <v>6995874</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6717,7 +6712,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6744,32 +6739,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350881</v>
+        <v>130350875</v>
       </c>
       <c r="B63" t="n">
-        <v>97794</v>
+        <v>57849</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6779,10 +6774,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649111</v>
+        <v>648755</v>
       </c>
       <c r="R63" t="n">
-        <v>6995725</v>
+        <v>6995792</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6815,6 +6810,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6841,32 +6841,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350910</v>
+        <v>130350881</v>
       </c>
       <c r="B64" t="n">
-        <v>89125</v>
+        <v>97820</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6876,10 +6876,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>648873</v>
+        <v>649111</v>
       </c>
       <c r="R64" t="n">
-        <v>6995569</v>
+        <v>6995725</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6941,7 +6941,7 @@
         <v>130350842</v>
       </c>
       <c r="B65" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7035,32 +7035,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130350875</v>
+        <v>130350889</v>
       </c>
       <c r="B66" t="n">
-        <v>57823</v>
+        <v>80274</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>648755</v>
+        <v>649384</v>
       </c>
       <c r="R66" t="n">
-        <v>6995792</v>
+        <v>6995514</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7106,11 +7106,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7137,32 +7132,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130350889</v>
+        <v>130350893</v>
       </c>
       <c r="B67" t="n">
-        <v>80248</v>
+        <v>57033</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229497</v>
+        <v>102612</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7172,10 +7167,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649384</v>
+        <v>649144</v>
       </c>
       <c r="R67" t="n">
-        <v>6995514</v>
+        <v>6995799</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7208,6 +7203,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7237,7 +7237,7 @@
         <v>130350848</v>
       </c>
       <c r="B68" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>130350884</v>
       </c>
       <c r="B69" t="n">
-        <v>96149</v>
+        <v>96175</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350908</v>
+        <v>130350902</v>
       </c>
       <c r="B4" t="n">
-        <v>89151</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649250</v>
+        <v>648702</v>
       </c>
       <c r="R4" t="n">
-        <v>6995605</v>
+        <v>6995939</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350902</v>
+        <v>130350908</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>89151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648702</v>
+        <v>649250</v>
       </c>
       <c r="R5" t="n">
-        <v>6995939</v>
+        <v>6995605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130350866</v>
+        <v>130350904</v>
       </c>
       <c r="B8" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649049</v>
+        <v>649056</v>
       </c>
       <c r="R8" t="n">
-        <v>6995652</v>
+        <v>6995686</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,7 +1387,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130350870</v>
+        <v>130350866</v>
       </c>
       <c r="B9" t="n">
         <v>57852</v>
@@ -1427,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649039</v>
+        <v>649049</v>
       </c>
       <c r="R9" t="n">
-        <v>6995705</v>
+        <v>6995652</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,7 +1462,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,7 +1489,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130350860</v>
+        <v>130350870</v>
       </c>
       <c r="B10" t="n">
         <v>57852</v>
@@ -1529,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>648687</v>
+        <v>649039</v>
       </c>
       <c r="R10" t="n">
-        <v>6995932</v>
+        <v>6995705</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130350904</v>
+        <v>130350860</v>
       </c>
       <c r="B11" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,21 +1602,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1631,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649056</v>
+        <v>648687</v>
       </c>
       <c r="R11" t="n">
-        <v>6995686</v>
+        <v>6995932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,6 +1662,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130351125</v>
+        <v>130350844</v>
       </c>
       <c r="B14" t="n">
-        <v>92176</v>
+        <v>91757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>648877</v>
+        <v>649036</v>
       </c>
       <c r="R14" t="n">
-        <v>6995565</v>
+        <v>6995660</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130350844</v>
+        <v>130350903</v>
       </c>
       <c r="B15" t="n">
-        <v>91757</v>
+        <v>79209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>649036</v>
+        <v>648792</v>
       </c>
       <c r="R15" t="n">
-        <v>6995660</v>
+        <v>6995927</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130350899</v>
+        <v>130350861</v>
       </c>
       <c r="B16" t="n">
-        <v>91777</v>
+        <v>57852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,19 +2102,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2122,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648996</v>
+        <v>648707</v>
       </c>
       <c r="R16" t="n">
-        <v>6995647</v>
+        <v>6995954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,6 +2162,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2184,10 +2193,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130350903</v>
+        <v>130351125</v>
       </c>
       <c r="B17" t="n">
-        <v>79209</v>
+        <v>92176</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,21 +2204,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2228,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648792</v>
+        <v>648877</v>
       </c>
       <c r="R17" t="n">
-        <v>6995927</v>
+        <v>6995565</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,10 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130350861</v>
+        <v>130350899</v>
       </c>
       <c r="B18" t="n">
-        <v>57852</v>
+        <v>91777</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,23 +2301,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2316,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648707</v>
+        <v>648996</v>
       </c>
       <c r="R18" t="n">
-        <v>6995954</v>
+        <v>6995647</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,11 +2357,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -5453,32 +5453,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130350883</v>
+        <v>130350909</v>
       </c>
       <c r="B50" t="n">
-        <v>80342</v>
+        <v>89151</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>649094</v>
+        <v>648957</v>
       </c>
       <c r="R50" t="n">
-        <v>6995519</v>
+        <v>6995579</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130350909</v>
+        <v>130350839</v>
       </c>
       <c r="B51" t="n">
-        <v>89151</v>
+        <v>91757</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>648957</v>
+        <v>649369</v>
       </c>
       <c r="R51" t="n">
-        <v>6995579</v>
+        <v>6995531</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,32 +5647,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350839</v>
+        <v>130350883</v>
       </c>
       <c r="B52" t="n">
-        <v>91757</v>
+        <v>80342</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>649369</v>
+        <v>649094</v>
       </c>
       <c r="R52" t="n">
-        <v>6995531</v>
+        <v>6995519</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350864</v>
+        <v>130350879</v>
       </c>
       <c r="B54" t="n">
-        <v>57852</v>
+        <v>92055</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>648993</v>
+        <v>649062</v>
       </c>
       <c r="R54" t="n">
-        <v>6995756</v>
+        <v>6995641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5912,11 +5912,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5943,7 +5938,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130350867</v>
+        <v>130350864</v>
       </c>
       <c r="B55" t="n">
         <v>57852</v>
@@ -5978,10 +5973,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>649095</v>
+        <v>648993</v>
       </c>
       <c r="R55" t="n">
-        <v>6995637</v>
+        <v>6995756</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6018,7 +6013,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6045,10 +6040,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130350879</v>
+        <v>130350867</v>
       </c>
       <c r="B56" t="n">
-        <v>92055</v>
+        <v>57852</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6056,21 +6051,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6080,10 +6075,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>649062</v>
+        <v>649095</v>
       </c>
       <c r="R56" t="n">
-        <v>6995641</v>
+        <v>6995637</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6116,6 +6111,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6637,10 +6637,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130350862</v>
+        <v>130350842</v>
       </c>
       <c r="B62" t="n">
-        <v>57852</v>
+        <v>91757</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6648,21 +6648,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>648830</v>
+        <v>649096</v>
       </c>
       <c r="R62" t="n">
-        <v>6995874</v>
+        <v>6995501</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6708,11 +6708,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6938,32 +6933,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350842</v>
+        <v>130350889</v>
       </c>
       <c r="B65" t="n">
-        <v>91757</v>
+        <v>80274</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6973,10 +6968,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>649096</v>
+        <v>649384</v>
       </c>
       <c r="R65" t="n">
-        <v>6995501</v>
+        <v>6995514</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7035,32 +7030,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130350889</v>
+        <v>130350893</v>
       </c>
       <c r="B66" t="n">
-        <v>80274</v>
+        <v>57033</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>102612</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7070,10 +7065,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>649384</v>
+        <v>649144</v>
       </c>
       <c r="R66" t="n">
-        <v>6995514</v>
+        <v>6995799</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7106,6 +7101,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7132,10 +7132,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130350893</v>
+        <v>130350862</v>
       </c>
       <c r="B67" t="n">
-        <v>57033</v>
+        <v>57852</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7143,16 +7143,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7167,10 +7167,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649144</v>
+        <v>648830</v>
       </c>
       <c r="R67" t="n">
-        <v>6995799</v>
+        <v>6995874</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350902</v>
+        <v>130350908</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>89152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648702</v>
+        <v>649250</v>
       </c>
       <c r="R4" t="n">
-        <v>6995939</v>
+        <v>6995605</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350908</v>
+        <v>130350902</v>
       </c>
       <c r="B5" t="n">
-        <v>89151</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649250</v>
+        <v>648702</v>
       </c>
       <c r="R5" t="n">
-        <v>6995605</v>
+        <v>6995939</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1900,7 +1900,7 @@
         <v>130350844</v>
       </c>
       <c r="B14" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130350861</v>
+        <v>130351125</v>
       </c>
       <c r="B16" t="n">
-        <v>57852</v>
+        <v>92177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648707</v>
+        <v>648877</v>
       </c>
       <c r="R16" t="n">
-        <v>6995954</v>
+        <v>6995565</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,11 +2162,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,10 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130351125</v>
+        <v>130350899</v>
       </c>
       <c r="B17" t="n">
-        <v>92176</v>
+        <v>91778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2204,23 +2199,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6040186</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2228,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648877</v>
+        <v>648996</v>
       </c>
       <c r="R17" t="n">
-        <v>6995565</v>
+        <v>6995647</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130350899</v>
+        <v>130350861</v>
       </c>
       <c r="B18" t="n">
-        <v>91777</v>
+        <v>57852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,19 +2292,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2321,10 +2316,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648996</v>
+        <v>648707</v>
       </c>
       <c r="R18" t="n">
-        <v>6995647</v>
+        <v>6995954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,6 +2352,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2386,7 +2386,7 @@
         <v>130350838</v>
       </c>
       <c r="B19" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130351124</v>
+        <v>130350868</v>
       </c>
       <c r="B20" t="n">
-        <v>92176</v>
+        <v>57852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2491,21 +2491,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649116</v>
+        <v>649093</v>
       </c>
       <c r="R20" t="n">
-        <v>6995496</v>
+        <v>6995638</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,6 +2551,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2577,7 +2582,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130350868</v>
+        <v>130350863</v>
       </c>
       <c r="B21" t="n">
         <v>57852</v>
@@ -2612,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>649093</v>
+        <v>649031</v>
       </c>
       <c r="R21" t="n">
-        <v>6995638</v>
+        <v>6995803</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,7 +2684,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130350863</v>
+        <v>130350847</v>
       </c>
       <c r="B22" t="n">
         <v>57852</v>
@@ -2714,10 +2719,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>649031</v>
+        <v>649222</v>
       </c>
       <c r="R22" t="n">
-        <v>6995803</v>
+        <v>6995657</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2754,7 +2759,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2781,10 +2786,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130350847</v>
+        <v>130351124</v>
       </c>
       <c r="B23" t="n">
-        <v>57852</v>
+        <v>92177</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2792,21 +2797,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2816,10 +2821,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649222</v>
+        <v>649116</v>
       </c>
       <c r="R23" t="n">
-        <v>6995657</v>
+        <v>6995496</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,11 +2857,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3080,7 +3080,7 @@
         <v>130350878</v>
       </c>
       <c r="B26" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>130350877</v>
       </c>
       <c r="B27" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,32 +3475,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350846</v>
+        <v>130350891</v>
       </c>
       <c r="B30" t="n">
-        <v>91757</v>
+        <v>80274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>649063</v>
+        <v>649044</v>
       </c>
       <c r="R30" t="n">
-        <v>6995635</v>
+        <v>6995628</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130350898</v>
+        <v>130350846</v>
       </c>
       <c r="B31" t="n">
-        <v>91777</v>
+        <v>91758</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3583,19 +3583,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3603,10 +3607,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>648849</v>
+        <v>649063</v>
       </c>
       <c r="R31" t="n">
-        <v>6995437</v>
+        <v>6995635</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3665,10 +3669,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350858</v>
+        <v>130350898</v>
       </c>
       <c r="B32" t="n">
-        <v>57852</v>
+        <v>91778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,23 +3680,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>648826</v>
+        <v>648849</v>
       </c>
       <c r="R32" t="n">
-        <v>6995403</v>
+        <v>6995437</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,11 +3736,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3767,32 +3762,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130350891</v>
+        <v>130350858</v>
       </c>
       <c r="B33" t="n">
-        <v>80274</v>
+        <v>57852</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3802,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>649044</v>
+        <v>648826</v>
       </c>
       <c r="R33" t="n">
-        <v>6995628</v>
+        <v>6995403</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,6 +3833,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4173,7 +4173,7 @@
         <v>130350911</v>
       </c>
       <c r="B37" t="n">
-        <v>89151</v>
+        <v>89152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>130350840</v>
       </c>
       <c r="B39" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>130350897</v>
       </c>
       <c r="B40" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>130350845</v>
       </c>
       <c r="B42" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350837</v>
+        <v>130350896</v>
       </c>
       <c r="B43" t="n">
-        <v>91944</v>
+        <v>91778</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,23 +4769,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1588</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4793,10 +4789,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>649254</v>
+        <v>648854</v>
       </c>
       <c r="R43" t="n">
-        <v>6995609</v>
+        <v>6995532</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4855,10 +4851,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350896</v>
+        <v>130350892</v>
       </c>
       <c r="B44" t="n">
-        <v>91777</v>
+        <v>57033</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,19 +4862,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648854</v>
+        <v>649126</v>
       </c>
       <c r="R44" t="n">
-        <v>6995532</v>
+        <v>6995764</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4922,6 +4922,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4948,10 +4953,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350886</v>
+        <v>130350837</v>
       </c>
       <c r="B45" t="n">
-        <v>80314</v>
+        <v>91945</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4959,21 +4964,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4983,10 +4988,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648997</v>
+        <v>649254</v>
       </c>
       <c r="R45" t="n">
-        <v>6995649</v>
+        <v>6995609</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5045,10 +5050,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350892</v>
+        <v>130350886</v>
       </c>
       <c r="B46" t="n">
-        <v>57033</v>
+        <v>80314</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5056,21 +5061,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5080,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>649126</v>
+        <v>648997</v>
       </c>
       <c r="R46" t="n">
-        <v>6995764</v>
+        <v>6995649</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5116,11 +5121,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5453,10 +5453,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130350909</v>
+        <v>130350839</v>
       </c>
       <c r="B50" t="n">
-        <v>89151</v>
+        <v>91758</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5464,21 +5464,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>648957</v>
+        <v>649369</v>
       </c>
       <c r="R50" t="n">
-        <v>6995579</v>
+        <v>6995531</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5550,32 +5550,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130350839</v>
+        <v>130350883</v>
       </c>
       <c r="B51" t="n">
-        <v>91757</v>
+        <v>80342</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>649369</v>
+        <v>649094</v>
       </c>
       <c r="R51" t="n">
-        <v>6995531</v>
+        <v>6995519</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,32 +5647,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350883</v>
+        <v>130350909</v>
       </c>
       <c r="B52" t="n">
-        <v>80342</v>
+        <v>89152</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>649094</v>
+        <v>648957</v>
       </c>
       <c r="R52" t="n">
-        <v>6995519</v>
+        <v>6995579</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5747,7 +5747,7 @@
         <v>130350841</v>
       </c>
       <c r="B53" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>130350879</v>
       </c>
       <c r="B54" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350901</v>
+        <v>130350874</v>
       </c>
       <c r="B58" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648771</v>
+        <v>648811</v>
       </c>
       <c r="R58" t="n">
-        <v>6995702</v>
+        <v>6995477</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,6 +6310,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6336,7 +6341,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350874</v>
+        <v>130350876</v>
       </c>
       <c r="B59" t="n">
         <v>57849</v>
@@ -6371,10 +6376,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>648811</v>
+        <v>649127</v>
       </c>
       <c r="R59" t="n">
-        <v>6995477</v>
+        <v>6995704</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,7 +6416,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6438,10 +6443,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350876</v>
+        <v>130350901</v>
       </c>
       <c r="B60" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6449,21 +6454,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6473,10 +6478,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>649127</v>
+        <v>648771</v>
       </c>
       <c r="R60" t="n">
-        <v>6995704</v>
+        <v>6995702</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6509,11 +6514,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6540,32 +6540,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130350910</v>
+        <v>130350881</v>
       </c>
       <c r="B61" t="n">
-        <v>89151</v>
+        <v>97821</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>648873</v>
+        <v>649111</v>
       </c>
       <c r="R61" t="n">
-        <v>6995569</v>
+        <v>6995725</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6637,32 +6637,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130350842</v>
+        <v>130350889</v>
       </c>
       <c r="B62" t="n">
-        <v>91757</v>
+        <v>80274</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>649096</v>
+        <v>649384</v>
       </c>
       <c r="R62" t="n">
-        <v>6995501</v>
+        <v>6995514</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350875</v>
+        <v>130350910</v>
       </c>
       <c r="B63" t="n">
-        <v>57849</v>
+        <v>89152</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>648755</v>
+        <v>648873</v>
       </c>
       <c r="R63" t="n">
-        <v>6995792</v>
+        <v>6995569</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6805,11 +6805,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6836,32 +6831,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350881</v>
+        <v>130350842</v>
       </c>
       <c r="B64" t="n">
-        <v>97820</v>
+        <v>91758</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6871,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>649111</v>
+        <v>649096</v>
       </c>
       <c r="R64" t="n">
-        <v>6995725</v>
+        <v>6995501</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6933,32 +6928,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350889</v>
+        <v>130350875</v>
       </c>
       <c r="B65" t="n">
-        <v>80274</v>
+        <v>57849</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6968,10 +6963,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>649384</v>
+        <v>648755</v>
       </c>
       <c r="R65" t="n">
-        <v>6995514</v>
+        <v>6995792</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7004,6 +6999,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7030,10 +7030,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130350893</v>
+        <v>130350862</v>
       </c>
       <c r="B66" t="n">
-        <v>57033</v>
+        <v>57852</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7041,16 +7041,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>649144</v>
+        <v>648830</v>
       </c>
       <c r="R66" t="n">
-        <v>6995799</v>
+        <v>6995874</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7132,10 +7132,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130350862</v>
+        <v>130350893</v>
       </c>
       <c r="B67" t="n">
-        <v>57852</v>
+        <v>57033</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7143,16 +7143,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7167,10 +7167,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>648830</v>
+        <v>649144</v>
       </c>
       <c r="R67" t="n">
-        <v>6995874</v>
+        <v>6995799</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7339,7 +7339,7 @@
         <v>130350884</v>
       </c>
       <c r="B69" t="n">
-        <v>96175</v>
+        <v>96176</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>130350908</v>
       </c>
       <c r="B4" t="n">
-        <v>89152</v>
+        <v>89153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350844</v>
+        <v>130350861</v>
       </c>
       <c r="B14" t="n">
-        <v>91758</v>
+        <v>57852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649036</v>
+        <v>648707</v>
       </c>
       <c r="R14" t="n">
-        <v>6995660</v>
+        <v>6995954</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,6 +1968,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1994,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130350903</v>
+        <v>130351125</v>
       </c>
       <c r="B15" t="n">
-        <v>79209</v>
+        <v>92178</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2010,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2034,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648792</v>
+        <v>648877</v>
       </c>
       <c r="R15" t="n">
-        <v>6995927</v>
+        <v>6995565</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,10 +2096,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130351125</v>
+        <v>130350899</v>
       </c>
       <c r="B16" t="n">
-        <v>92177</v>
+        <v>91779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,23 +2107,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2126,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648877</v>
+        <v>648996</v>
       </c>
       <c r="R16" t="n">
-        <v>6995565</v>
+        <v>6995647</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2188,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130350899</v>
+        <v>130350903</v>
       </c>
       <c r="B17" t="n">
-        <v>91778</v>
+        <v>79209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2199,19 +2200,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2219,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648996</v>
+        <v>648792</v>
       </c>
       <c r="R17" t="n">
-        <v>6995647</v>
+        <v>6995927</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,10 +2286,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130350861</v>
+        <v>130350844</v>
       </c>
       <c r="B18" t="n">
-        <v>57852</v>
+        <v>91759</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,21 +2297,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2316,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648707</v>
+        <v>649036</v>
       </c>
       <c r="R18" t="n">
-        <v>6995954</v>
+        <v>6995660</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,11 +2357,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2386,7 +2386,7 @@
         <v>130350838</v>
       </c>
       <c r="B19" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>130351124</v>
       </c>
       <c r="B23" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350900</v>
+        <v>130350878</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>92212</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>649027</v>
+        <v>649038</v>
       </c>
       <c r="R24" t="n">
-        <v>6995592</v>
+        <v>6995626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350905</v>
+        <v>130350877</v>
       </c>
       <c r="B25" t="n">
-        <v>79209</v>
+        <v>92212</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>649120</v>
+        <v>648991</v>
       </c>
       <c r="R25" t="n">
-        <v>6995740</v>
+        <v>6995659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130350878</v>
+        <v>130350900</v>
       </c>
       <c r="B26" t="n">
-        <v>92211</v>
+        <v>79209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>649038</v>
+        <v>649027</v>
       </c>
       <c r="R26" t="n">
-        <v>6995626</v>
+        <v>6995592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,32 +3174,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130350877</v>
+        <v>130350905</v>
       </c>
       <c r="B27" t="n">
-        <v>92211</v>
+        <v>79209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>648991</v>
+        <v>649120</v>
       </c>
       <c r="R27" t="n">
-        <v>6995659</v>
+        <v>6995740</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3475,32 +3475,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350891</v>
+        <v>130350846</v>
       </c>
       <c r="B30" t="n">
-        <v>80274</v>
+        <v>91759</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>649044</v>
+        <v>649063</v>
       </c>
       <c r="R30" t="n">
-        <v>6995628</v>
+        <v>6995635</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130350846</v>
+        <v>130350898</v>
       </c>
       <c r="B31" t="n">
-        <v>91758</v>
+        <v>91779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3583,23 +3583,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3607,10 +3603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>649063</v>
+        <v>648849</v>
       </c>
       <c r="R31" t="n">
-        <v>6995635</v>
+        <v>6995437</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3669,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350898</v>
+        <v>130350858</v>
       </c>
       <c r="B32" t="n">
-        <v>91778</v>
+        <v>57852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3680,19 +3676,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>648849</v>
+        <v>648826</v>
       </c>
       <c r="R32" t="n">
-        <v>6995437</v>
+        <v>6995403</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,6 +3736,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3762,32 +3767,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130350858</v>
+        <v>130350891</v>
       </c>
       <c r="B33" t="n">
-        <v>57852</v>
+        <v>80274</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3797,10 +3802,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>648826</v>
+        <v>649044</v>
       </c>
       <c r="R33" t="n">
-        <v>6995403</v>
+        <v>6995628</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3833,11 +3838,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4173,7 +4173,7 @@
         <v>130350911</v>
       </c>
       <c r="B37" t="n">
-        <v>89152</v>
+        <v>89153</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,10 +4369,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130350840</v>
+        <v>130350897</v>
       </c>
       <c r="B39" t="n">
-        <v>91758</v>
+        <v>91779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4380,23 +4380,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4404,10 +4400,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>649262</v>
+        <v>648848</v>
       </c>
       <c r="R39" t="n">
-        <v>6995647</v>
+        <v>6995528</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4466,10 +4462,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130350897</v>
+        <v>130350871</v>
       </c>
       <c r="B40" t="n">
-        <v>91778</v>
+        <v>57852</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4477,19 +4473,23 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>648848</v>
+        <v>649048</v>
       </c>
       <c r="R40" t="n">
-        <v>6995528</v>
+        <v>6995714</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4533,6 +4533,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4559,10 +4564,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130350871</v>
+        <v>130350840</v>
       </c>
       <c r="B41" t="n">
-        <v>57852</v>
+        <v>91759</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4570,21 +4575,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4594,10 +4599,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>649048</v>
+        <v>649262</v>
       </c>
       <c r="R41" t="n">
-        <v>6995714</v>
+        <v>6995647</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4630,11 +4635,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4664,7 +4664,7 @@
         <v>130350845</v>
       </c>
       <c r="B42" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350896</v>
+        <v>130350892</v>
       </c>
       <c r="B43" t="n">
-        <v>91778</v>
+        <v>57033</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,19 +4769,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4789,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>648854</v>
+        <v>649126</v>
       </c>
       <c r="R43" t="n">
-        <v>6995532</v>
+        <v>6995764</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4825,6 +4829,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4851,10 +4860,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350892</v>
+        <v>130350886</v>
       </c>
       <c r="B44" t="n">
-        <v>57033</v>
+        <v>80314</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4862,21 +4871,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4886,10 +4895,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>649126</v>
+        <v>648997</v>
       </c>
       <c r="R44" t="n">
-        <v>6995764</v>
+        <v>6995649</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4922,11 +4931,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,7 +4960,7 @@
         <v>130350837</v>
       </c>
       <c r="B45" t="n">
-        <v>91945</v>
+        <v>91946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5050,10 +5054,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350886</v>
+        <v>130350896</v>
       </c>
       <c r="B46" t="n">
-        <v>80314</v>
+        <v>91779</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5061,23 +5065,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648997</v>
+        <v>648854</v>
       </c>
       <c r="R46" t="n">
-        <v>6995649</v>
+        <v>6995532</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5456,7 +5456,7 @@
         <v>130350839</v>
       </c>
       <c r="B50" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5550,32 +5550,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130350883</v>
+        <v>130350909</v>
       </c>
       <c r="B51" t="n">
-        <v>80342</v>
+        <v>89153</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>649094</v>
+        <v>648957</v>
       </c>
       <c r="R51" t="n">
-        <v>6995519</v>
+        <v>6995579</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,32 +5647,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350909</v>
+        <v>130350883</v>
       </c>
       <c r="B52" t="n">
-        <v>89152</v>
+        <v>80342</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>510</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>648957</v>
+        <v>649094</v>
       </c>
       <c r="R52" t="n">
-        <v>6995579</v>
+        <v>6995519</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5744,32 +5744,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350841</v>
+        <v>130350890</v>
       </c>
       <c r="B53" t="n">
-        <v>91758</v>
+        <v>80274</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649195</v>
+        <v>649374</v>
       </c>
       <c r="R53" t="n">
-        <v>6995694</v>
+        <v>6995542</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350879</v>
+        <v>130350864</v>
       </c>
       <c r="B54" t="n">
-        <v>92056</v>
+        <v>57852</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>649062</v>
+        <v>648993</v>
       </c>
       <c r="R54" t="n">
-        <v>6995641</v>
+        <v>6995756</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5912,6 +5912,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5938,7 +5943,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130350864</v>
+        <v>130350867</v>
       </c>
       <c r="B55" t="n">
         <v>57852</v>
@@ -5973,10 +5978,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>648993</v>
+        <v>649095</v>
       </c>
       <c r="R55" t="n">
-        <v>6995756</v>
+        <v>6995637</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6013,7 +6018,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6040,10 +6045,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130350867</v>
+        <v>130350841</v>
       </c>
       <c r="B56" t="n">
-        <v>57852</v>
+        <v>91759</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6051,21 +6056,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6075,10 +6080,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>649095</v>
+        <v>649195</v>
       </c>
       <c r="R56" t="n">
-        <v>6995637</v>
+        <v>6995694</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6111,11 +6116,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6142,32 +6142,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130350890</v>
+        <v>130350879</v>
       </c>
       <c r="B57" t="n">
-        <v>80274</v>
+        <v>92057</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>649374</v>
+        <v>649062</v>
       </c>
       <c r="R57" t="n">
-        <v>6995542</v>
+        <v>6995641</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350874</v>
+        <v>130350901</v>
       </c>
       <c r="B58" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648811</v>
+        <v>648771</v>
       </c>
       <c r="R58" t="n">
-        <v>6995477</v>
+        <v>6995702</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,11 +6310,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6443,10 +6438,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350901</v>
+        <v>130350874</v>
       </c>
       <c r="B60" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6454,21 +6449,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6478,10 +6473,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>648771</v>
+        <v>648811</v>
       </c>
       <c r="R60" t="n">
-        <v>6995702</v>
+        <v>6995477</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6514,6 +6509,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6540,32 +6540,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130350881</v>
+        <v>130350910</v>
       </c>
       <c r="B61" t="n">
-        <v>97821</v>
+        <v>89153</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>649111</v>
+        <v>648873</v>
       </c>
       <c r="R61" t="n">
-        <v>6995725</v>
+        <v>6995569</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6637,32 +6637,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130350889</v>
+        <v>130350842</v>
       </c>
       <c r="B62" t="n">
-        <v>80274</v>
+        <v>91759</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>649384</v>
+        <v>649096</v>
       </c>
       <c r="R62" t="n">
-        <v>6995514</v>
+        <v>6995501</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350910</v>
+        <v>130350875</v>
       </c>
       <c r="B63" t="n">
-        <v>89152</v>
+        <v>57849</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>648873</v>
+        <v>648755</v>
       </c>
       <c r="R63" t="n">
-        <v>6995569</v>
+        <v>6995792</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6805,6 +6805,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6831,10 +6836,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350842</v>
+        <v>130350893</v>
       </c>
       <c r="B64" t="n">
-        <v>91758</v>
+        <v>57033</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,21 +6847,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6866,10 +6871,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>649096</v>
+        <v>649144</v>
       </c>
       <c r="R64" t="n">
-        <v>6995501</v>
+        <v>6995799</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6902,6 +6907,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6928,32 +6938,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350875</v>
+        <v>130350889</v>
       </c>
       <c r="B65" t="n">
-        <v>57849</v>
+        <v>80274</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6963,10 +6973,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>648755</v>
+        <v>649384</v>
       </c>
       <c r="R65" t="n">
-        <v>6995792</v>
+        <v>6995514</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6999,11 +7009,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7132,32 +7137,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130350893</v>
+        <v>130350881</v>
       </c>
       <c r="B67" t="n">
-        <v>57033</v>
+        <v>97822</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7167,10 +7172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649144</v>
+        <v>649111</v>
       </c>
       <c r="R67" t="n">
-        <v>6995799</v>
+        <v>6995725</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7203,11 +7208,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7339,7 +7339,7 @@
         <v>130350884</v>
       </c>
       <c r="B69" t="n">
-        <v>96176</v>
+        <v>96177</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130350885</v>
       </c>
       <c r="B3" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>130350908</v>
       </c>
       <c r="B4" t="n">
-        <v>89153</v>
+        <v>89155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>130350902</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>130350873</v>
       </c>
       <c r="B6" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>130350865</v>
       </c>
       <c r="B7" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>130350904</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>130350866</v>
       </c>
       <c r="B9" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>130350870</v>
       </c>
       <c r="B10" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>130350860</v>
       </c>
       <c r="B11" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>130350853</v>
       </c>
       <c r="B12" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130350857</v>
       </c>
       <c r="B13" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350861</v>
+        <v>130350844</v>
       </c>
       <c r="B14" t="n">
-        <v>57852</v>
+        <v>91761</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>648707</v>
+        <v>649036</v>
       </c>
       <c r="R14" t="n">
-        <v>6995954</v>
+        <v>6995660</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,11 +1968,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1999,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130351125</v>
+        <v>130350903</v>
       </c>
       <c r="B15" t="n">
-        <v>92178</v>
+        <v>79211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2034,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648877</v>
+        <v>648792</v>
       </c>
       <c r="R15" t="n">
-        <v>6995565</v>
+        <v>6995927</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,7 +2094,7 @@
         <v>130350899</v>
       </c>
       <c r="B16" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130350903</v>
+        <v>130351125</v>
       </c>
       <c r="B17" t="n">
-        <v>79209</v>
+        <v>92180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2195,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648792</v>
+        <v>648877</v>
       </c>
       <c r="R17" t="n">
-        <v>6995927</v>
+        <v>6995565</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130350844</v>
+        <v>130350861</v>
       </c>
       <c r="B18" t="n">
-        <v>91759</v>
+        <v>57854</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,21 +2292,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2316,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>649036</v>
+        <v>648707</v>
       </c>
       <c r="R18" t="n">
-        <v>6995660</v>
+        <v>6995954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,6 +2352,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130350838</v>
+        <v>130351124</v>
       </c>
       <c r="B19" t="n">
-        <v>91723</v>
+        <v>92180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6040186</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649074</v>
+        <v>649116</v>
       </c>
       <c r="R19" t="n">
-        <v>6995652</v>
+        <v>6995496</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,32 +2480,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130350868</v>
+        <v>130350838</v>
       </c>
       <c r="B20" t="n">
-        <v>57852</v>
+        <v>91725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649093</v>
+        <v>649074</v>
       </c>
       <c r="R20" t="n">
-        <v>6995638</v>
+        <v>6995652</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,11 +2551,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2582,10 +2577,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130350863</v>
+        <v>130350868</v>
       </c>
       <c r="B21" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2617,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>649031</v>
+        <v>649093</v>
       </c>
       <c r="R21" t="n">
-        <v>6995803</v>
+        <v>6995638</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,10 +2679,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130350847</v>
+        <v>130350863</v>
       </c>
       <c r="B22" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2719,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>649222</v>
+        <v>649031</v>
       </c>
       <c r="R22" t="n">
-        <v>6995657</v>
+        <v>6995803</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2759,7 +2754,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2786,10 +2781,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351124</v>
+        <v>130350847</v>
       </c>
       <c r="B23" t="n">
-        <v>92178</v>
+        <v>57854</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2797,21 +2792,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2821,10 +2816,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649116</v>
+        <v>649222</v>
       </c>
       <c r="R23" t="n">
-        <v>6995496</v>
+        <v>6995657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2857,6 +2852,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2886,7 +2886,7 @@
         <v>130350878</v>
       </c>
       <c r="B24" t="n">
-        <v>92212</v>
+        <v>92214</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>130350877</v>
       </c>
       <c r="B25" t="n">
-        <v>92212</v>
+        <v>92214</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>130350900</v>
       </c>
       <c r="B26" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>130350905</v>
       </c>
       <c r="B27" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>130350849</v>
       </c>
       <c r="B28" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>130350850</v>
       </c>
       <c r="B29" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>130350846</v>
       </c>
       <c r="B30" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>130350898</v>
       </c>
       <c r="B31" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>130350858</v>
       </c>
       <c r="B32" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>130350891</v>
       </c>
       <c r="B33" t="n">
-        <v>80274</v>
+        <v>80276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>130350852</v>
       </c>
       <c r="B34" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>130350869</v>
       </c>
       <c r="B35" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>130350855</v>
       </c>
       <c r="B36" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>130350911</v>
       </c>
       <c r="B37" t="n">
-        <v>89153</v>
+        <v>89155</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>130350872</v>
       </c>
       <c r="B38" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4369,10 +4369,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130350897</v>
+        <v>130350840</v>
       </c>
       <c r="B39" t="n">
-        <v>91779</v>
+        <v>91761</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4380,19 +4380,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4400,10 +4404,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>648848</v>
+        <v>649262</v>
       </c>
       <c r="R39" t="n">
-        <v>6995528</v>
+        <v>6995647</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4462,10 +4466,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130350871</v>
+        <v>130350897</v>
       </c>
       <c r="B40" t="n">
-        <v>57852</v>
+        <v>91781</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4473,23 +4477,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>649048</v>
+        <v>648848</v>
       </c>
       <c r="R40" t="n">
-        <v>6995714</v>
+        <v>6995528</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4533,11 +4533,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4564,10 +4559,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130350840</v>
+        <v>130350871</v>
       </c>
       <c r="B41" t="n">
-        <v>91759</v>
+        <v>57854</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,21 +4570,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4599,10 +4594,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>649262</v>
+        <v>649048</v>
       </c>
       <c r="R41" t="n">
-        <v>6995647</v>
+        <v>6995714</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4635,6 +4630,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4664,7 +4664,7 @@
         <v>130350845</v>
       </c>
       <c r="B42" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350892</v>
+        <v>130350886</v>
       </c>
       <c r="B43" t="n">
-        <v>57033</v>
+        <v>80316</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>649126</v>
+        <v>648997</v>
       </c>
       <c r="R43" t="n">
-        <v>6995764</v>
+        <v>6995649</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4829,11 +4829,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4860,10 +4855,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350886</v>
+        <v>130350896</v>
       </c>
       <c r="B44" t="n">
-        <v>80314</v>
+        <v>91781</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,23 +4866,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4895,10 +4886,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648997</v>
+        <v>648854</v>
       </c>
       <c r="R44" t="n">
-        <v>6995649</v>
+        <v>6995532</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4957,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350837</v>
+        <v>130350892</v>
       </c>
       <c r="B45" t="n">
-        <v>91946</v>
+        <v>57035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,21 +4959,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1588</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4992,10 +4983,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>649254</v>
+        <v>649126</v>
       </c>
       <c r="R45" t="n">
-        <v>6995609</v>
+        <v>6995764</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5028,6 +5019,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5054,10 +5050,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350896</v>
+        <v>130350837</v>
       </c>
       <c r="B46" t="n">
-        <v>91779</v>
+        <v>91948</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,19 +5061,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>1588</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648854</v>
+        <v>649254</v>
       </c>
       <c r="R46" t="n">
-        <v>6995532</v>
+        <v>6995609</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5150,7 +5150,7 @@
         <v>130350859</v>
       </c>
       <c r="B47" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>130350856</v>
       </c>
       <c r="B48" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>130350854</v>
       </c>
       <c r="B49" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>130350839</v>
       </c>
       <c r="B50" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>130350909</v>
       </c>
       <c r="B51" t="n">
-        <v>89153</v>
+        <v>89155</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>130350883</v>
       </c>
       <c r="B52" t="n">
-        <v>80342</v>
+        <v>80344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5744,32 +5744,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350890</v>
+        <v>130350841</v>
       </c>
       <c r="B53" t="n">
-        <v>80274</v>
+        <v>91761</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649374</v>
+        <v>649195</v>
       </c>
       <c r="R53" t="n">
-        <v>6995542</v>
+        <v>6995694</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350864</v>
+        <v>130350879</v>
       </c>
       <c r="B54" t="n">
-        <v>57852</v>
+        <v>92059</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>648993</v>
+        <v>649062</v>
       </c>
       <c r="R54" t="n">
-        <v>6995756</v>
+        <v>6995641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5912,11 +5912,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5943,10 +5938,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130350867</v>
+        <v>130350864</v>
       </c>
       <c r="B55" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5978,10 +5973,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>649095</v>
+        <v>648993</v>
       </c>
       <c r="R55" t="n">
-        <v>6995637</v>
+        <v>6995756</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6018,7 +6013,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6045,10 +6040,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130350841</v>
+        <v>130350867</v>
       </c>
       <c r="B56" t="n">
-        <v>91759</v>
+        <v>57854</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6056,21 +6051,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6080,10 +6075,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>649195</v>
+        <v>649095</v>
       </c>
       <c r="R56" t="n">
-        <v>6995694</v>
+        <v>6995637</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6116,6 +6111,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6142,32 +6142,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130350879</v>
+        <v>130350890</v>
       </c>
       <c r="B57" t="n">
-        <v>92057</v>
+        <v>80276</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>649062</v>
+        <v>649374</v>
       </c>
       <c r="R57" t="n">
-        <v>6995641</v>
+        <v>6995542</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6242,7 +6242,7 @@
         <v>130350901</v>
       </c>
       <c r="B58" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350876</v>
+        <v>130350874</v>
       </c>
       <c r="B59" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>649127</v>
+        <v>648811</v>
       </c>
       <c r="R59" t="n">
-        <v>6995704</v>
+        <v>6995477</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6438,10 +6438,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350874</v>
+        <v>130350876</v>
       </c>
       <c r="B60" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>648811</v>
+        <v>649127</v>
       </c>
       <c r="R60" t="n">
-        <v>6995477</v>
+        <v>6995704</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6540,10 +6540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130350910</v>
+        <v>130350862</v>
       </c>
       <c r="B61" t="n">
-        <v>89153</v>
+        <v>57854</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>648873</v>
+        <v>648830</v>
       </c>
       <c r="R61" t="n">
-        <v>6995569</v>
+        <v>6995874</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6611,6 +6611,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6637,10 +6642,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130350842</v>
+        <v>130350875</v>
       </c>
       <c r="B62" t="n">
-        <v>91759</v>
+        <v>57851</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6648,21 +6653,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>649096</v>
+        <v>648755</v>
       </c>
       <c r="R62" t="n">
-        <v>6995501</v>
+        <v>6995792</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6708,6 +6713,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6734,10 +6744,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350875</v>
+        <v>130350893</v>
       </c>
       <c r="B63" t="n">
-        <v>57849</v>
+        <v>57035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,16 +6755,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6769,10 +6779,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>648755</v>
+        <v>649144</v>
       </c>
       <c r="R63" t="n">
-        <v>6995792</v>
+        <v>6995799</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,7 +6819,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6836,32 +6846,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350893</v>
+        <v>130350881</v>
       </c>
       <c r="B64" t="n">
-        <v>57033</v>
+        <v>97824</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6871,10 +6881,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>649144</v>
+        <v>649111</v>
       </c>
       <c r="R64" t="n">
-        <v>6995799</v>
+        <v>6995725</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6907,11 +6917,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6941,7 +6946,7 @@
         <v>130350889</v>
       </c>
       <c r="B65" t="n">
-        <v>80274</v>
+        <v>80276</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7035,10 +7040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130350862</v>
+        <v>130350910</v>
       </c>
       <c r="B66" t="n">
-        <v>57852</v>
+        <v>89155</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7046,21 +7051,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7070,10 +7075,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>648830</v>
+        <v>648873</v>
       </c>
       <c r="R66" t="n">
-        <v>6995874</v>
+        <v>6995569</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7106,11 +7111,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7137,32 +7137,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130350881</v>
+        <v>130350842</v>
       </c>
       <c r="B67" t="n">
-        <v>97822</v>
+        <v>91761</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649111</v>
+        <v>649096</v>
       </c>
       <c r="R67" t="n">
-        <v>6995725</v>
+        <v>6995501</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7237,7 +7237,7 @@
         <v>130350848</v>
       </c>
       <c r="B68" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>130350884</v>
       </c>
       <c r="B69" t="n">
-        <v>96177</v>
+        <v>96179</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350908</v>
+        <v>130350873</v>
       </c>
       <c r="B4" t="n">
-        <v>89155</v>
+        <v>57044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649250</v>
+        <v>649139</v>
       </c>
       <c r="R4" t="n">
-        <v>6995605</v>
+        <v>6995673</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350902</v>
+        <v>130350908</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>89155</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648702</v>
+        <v>649250</v>
       </c>
       <c r="R5" t="n">
-        <v>6995939</v>
+        <v>6995605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,32 +1091,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130350873</v>
+        <v>130350902</v>
       </c>
       <c r="B6" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649139</v>
+        <v>648702</v>
       </c>
       <c r="R6" t="n">
-        <v>6995673</v>
+        <v>6995939</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,11 +1162,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350844</v>
+        <v>130350903</v>
       </c>
       <c r="B14" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649036</v>
+        <v>648792</v>
       </c>
       <c r="R14" t="n">
-        <v>6995660</v>
+        <v>6995927</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130350903</v>
+        <v>130350844</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>91761</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648792</v>
+        <v>649036</v>
       </c>
       <c r="R15" t="n">
-        <v>6995927</v>
+        <v>6995660</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130351125</v>
+        <v>130350861</v>
       </c>
       <c r="B17" t="n">
-        <v>92180</v>
+        <v>57854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,21 +2195,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648877</v>
+        <v>648707</v>
       </c>
       <c r="R17" t="n">
-        <v>6995565</v>
+        <v>6995954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,6 +2255,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2281,10 +2286,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130350861</v>
+        <v>130351125</v>
       </c>
       <c r="B18" t="n">
-        <v>57854</v>
+        <v>92180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,21 +2297,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2316,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648707</v>
+        <v>648877</v>
       </c>
       <c r="R18" t="n">
-        <v>6995954</v>
+        <v>6995565</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,11 +2357,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2383,10 +2383,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130351124</v>
+        <v>130350868</v>
       </c>
       <c r="B19" t="n">
-        <v>92180</v>
+        <v>57854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2394,21 +2394,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649116</v>
+        <v>649093</v>
       </c>
       <c r="R19" t="n">
-        <v>6995496</v>
+        <v>6995638</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,6 +2454,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2480,32 +2485,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130350838</v>
+        <v>130350863</v>
       </c>
       <c r="B20" t="n">
-        <v>91725</v>
+        <v>57854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649074</v>
+        <v>649031</v>
       </c>
       <c r="R20" t="n">
-        <v>6995652</v>
+        <v>6995803</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,6 +2556,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2577,7 +2587,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130350868</v>
+        <v>130350847</v>
       </c>
       <c r="B21" t="n">
         <v>57854</v>
@@ -2612,10 +2622,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>649093</v>
+        <v>649222</v>
       </c>
       <c r="R21" t="n">
-        <v>6995638</v>
+        <v>6995657</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2652,7 +2662,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2679,32 +2689,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130350863</v>
+        <v>130350838</v>
       </c>
       <c r="B22" t="n">
-        <v>57854</v>
+        <v>91725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2714,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>649031</v>
+        <v>649074</v>
       </c>
       <c r="R22" t="n">
-        <v>6995803</v>
+        <v>6995652</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2750,11 +2760,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2781,10 +2786,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130350847</v>
+        <v>130351124</v>
       </c>
       <c r="B23" t="n">
-        <v>57854</v>
+        <v>92180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2792,21 +2797,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2816,10 +2821,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649222</v>
+        <v>649116</v>
       </c>
       <c r="R23" t="n">
-        <v>6995657</v>
+        <v>6995496</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,11 +2857,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2883,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350878</v>
+        <v>130350900</v>
       </c>
       <c r="B24" t="n">
-        <v>92214</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>649038</v>
+        <v>649027</v>
       </c>
       <c r="R24" t="n">
-        <v>6995626</v>
+        <v>6995592</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350877</v>
+        <v>130350905</v>
       </c>
       <c r="B25" t="n">
-        <v>92214</v>
+        <v>79211</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>648991</v>
+        <v>649120</v>
       </c>
       <c r="R25" t="n">
-        <v>6995659</v>
+        <v>6995740</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130350900</v>
+        <v>130350878</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>92220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>649027</v>
+        <v>649038</v>
       </c>
       <c r="R26" t="n">
-        <v>6995592</v>
+        <v>6995626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,32 +3174,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130350905</v>
+        <v>130350877</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>92220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>649120</v>
+        <v>648991</v>
       </c>
       <c r="R27" t="n">
-        <v>6995740</v>
+        <v>6995659</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130350911</v>
+        <v>130350872</v>
       </c>
       <c r="B37" t="n">
-        <v>89155</v>
+        <v>57854</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4181,21 +4181,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>648698</v>
+        <v>649146</v>
       </c>
       <c r="R37" t="n">
-        <v>6995926</v>
+        <v>6995662</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4241,6 +4241,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4267,10 +4272,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130350872</v>
+        <v>130350911</v>
       </c>
       <c r="B38" t="n">
-        <v>57854</v>
+        <v>89155</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4278,21 +4283,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4302,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>649146</v>
+        <v>648698</v>
       </c>
       <c r="R38" t="n">
-        <v>6995662</v>
+        <v>6995926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4338,11 +4343,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350886</v>
+        <v>130350892</v>
       </c>
       <c r="B43" t="n">
-        <v>80316</v>
+        <v>57035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>648997</v>
+        <v>649126</v>
       </c>
       <c r="R43" t="n">
-        <v>6995649</v>
+        <v>6995764</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4829,6 +4829,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4855,10 +4860,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350896</v>
+        <v>130350859</v>
       </c>
       <c r="B44" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,19 +4871,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4886,10 +4895,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648854</v>
+        <v>648771</v>
       </c>
       <c r="R44" t="n">
-        <v>6995532</v>
+        <v>6995688</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4922,6 +4931,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4948,10 +4962,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350892</v>
+        <v>130350856</v>
       </c>
       <c r="B45" t="n">
-        <v>57035</v>
+        <v>57854</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4959,16 +4973,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4983,10 +4997,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>649126</v>
+        <v>648835</v>
       </c>
       <c r="R45" t="n">
-        <v>6995764</v>
+        <v>6995397</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5023,7 +5037,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5050,10 +5064,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350837</v>
+        <v>130350854</v>
       </c>
       <c r="B46" t="n">
-        <v>91948</v>
+        <v>57854</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5061,21 +5075,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5085,10 +5099,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>649254</v>
+        <v>648853</v>
       </c>
       <c r="R46" t="n">
-        <v>6995609</v>
+        <v>6995420</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5121,6 +5135,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5147,10 +5166,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350859</v>
+        <v>130350886</v>
       </c>
       <c r="B47" t="n">
-        <v>57854</v>
+        <v>80316</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,21 +5177,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5182,10 +5201,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648771</v>
+        <v>648997</v>
       </c>
       <c r="R47" t="n">
-        <v>6995688</v>
+        <v>6995649</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5218,11 +5237,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5249,10 +5263,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350856</v>
+        <v>130350896</v>
       </c>
       <c r="B48" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5260,23 +5274,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5284,10 +5294,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648835</v>
+        <v>648854</v>
       </c>
       <c r="R48" t="n">
-        <v>6995397</v>
+        <v>6995532</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5320,11 +5330,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5351,10 +5356,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350854</v>
+        <v>130350837</v>
       </c>
       <c r="B49" t="n">
-        <v>57854</v>
+        <v>91948</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,21 +5367,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5386,10 +5391,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>648853</v>
+        <v>649254</v>
       </c>
       <c r="R49" t="n">
-        <v>6995420</v>
+        <v>6995609</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5422,11 +5427,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5453,32 +5453,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130350839</v>
+        <v>130350883</v>
       </c>
       <c r="B50" t="n">
-        <v>91761</v>
+        <v>80344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>649369</v>
+        <v>649094</v>
       </c>
       <c r="R50" t="n">
-        <v>6995531</v>
+        <v>6995519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130350909</v>
+        <v>130350839</v>
       </c>
       <c r="B51" t="n">
-        <v>89155</v>
+        <v>91761</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>648957</v>
+        <v>649369</v>
       </c>
       <c r="R51" t="n">
-        <v>6995579</v>
+        <v>6995531</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,32 +5647,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350883</v>
+        <v>130350909</v>
       </c>
       <c r="B52" t="n">
-        <v>80344</v>
+        <v>89155</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>649094</v>
+        <v>648957</v>
       </c>
       <c r="R52" t="n">
-        <v>6995519</v>
+        <v>6995579</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350841</v>
+        <v>130350864</v>
       </c>
       <c r="B53" t="n">
-        <v>91761</v>
+        <v>57854</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5755,21 +5755,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649195</v>
+        <v>648993</v>
       </c>
       <c r="R53" t="n">
-        <v>6995694</v>
+        <v>6995756</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5815,6 +5815,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5841,10 +5846,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350879</v>
+        <v>130350867</v>
       </c>
       <c r="B54" t="n">
-        <v>92059</v>
+        <v>57854</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,21 +5857,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5881,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>649062</v>
+        <v>649095</v>
       </c>
       <c r="R54" t="n">
-        <v>6995641</v>
+        <v>6995637</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5912,6 +5917,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5938,32 +5948,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130350864</v>
+        <v>130350890</v>
       </c>
       <c r="B55" t="n">
-        <v>57854</v>
+        <v>80276</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5973,10 +5983,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>648993</v>
+        <v>649374</v>
       </c>
       <c r="R55" t="n">
-        <v>6995756</v>
+        <v>6995542</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6009,11 +6019,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6040,10 +6045,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130350867</v>
+        <v>130350841</v>
       </c>
       <c r="B56" t="n">
-        <v>57854</v>
+        <v>91761</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6051,21 +6056,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6075,10 +6080,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>649095</v>
+        <v>649195</v>
       </c>
       <c r="R56" t="n">
-        <v>6995637</v>
+        <v>6995694</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6111,11 +6116,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6142,32 +6142,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130350890</v>
+        <v>130350879</v>
       </c>
       <c r="B57" t="n">
-        <v>80276</v>
+        <v>92059</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>649374</v>
+        <v>649062</v>
       </c>
       <c r="R57" t="n">
-        <v>6995542</v>
+        <v>6995641</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6540,10 +6540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130350862</v>
+        <v>130350910</v>
       </c>
       <c r="B61" t="n">
-        <v>57854</v>
+        <v>89155</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>648830</v>
+        <v>648873</v>
       </c>
       <c r="R61" t="n">
-        <v>6995874</v>
+        <v>6995569</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6611,11 +6611,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6642,10 +6637,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130350875</v>
+        <v>130350842</v>
       </c>
       <c r="B62" t="n">
-        <v>57851</v>
+        <v>91761</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6653,21 +6648,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6677,10 +6672,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>648755</v>
+        <v>649096</v>
       </c>
       <c r="R62" t="n">
-        <v>6995792</v>
+        <v>6995501</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6713,11 +6708,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6744,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350893</v>
+        <v>130350875</v>
       </c>
       <c r="B63" t="n">
-        <v>57035</v>
+        <v>57851</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6755,16 +6745,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6779,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649144</v>
+        <v>648755</v>
       </c>
       <c r="R63" t="n">
-        <v>6995799</v>
+        <v>6995792</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6819,7 +6809,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6846,32 +6836,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350881</v>
+        <v>130350893</v>
       </c>
       <c r="B64" t="n">
-        <v>97824</v>
+        <v>57035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6881,10 +6871,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>649111</v>
+        <v>649144</v>
       </c>
       <c r="R64" t="n">
-        <v>6995725</v>
+        <v>6995799</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6917,6 +6907,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6943,32 +6938,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350889</v>
+        <v>130350862</v>
       </c>
       <c r="B65" t="n">
-        <v>80276</v>
+        <v>57854</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6978,10 +6973,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>649384</v>
+        <v>648830</v>
       </c>
       <c r="R65" t="n">
-        <v>6995514</v>
+        <v>6995874</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7014,6 +7009,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7040,32 +7040,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130350910</v>
+        <v>130350889</v>
       </c>
       <c r="B66" t="n">
-        <v>89155</v>
+        <v>80276</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>510</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>648873</v>
+        <v>649384</v>
       </c>
       <c r="R66" t="n">
-        <v>6995569</v>
+        <v>6995514</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7137,32 +7137,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130350842</v>
+        <v>130350881</v>
       </c>
       <c r="B67" t="n">
-        <v>91761</v>
+        <v>97828</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649096</v>
+        <v>649111</v>
       </c>
       <c r="R67" t="n">
-        <v>6995501</v>
+        <v>6995725</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7339,7 +7339,7 @@
         <v>130350884</v>
       </c>
       <c r="B69" t="n">
-        <v>96179</v>
+        <v>96183</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350873</v>
+        <v>130350908</v>
       </c>
       <c r="B4" t="n">
-        <v>57044</v>
+        <v>89155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649139</v>
+        <v>649250</v>
       </c>
       <c r="R4" t="n">
-        <v>6995673</v>
+        <v>6995605</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350908</v>
+        <v>130350902</v>
       </c>
       <c r="B5" t="n">
-        <v>89155</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649250</v>
+        <v>648702</v>
       </c>
       <c r="R5" t="n">
-        <v>6995605</v>
+        <v>6995939</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130350902</v>
+        <v>130350873</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>648702</v>
+        <v>649139</v>
       </c>
       <c r="R6" t="n">
-        <v>6995939</v>
+        <v>6995673</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1157,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350903</v>
+        <v>130350844</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>91761</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>648792</v>
+        <v>649036</v>
       </c>
       <c r="R14" t="n">
-        <v>6995927</v>
+        <v>6995660</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130350844</v>
+        <v>130350903</v>
       </c>
       <c r="B15" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>649036</v>
+        <v>648792</v>
       </c>
       <c r="R15" t="n">
-        <v>6995660</v>
+        <v>6995927</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130350899</v>
+        <v>130350861</v>
       </c>
       <c r="B16" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,19 +2102,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2122,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648996</v>
+        <v>648707</v>
       </c>
       <c r="R16" t="n">
-        <v>6995647</v>
+        <v>6995954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,6 +2162,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2184,10 +2193,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130350861</v>
+        <v>130351125</v>
       </c>
       <c r="B17" t="n">
-        <v>57854</v>
+        <v>92180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,21 +2204,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2228,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648707</v>
+        <v>648877</v>
       </c>
       <c r="R17" t="n">
-        <v>6995954</v>
+        <v>6995565</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,11 +2264,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2286,10 +2290,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130351125</v>
+        <v>130350899</v>
       </c>
       <c r="B18" t="n">
-        <v>92180</v>
+        <v>91781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,23 +2301,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040186</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648877</v>
+        <v>648996</v>
       </c>
       <c r="R18" t="n">
-        <v>6995565</v>
+        <v>6995647</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130350868</v>
+        <v>130350838</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>91725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649093</v>
+        <v>649074</v>
       </c>
       <c r="R19" t="n">
-        <v>6995638</v>
+        <v>6995652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,11 +2454,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2485,7 +2480,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130350863</v>
+        <v>130350868</v>
       </c>
       <c r="B20" t="n">
         <v>57854</v>
@@ -2520,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649031</v>
+        <v>649093</v>
       </c>
       <c r="R20" t="n">
-        <v>6995803</v>
+        <v>6995638</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2587,7 +2582,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130350847</v>
+        <v>130350863</v>
       </c>
       <c r="B21" t="n">
         <v>57854</v>
@@ -2622,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>649222</v>
+        <v>649031</v>
       </c>
       <c r="R21" t="n">
-        <v>6995657</v>
+        <v>6995803</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2662,7 +2657,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2689,32 +2684,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130350838</v>
+        <v>130350847</v>
       </c>
       <c r="B22" t="n">
-        <v>91725</v>
+        <v>57854</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2724,10 +2719,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>649074</v>
+        <v>649222</v>
       </c>
       <c r="R22" t="n">
-        <v>6995652</v>
+        <v>6995657</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2760,6 +2755,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2883,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350900</v>
+        <v>130350877</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>92220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>649027</v>
+        <v>648991</v>
       </c>
       <c r="R24" t="n">
-        <v>6995592</v>
+        <v>6995659</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350905</v>
+        <v>130350878</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>92220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>649120</v>
+        <v>649038</v>
       </c>
       <c r="R25" t="n">
-        <v>6995740</v>
+        <v>6995626</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130350878</v>
+        <v>130350900</v>
       </c>
       <c r="B26" t="n">
-        <v>92220</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>649038</v>
+        <v>649027</v>
       </c>
       <c r="R26" t="n">
-        <v>6995626</v>
+        <v>6995592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,32 +3174,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130350877</v>
+        <v>130350905</v>
       </c>
       <c r="B27" t="n">
-        <v>92220</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>648991</v>
+        <v>649120</v>
       </c>
       <c r="R27" t="n">
-        <v>6995659</v>
+        <v>6995740</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130350898</v>
+        <v>130350858</v>
       </c>
       <c r="B31" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3583,19 +3583,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3603,10 +3607,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>648849</v>
+        <v>648826</v>
       </c>
       <c r="R31" t="n">
-        <v>6995437</v>
+        <v>6995403</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3639,6 +3643,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3665,32 +3674,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350858</v>
+        <v>130350891</v>
       </c>
       <c r="B32" t="n">
-        <v>57854</v>
+        <v>80276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3700,10 +3709,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>648826</v>
+        <v>649044</v>
       </c>
       <c r="R32" t="n">
-        <v>6995403</v>
+        <v>6995628</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,11 +3745,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3767,34 +3771,30 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130350891</v>
+        <v>130350898</v>
       </c>
       <c r="B33" t="n">
-        <v>80276</v>
+        <v>91781</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>649044</v>
+        <v>648849</v>
       </c>
       <c r="R33" t="n">
-        <v>6995628</v>
+        <v>6995437</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130350869</v>
+        <v>130350855</v>
       </c>
       <c r="B35" t="n">
         <v>57854</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>649090</v>
+        <v>648855</v>
       </c>
       <c r="R35" t="n">
-        <v>6995641</v>
+        <v>6995417</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4068,7 +4068,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130350855</v>
+        <v>130350869</v>
       </c>
       <c r="B36" t="n">
         <v>57854</v>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>648855</v>
+        <v>649090</v>
       </c>
       <c r="R36" t="n">
-        <v>6995417</v>
+        <v>6995641</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4170,10 +4170,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130350872</v>
+        <v>130350911</v>
       </c>
       <c r="B37" t="n">
-        <v>57854</v>
+        <v>89155</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4181,21 +4181,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>649146</v>
+        <v>648698</v>
       </c>
       <c r="R37" t="n">
-        <v>6995662</v>
+        <v>6995926</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4241,11 +4241,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4272,10 +4267,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130350911</v>
+        <v>130350872</v>
       </c>
       <c r="B38" t="n">
-        <v>89155</v>
+        <v>57854</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4283,21 +4278,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4307,10 +4302,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>648698</v>
+        <v>649146</v>
       </c>
       <c r="R38" t="n">
-        <v>6995926</v>
+        <v>6995662</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4343,6 +4338,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350892</v>
+        <v>130350837</v>
       </c>
       <c r="B43" t="n">
-        <v>57035</v>
+        <v>91948</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>1588</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>649126</v>
+        <v>649254</v>
       </c>
       <c r="R43" t="n">
-        <v>6995764</v>
+        <v>6995609</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4829,11 +4829,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4860,7 +4855,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350859</v>
+        <v>130350856</v>
       </c>
       <c r="B44" t="n">
         <v>57854</v>
@@ -4895,10 +4890,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648771</v>
+        <v>648835</v>
       </c>
       <c r="R44" t="n">
-        <v>6995688</v>
+        <v>6995397</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4935,7 +4930,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4962,7 +4957,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350856</v>
+        <v>130350854</v>
       </c>
       <c r="B45" t="n">
         <v>57854</v>
@@ -4997,10 +4992,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648835</v>
+        <v>648853</v>
       </c>
       <c r="R45" t="n">
-        <v>6995397</v>
+        <v>6995420</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5064,10 +5059,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350854</v>
+        <v>130350892</v>
       </c>
       <c r="B46" t="n">
-        <v>57854</v>
+        <v>57035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5075,16 +5070,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5099,10 +5094,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648853</v>
+        <v>649126</v>
       </c>
       <c r="R46" t="n">
-        <v>6995420</v>
+        <v>6995764</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5139,7 +5134,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5356,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350837</v>
+        <v>130350859</v>
       </c>
       <c r="B49" t="n">
-        <v>91948</v>
+        <v>57854</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,21 +5362,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5391,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>649254</v>
+        <v>648771</v>
       </c>
       <c r="R49" t="n">
-        <v>6995609</v>
+        <v>6995688</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5427,6 +5422,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5453,32 +5453,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130350883</v>
+        <v>130350839</v>
       </c>
       <c r="B50" t="n">
-        <v>80344</v>
+        <v>91761</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>649094</v>
+        <v>649369</v>
       </c>
       <c r="R50" t="n">
-        <v>6995519</v>
+        <v>6995531</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130350839</v>
+        <v>130350909</v>
       </c>
       <c r="B51" t="n">
-        <v>91761</v>
+        <v>89155</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>649369</v>
+        <v>648957</v>
       </c>
       <c r="R51" t="n">
-        <v>6995531</v>
+        <v>6995579</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,32 +5647,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350909</v>
+        <v>130350883</v>
       </c>
       <c r="B52" t="n">
-        <v>89155</v>
+        <v>80344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>510</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>648957</v>
+        <v>649094</v>
       </c>
       <c r="R52" t="n">
-        <v>6995579</v>
+        <v>6995519</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5744,32 +5744,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350864</v>
+        <v>130350890</v>
       </c>
       <c r="B53" t="n">
-        <v>57854</v>
+        <v>80276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>648993</v>
+        <v>649374</v>
       </c>
       <c r="R53" t="n">
-        <v>6995756</v>
+        <v>6995542</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5815,11 +5815,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5846,7 +5841,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350867</v>
+        <v>130350864</v>
       </c>
       <c r="B54" t="n">
         <v>57854</v>
@@ -5881,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>649095</v>
+        <v>648993</v>
       </c>
       <c r="R54" t="n">
-        <v>6995637</v>
+        <v>6995756</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5921,7 +5916,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5948,32 +5943,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130350890</v>
+        <v>130350867</v>
       </c>
       <c r="B55" t="n">
-        <v>80276</v>
+        <v>57854</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5983,10 +5978,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>649374</v>
+        <v>649095</v>
       </c>
       <c r="R55" t="n">
-        <v>6995542</v>
+        <v>6995637</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6019,6 +6014,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6336,7 +6336,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350874</v>
+        <v>130350876</v>
       </c>
       <c r="B59" t="n">
         <v>57851</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>648811</v>
+        <v>649127</v>
       </c>
       <c r="R59" t="n">
-        <v>6995477</v>
+        <v>6995704</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6438,7 +6438,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350876</v>
+        <v>130350874</v>
       </c>
       <c r="B60" t="n">
         <v>57851</v>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>649127</v>
+        <v>648811</v>
       </c>
       <c r="R60" t="n">
-        <v>6995704</v>
+        <v>6995477</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6540,10 +6540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130350910</v>
+        <v>130350875</v>
       </c>
       <c r="B61" t="n">
-        <v>89155</v>
+        <v>57851</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>648873</v>
+        <v>648755</v>
       </c>
       <c r="R61" t="n">
-        <v>6995569</v>
+        <v>6995792</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6611,6 +6611,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6637,10 +6642,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130350842</v>
+        <v>130350893</v>
       </c>
       <c r="B62" t="n">
-        <v>91761</v>
+        <v>57035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6648,21 +6653,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>649096</v>
+        <v>649144</v>
       </c>
       <c r="R62" t="n">
-        <v>6995501</v>
+        <v>6995799</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6708,6 +6713,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6734,32 +6744,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350875</v>
+        <v>130350889</v>
       </c>
       <c r="B63" t="n">
-        <v>57851</v>
+        <v>80276</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6779,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>648755</v>
+        <v>649384</v>
       </c>
       <c r="R63" t="n">
-        <v>6995792</v>
+        <v>6995514</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6805,11 +6815,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6836,10 +6841,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350893</v>
+        <v>130350910</v>
       </c>
       <c r="B64" t="n">
-        <v>57035</v>
+        <v>89155</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6847,21 +6852,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>510</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6871,10 +6876,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>649144</v>
+        <v>648873</v>
       </c>
       <c r="R64" t="n">
-        <v>6995799</v>
+        <v>6995569</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6907,11 +6912,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6938,10 +6938,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350862</v>
+        <v>130350842</v>
       </c>
       <c r="B65" t="n">
-        <v>57854</v>
+        <v>91761</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6949,21 +6949,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>648830</v>
+        <v>649096</v>
       </c>
       <c r="R65" t="n">
-        <v>6995874</v>
+        <v>6995501</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7009,11 +7009,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7040,32 +7035,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130350889</v>
+        <v>130350862</v>
       </c>
       <c r="B66" t="n">
-        <v>80276</v>
+        <v>57854</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7075,10 +7070,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>649384</v>
+        <v>648830</v>
       </c>
       <c r="R66" t="n">
-        <v>6995514</v>
+        <v>6995874</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7111,6 +7106,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -989,32 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350902</v>
+        <v>130350873</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648702</v>
+        <v>649139</v>
       </c>
       <c r="R5" t="n">
-        <v>6995939</v>
+        <v>6995673</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1060,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,32 +1091,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130350873</v>
+        <v>130350902</v>
       </c>
       <c r="B6" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649139</v>
+        <v>648702</v>
       </c>
       <c r="R6" t="n">
-        <v>6995673</v>
+        <v>6995939</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,11 +1162,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1387,7 +1387,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130350866</v>
+        <v>130350860</v>
       </c>
       <c r="B9" t="n">
         <v>57854</v>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649049</v>
+        <v>648687</v>
       </c>
       <c r="R9" t="n">
-        <v>6995652</v>
+        <v>6995932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,7 +1591,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130350860</v>
+        <v>130350866</v>
       </c>
       <c r="B11" t="n">
         <v>57854</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>648687</v>
+        <v>649049</v>
       </c>
       <c r="R11" t="n">
-        <v>6995932</v>
+        <v>6995652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,7 +1693,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130350853</v>
+        <v>130350857</v>
       </c>
       <c r="B12" t="n">
         <v>57854</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648941</v>
+        <v>648826</v>
       </c>
       <c r="R12" t="n">
-        <v>6995608</v>
+        <v>6995407</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,7 +1795,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130350857</v>
+        <v>130350853</v>
       </c>
       <c r="B13" t="n">
         <v>57854</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648826</v>
+        <v>648941</v>
       </c>
       <c r="R13" t="n">
-        <v>6995407</v>
+        <v>6995608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350844</v>
+        <v>130350899</v>
       </c>
       <c r="B14" t="n">
-        <v>91761</v>
+        <v>91781</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,23 +1908,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1932,10 +1928,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649036</v>
+        <v>648996</v>
       </c>
       <c r="R14" t="n">
-        <v>6995660</v>
+        <v>6995647</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1990,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130350903</v>
+        <v>130350861</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2001,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2025,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648792</v>
+        <v>648707</v>
       </c>
       <c r="R15" t="n">
-        <v>6995927</v>
+        <v>6995954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,6 +2061,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2091,10 +2092,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130350861</v>
+        <v>130350844</v>
       </c>
       <c r="B16" t="n">
-        <v>57854</v>
+        <v>91761</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2103,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648707</v>
+        <v>649036</v>
       </c>
       <c r="R16" t="n">
-        <v>6995954</v>
+        <v>6995660</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,11 +2163,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130351125</v>
+        <v>130350903</v>
       </c>
       <c r="B17" t="n">
-        <v>92180</v>
+        <v>79211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2204,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6040186</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2228,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648877</v>
+        <v>648792</v>
       </c>
       <c r="R17" t="n">
-        <v>6995565</v>
+        <v>6995927</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,10 +2286,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130350899</v>
+        <v>130351125</v>
       </c>
       <c r="B18" t="n">
-        <v>91781</v>
+        <v>92180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2301,19 +2297,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6040186</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648996</v>
+        <v>648877</v>
       </c>
       <c r="R18" t="n">
-        <v>6995647</v>
+        <v>6995565</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130350838</v>
+        <v>130351124</v>
       </c>
       <c r="B19" t="n">
-        <v>91725</v>
+        <v>92180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6040186</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649074</v>
+        <v>649116</v>
       </c>
       <c r="R19" t="n">
-        <v>6995652</v>
+        <v>6995496</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,32 +2480,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130350868</v>
+        <v>130350838</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>91725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649093</v>
+        <v>649074</v>
       </c>
       <c r="R20" t="n">
-        <v>6995638</v>
+        <v>6995652</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,11 +2551,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,10 +2781,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130351124</v>
+        <v>130350868</v>
       </c>
       <c r="B23" t="n">
-        <v>92180</v>
+        <v>57854</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2797,21 +2792,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2821,10 +2816,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649116</v>
+        <v>649093</v>
       </c>
       <c r="R23" t="n">
-        <v>6995496</v>
+        <v>6995638</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2857,6 +2852,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2883,7 +2883,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350877</v>
+        <v>130350878</v>
       </c>
       <c r="B24" t="n">
         <v>92220</v>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>648991</v>
+        <v>649038</v>
       </c>
       <c r="R24" t="n">
-        <v>6995659</v>
+        <v>6995626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350878</v>
+        <v>130350877</v>
       </c>
       <c r="B25" t="n">
         <v>92220</v>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>649038</v>
+        <v>648991</v>
       </c>
       <c r="R25" t="n">
-        <v>6995626</v>
+        <v>6995659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350846</v>
+        <v>130350858</v>
       </c>
       <c r="B30" t="n">
-        <v>91761</v>
+        <v>57854</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3486,21 +3486,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>649063</v>
+        <v>648826</v>
       </c>
       <c r="R30" t="n">
-        <v>6995635</v>
+        <v>6995403</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3546,6 +3546,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3572,32 +3577,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130350858</v>
+        <v>130350891</v>
       </c>
       <c r="B31" t="n">
-        <v>57854</v>
+        <v>80276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3607,10 +3612,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>648826</v>
+        <v>649044</v>
       </c>
       <c r="R31" t="n">
-        <v>6995403</v>
+        <v>6995628</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3643,11 +3648,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3674,32 +3674,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350891</v>
+        <v>130350846</v>
       </c>
       <c r="B32" t="n">
-        <v>80276</v>
+        <v>91761</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>649044</v>
+        <v>649063</v>
       </c>
       <c r="R32" t="n">
-        <v>6995628</v>
+        <v>6995635</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130350852</v>
+        <v>130350855</v>
       </c>
       <c r="B34" t="n">
         <v>57854</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>649032</v>
+        <v>648855</v>
       </c>
       <c r="R34" t="n">
-        <v>6995530</v>
+        <v>6995417</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3966,7 +3966,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130350855</v>
+        <v>130350852</v>
       </c>
       <c r="B35" t="n">
         <v>57854</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>648855</v>
+        <v>649032</v>
       </c>
       <c r="R35" t="n">
-        <v>6995417</v>
+        <v>6995530</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4855,10 +4855,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350856</v>
+        <v>130350896</v>
       </c>
       <c r="B44" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,23 +4866,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4890,10 +4886,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648835</v>
+        <v>648854</v>
       </c>
       <c r="R44" t="n">
-        <v>6995397</v>
+        <v>6995532</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,11 +4922,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4957,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350854</v>
+        <v>130350886</v>
       </c>
       <c r="B45" t="n">
-        <v>57854</v>
+        <v>80316</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,21 +4959,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4992,10 +4983,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648853</v>
+        <v>648997</v>
       </c>
       <c r="R45" t="n">
-        <v>6995420</v>
+        <v>6995649</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5028,11 +5019,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5059,10 +5045,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350892</v>
+        <v>130350859</v>
       </c>
       <c r="B46" t="n">
-        <v>57035</v>
+        <v>57854</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5070,16 +5056,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5094,10 +5080,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>649126</v>
+        <v>648771</v>
       </c>
       <c r="R46" t="n">
-        <v>6995764</v>
+        <v>6995688</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5134,7 +5120,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5161,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350886</v>
+        <v>130350856</v>
       </c>
       <c r="B47" t="n">
-        <v>80316</v>
+        <v>57854</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5172,21 +5158,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5196,10 +5182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648997</v>
+        <v>648835</v>
       </c>
       <c r="R47" t="n">
-        <v>6995649</v>
+        <v>6995397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5232,6 +5218,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5258,10 +5249,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350896</v>
+        <v>130350854</v>
       </c>
       <c r="B48" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5269,19 +5260,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5289,10 +5284,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648854</v>
+        <v>648853</v>
       </c>
       <c r="R48" t="n">
-        <v>6995532</v>
+        <v>6995420</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,6 +5320,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5351,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350859</v>
+        <v>130350892</v>
       </c>
       <c r="B49" t="n">
-        <v>57854</v>
+        <v>57035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>648771</v>
+        <v>649126</v>
       </c>
       <c r="R49" t="n">
-        <v>6995688</v>
+        <v>6995764</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5744,32 +5744,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350890</v>
+        <v>130350841</v>
       </c>
       <c r="B53" t="n">
-        <v>80276</v>
+        <v>91761</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649374</v>
+        <v>649195</v>
       </c>
       <c r="R53" t="n">
-        <v>6995542</v>
+        <v>6995694</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350864</v>
+        <v>130350879</v>
       </c>
       <c r="B54" t="n">
-        <v>57854</v>
+        <v>92059</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>648993</v>
+        <v>649062</v>
       </c>
       <c r="R54" t="n">
-        <v>6995756</v>
+        <v>6995641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5912,11 +5912,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6045,10 +6040,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130350841</v>
+        <v>130350864</v>
       </c>
       <c r="B56" t="n">
-        <v>91761</v>
+        <v>57854</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6056,21 +6051,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6080,10 +6075,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>649195</v>
+        <v>648993</v>
       </c>
       <c r="R56" t="n">
-        <v>6995694</v>
+        <v>6995756</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6116,6 +6111,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6142,32 +6142,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130350879</v>
+        <v>130350890</v>
       </c>
       <c r="B57" t="n">
-        <v>92059</v>
+        <v>80276</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>649062</v>
+        <v>649374</v>
       </c>
       <c r="R57" t="n">
-        <v>6995641</v>
+        <v>6995542</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6336,7 +6336,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350876</v>
+        <v>130350874</v>
       </c>
       <c r="B59" t="n">
         <v>57851</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>649127</v>
+        <v>648811</v>
       </c>
       <c r="R59" t="n">
-        <v>6995704</v>
+        <v>6995477</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6438,7 +6438,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350874</v>
+        <v>130350876</v>
       </c>
       <c r="B60" t="n">
         <v>57851</v>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>648811</v>
+        <v>649127</v>
       </c>
       <c r="R60" t="n">
-        <v>6995477</v>
+        <v>6995704</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6540,10 +6540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130350875</v>
+        <v>130350893</v>
       </c>
       <c r="B61" t="n">
-        <v>57851</v>
+        <v>57035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6551,16 +6551,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>648755</v>
+        <v>649144</v>
       </c>
       <c r="R61" t="n">
-        <v>6995792</v>
+        <v>6995799</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6642,32 +6642,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130350893</v>
+        <v>130350881</v>
       </c>
       <c r="B62" t="n">
-        <v>57035</v>
+        <v>97828</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>649144</v>
+        <v>649111</v>
       </c>
       <c r="R62" t="n">
-        <v>6995799</v>
+        <v>6995725</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6713,11 +6713,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6744,32 +6739,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350889</v>
+        <v>130350910</v>
       </c>
       <c r="B63" t="n">
-        <v>80276</v>
+        <v>89155</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>510</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6779,10 +6774,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649384</v>
+        <v>648873</v>
       </c>
       <c r="R63" t="n">
-        <v>6995514</v>
+        <v>6995569</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6841,10 +6836,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350910</v>
+        <v>130350842</v>
       </c>
       <c r="B64" t="n">
-        <v>89155</v>
+        <v>91761</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6852,21 +6847,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6876,10 +6871,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>648873</v>
+        <v>649096</v>
       </c>
       <c r="R64" t="n">
-        <v>6995569</v>
+        <v>6995501</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6938,10 +6933,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350842</v>
+        <v>130350875</v>
       </c>
       <c r="B65" t="n">
-        <v>91761</v>
+        <v>57851</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6949,21 +6944,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6973,10 +6968,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>649096</v>
+        <v>648755</v>
       </c>
       <c r="R65" t="n">
-        <v>6995501</v>
+        <v>6995792</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7009,6 +7004,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7137,10 +7137,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130350881</v>
+        <v>130350889</v>
       </c>
       <c r="B67" t="n">
-        <v>97828</v>
+        <v>80276</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7148,21 +7148,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649111</v>
+        <v>649384</v>
       </c>
       <c r="R67" t="n">
-        <v>6995725</v>
+        <v>6995514</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130350904</v>
+        <v>130350866</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649056</v>
+        <v>649049</v>
       </c>
       <c r="R8" t="n">
-        <v>6995686</v>
+        <v>6995652</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,6 +1361,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,7 +1392,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130350860</v>
+        <v>130350870</v>
       </c>
       <c r="B9" t="n">
         <v>57854</v>
@@ -1422,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>648687</v>
+        <v>649039</v>
       </c>
       <c r="R9" t="n">
-        <v>6995932</v>
+        <v>6995705</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1494,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130350870</v>
+        <v>130350860</v>
       </c>
       <c r="B10" t="n">
         <v>57854</v>
@@ -1524,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649039</v>
+        <v>648687</v>
       </c>
       <c r="R10" t="n">
-        <v>6995705</v>
+        <v>6995932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130350866</v>
+        <v>130350904</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,21 +1607,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1626,10 +1631,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649049</v>
+        <v>649056</v>
       </c>
       <c r="R11" t="n">
-        <v>6995652</v>
+        <v>6995686</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,11 +1667,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,7 +1693,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130350857</v>
+        <v>130350853</v>
       </c>
       <c r="B12" t="n">
         <v>57854</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648826</v>
+        <v>648941</v>
       </c>
       <c r="R12" t="n">
-        <v>6995407</v>
+        <v>6995608</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,7 +1795,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130350853</v>
+        <v>130350857</v>
       </c>
       <c r="B13" t="n">
         <v>57854</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648941</v>
+        <v>648826</v>
       </c>
       <c r="R13" t="n">
-        <v>6995608</v>
+        <v>6995407</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350899</v>
+        <v>130350844</v>
       </c>
       <c r="B14" t="n">
-        <v>91781</v>
+        <v>91761</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,19 +1908,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1928,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>648996</v>
+        <v>649036</v>
       </c>
       <c r="R14" t="n">
-        <v>6995647</v>
+        <v>6995660</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130350861</v>
+        <v>130350903</v>
       </c>
       <c r="B15" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2001,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2025,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648707</v>
+        <v>648792</v>
       </c>
       <c r="R15" t="n">
-        <v>6995954</v>
+        <v>6995927</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,11 +2065,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2092,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130350844</v>
+        <v>130351125</v>
       </c>
       <c r="B16" t="n">
-        <v>91761</v>
+        <v>92180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6040186</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2127,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>649036</v>
+        <v>648877</v>
       </c>
       <c r="R16" t="n">
-        <v>6995660</v>
+        <v>6995565</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,10 +2188,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130350903</v>
+        <v>130350899</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>91781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,23 +2199,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2224,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648792</v>
+        <v>648996</v>
       </c>
       <c r="R17" t="n">
-        <v>6995927</v>
+        <v>6995647</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130351125</v>
+        <v>130350861</v>
       </c>
       <c r="B18" t="n">
-        <v>92180</v>
+        <v>57854</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,21 +2292,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2316,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648877</v>
+        <v>648707</v>
       </c>
       <c r="R18" t="n">
-        <v>6995565</v>
+        <v>6995954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,6 +2352,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2383,10 +2383,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130351124</v>
+        <v>130350868</v>
       </c>
       <c r="B19" t="n">
-        <v>92180</v>
+        <v>57854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2394,21 +2394,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649116</v>
+        <v>649093</v>
       </c>
       <c r="R19" t="n">
-        <v>6995496</v>
+        <v>6995638</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,6 +2454,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2480,32 +2485,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130350838</v>
+        <v>130350863</v>
       </c>
       <c r="B20" t="n">
-        <v>91725</v>
+        <v>57854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2520,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649074</v>
+        <v>649031</v>
       </c>
       <c r="R20" t="n">
-        <v>6995652</v>
+        <v>6995803</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,6 +2556,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2577,7 +2587,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130350863</v>
+        <v>130350847</v>
       </c>
       <c r="B21" t="n">
         <v>57854</v>
@@ -2612,10 +2622,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>649031</v>
+        <v>649222</v>
       </c>
       <c r="R21" t="n">
-        <v>6995803</v>
+        <v>6995657</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2652,7 +2662,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2679,10 +2689,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130350847</v>
+        <v>130351124</v>
       </c>
       <c r="B22" t="n">
-        <v>57854</v>
+        <v>92180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2690,21 +2700,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2714,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>649222</v>
+        <v>649116</v>
       </c>
       <c r="R22" t="n">
-        <v>6995657</v>
+        <v>6995496</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2750,11 +2760,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2781,32 +2786,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130350868</v>
+        <v>130350838</v>
       </c>
       <c r="B23" t="n">
-        <v>57854</v>
+        <v>91725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2816,10 +2821,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649093</v>
+        <v>649074</v>
       </c>
       <c r="R23" t="n">
-        <v>6995638</v>
+        <v>6995652</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,11 +2857,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2883,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350878</v>
+        <v>130350900</v>
       </c>
       <c r="B24" t="n">
-        <v>92220</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>649038</v>
+        <v>649027</v>
       </c>
       <c r="R24" t="n">
-        <v>6995626</v>
+        <v>6995592</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350877</v>
+        <v>130350905</v>
       </c>
       <c r="B25" t="n">
-        <v>92220</v>
+        <v>79211</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>648991</v>
+        <v>649120</v>
       </c>
       <c r="R25" t="n">
-        <v>6995659</v>
+        <v>6995740</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130350900</v>
+        <v>130350878</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>92220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>649027</v>
+        <v>649038</v>
       </c>
       <c r="R26" t="n">
-        <v>6995592</v>
+        <v>6995626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,32 +3174,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130350905</v>
+        <v>130350877</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>92220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>649120</v>
+        <v>648991</v>
       </c>
       <c r="R27" t="n">
-        <v>6995740</v>
+        <v>6995659</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350858</v>
+        <v>130350898</v>
       </c>
       <c r="B30" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3486,23 +3486,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3510,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>648826</v>
+        <v>648849</v>
       </c>
       <c r="R30" t="n">
-        <v>6995403</v>
+        <v>6995437</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3546,11 +3542,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3577,32 +3568,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130350891</v>
+        <v>130350846</v>
       </c>
       <c r="B31" t="n">
-        <v>80276</v>
+        <v>91761</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3612,10 +3603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>649044</v>
+        <v>649063</v>
       </c>
       <c r="R31" t="n">
-        <v>6995628</v>
+        <v>6995635</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3674,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350846</v>
+        <v>130350858</v>
       </c>
       <c r="B32" t="n">
-        <v>91761</v>
+        <v>57854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,21 +3676,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3709,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>649063</v>
+        <v>648826</v>
       </c>
       <c r="R32" t="n">
-        <v>6995635</v>
+        <v>6995403</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3745,6 +3736,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3771,30 +3767,34 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130350898</v>
+        <v>130350891</v>
       </c>
       <c r="B33" t="n">
-        <v>91781</v>
+        <v>80276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>648849</v>
+        <v>649044</v>
       </c>
       <c r="R33" t="n">
-        <v>6995437</v>
+        <v>6995628</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130350855</v>
+        <v>130350852</v>
       </c>
       <c r="B34" t="n">
         <v>57854</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>648855</v>
+        <v>649032</v>
       </c>
       <c r="R34" t="n">
-        <v>6995417</v>
+        <v>6995530</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3966,7 +3966,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130350852</v>
+        <v>130350869</v>
       </c>
       <c r="B35" t="n">
         <v>57854</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>649032</v>
+        <v>649090</v>
       </c>
       <c r="R35" t="n">
-        <v>6995530</v>
+        <v>6995641</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130350869</v>
+        <v>130350855</v>
       </c>
       <c r="B36" t="n">
         <v>57854</v>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>649090</v>
+        <v>648855</v>
       </c>
       <c r="R36" t="n">
-        <v>6995641</v>
+        <v>6995417</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350837</v>
+        <v>130350892</v>
       </c>
       <c r="B43" t="n">
-        <v>91948</v>
+        <v>57035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1588</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>649254</v>
+        <v>649126</v>
       </c>
       <c r="R43" t="n">
-        <v>6995609</v>
+        <v>6995764</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4829,6 +4829,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4855,10 +4860,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350896</v>
+        <v>130350886</v>
       </c>
       <c r="B44" t="n">
-        <v>91781</v>
+        <v>80316</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,19 +4871,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4886,10 +4895,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648854</v>
+        <v>648997</v>
       </c>
       <c r="R44" t="n">
-        <v>6995532</v>
+        <v>6995649</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4948,10 +4957,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350886</v>
+        <v>130350837</v>
       </c>
       <c r="B45" t="n">
-        <v>80316</v>
+        <v>91948</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4959,21 +4968,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4983,10 +4992,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648997</v>
+        <v>649254</v>
       </c>
       <c r="R45" t="n">
-        <v>6995649</v>
+        <v>6995609</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5045,10 +5054,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350859</v>
+        <v>130350896</v>
       </c>
       <c r="B46" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5056,23 +5065,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5080,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648771</v>
+        <v>648854</v>
       </c>
       <c r="R46" t="n">
-        <v>6995688</v>
+        <v>6995532</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5116,11 +5121,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5147,7 +5147,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350856</v>
+        <v>130350859</v>
       </c>
       <c r="B47" t="n">
         <v>57854</v>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648835</v>
+        <v>648771</v>
       </c>
       <c r="R47" t="n">
-        <v>6995397</v>
+        <v>6995688</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5249,7 +5249,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350854</v>
+        <v>130350856</v>
       </c>
       <c r="B48" t="n">
         <v>57854</v>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648853</v>
+        <v>648835</v>
       </c>
       <c r="R48" t="n">
-        <v>6995420</v>
+        <v>6995397</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350892</v>
+        <v>130350854</v>
       </c>
       <c r="B49" t="n">
-        <v>57035</v>
+        <v>57854</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>649126</v>
+        <v>648853</v>
       </c>
       <c r="R49" t="n">
-        <v>6995764</v>
+        <v>6995420</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5744,32 +5744,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350841</v>
+        <v>130350890</v>
       </c>
       <c r="B53" t="n">
-        <v>91761</v>
+        <v>80276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649195</v>
+        <v>649374</v>
       </c>
       <c r="R53" t="n">
-        <v>6995694</v>
+        <v>6995542</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350879</v>
+        <v>130350841</v>
       </c>
       <c r="B54" t="n">
-        <v>92059</v>
+        <v>91761</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>649062</v>
+        <v>649195</v>
       </c>
       <c r="R54" t="n">
-        <v>6995641</v>
+        <v>6995694</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130350867</v>
+        <v>130350879</v>
       </c>
       <c r="B55" t="n">
-        <v>57854</v>
+        <v>92059</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>649095</v>
+        <v>649062</v>
       </c>
       <c r="R55" t="n">
-        <v>6995637</v>
+        <v>6995641</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6009,11 +6009,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6142,32 +6137,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130350890</v>
+        <v>130350867</v>
       </c>
       <c r="B57" t="n">
-        <v>80276</v>
+        <v>57854</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6177,10 +6172,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>649374</v>
+        <v>649095</v>
       </c>
       <c r="R57" t="n">
-        <v>6995542</v>
+        <v>6995637</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6213,6 +6208,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6540,10 +6540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130350893</v>
+        <v>130350910</v>
       </c>
       <c r="B61" t="n">
-        <v>57035</v>
+        <v>89155</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102612</v>
+        <v>510</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>649144</v>
+        <v>648873</v>
       </c>
       <c r="R61" t="n">
-        <v>6995799</v>
+        <v>6995569</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6611,11 +6611,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6642,32 +6637,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130350881</v>
+        <v>130350842</v>
       </c>
       <c r="B62" t="n">
-        <v>97828</v>
+        <v>91761</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6677,10 +6672,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>649111</v>
+        <v>649096</v>
       </c>
       <c r="R62" t="n">
-        <v>6995725</v>
+        <v>6995501</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6739,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350910</v>
+        <v>130350893</v>
       </c>
       <c r="B63" t="n">
-        <v>89155</v>
+        <v>57035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6750,21 +6745,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>510</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6774,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>648873</v>
+        <v>649144</v>
       </c>
       <c r="R63" t="n">
-        <v>6995569</v>
+        <v>6995799</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6810,6 +6805,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6836,10 +6836,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350842</v>
+        <v>130350862</v>
       </c>
       <c r="B64" t="n">
-        <v>91761</v>
+        <v>57854</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6847,21 +6847,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>649096</v>
+        <v>648830</v>
       </c>
       <c r="R64" t="n">
-        <v>6995501</v>
+        <v>6995874</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6907,6 +6907,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7035,32 +7040,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130350862</v>
+        <v>130350881</v>
       </c>
       <c r="B66" t="n">
-        <v>57854</v>
+        <v>97828</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7070,10 +7075,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>648830</v>
+        <v>649111</v>
       </c>
       <c r="R66" t="n">
-        <v>6995874</v>
+        <v>6995725</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7106,11 +7111,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130350885</v>
       </c>
       <c r="B3" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350908</v>
+        <v>130350902</v>
       </c>
       <c r="B4" t="n">
-        <v>89155</v>
+        <v>79219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649250</v>
+        <v>648702</v>
       </c>
       <c r="R4" t="n">
-        <v>6995605</v>
+        <v>6995939</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,32 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350873</v>
+        <v>130350908</v>
       </c>
       <c r="B5" t="n">
-        <v>57044</v>
+        <v>89167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649139</v>
+        <v>649250</v>
       </c>
       <c r="R5" t="n">
-        <v>6995673</v>
+        <v>6995605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,11 +1060,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130350902</v>
+        <v>130350873</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>57052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>648702</v>
+        <v>649139</v>
       </c>
       <c r="R6" t="n">
-        <v>6995939</v>
+        <v>6995673</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1157,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,7 +1191,7 @@
         <v>130350865</v>
       </c>
       <c r="B7" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>130350866</v>
       </c>
       <c r="B8" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>130350870</v>
       </c>
       <c r="B9" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>130350860</v>
       </c>
       <c r="B10" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>130350904</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>130350853</v>
       </c>
       <c r="B12" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130350857</v>
       </c>
       <c r="B13" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350844</v>
+        <v>130350903</v>
       </c>
       <c r="B14" t="n">
-        <v>91761</v>
+        <v>79219</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649036</v>
+        <v>648792</v>
       </c>
       <c r="R14" t="n">
-        <v>6995660</v>
+        <v>6995927</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130350903</v>
+        <v>130351125</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>92193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648792</v>
+        <v>648877</v>
       </c>
       <c r="R15" t="n">
-        <v>6995927</v>
+        <v>6995565</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130351125</v>
+        <v>130350861</v>
       </c>
       <c r="B16" t="n">
-        <v>92180</v>
+        <v>57862</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648877</v>
+        <v>648707</v>
       </c>
       <c r="R16" t="n">
-        <v>6995565</v>
+        <v>6995954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,6 +2162,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2191,7 +2196,7 @@
         <v>130350899</v>
       </c>
       <c r="B17" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2281,10 +2286,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130350861</v>
+        <v>130350844</v>
       </c>
       <c r="B18" t="n">
-        <v>57854</v>
+        <v>91774</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2292,21 +2297,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2316,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648707</v>
+        <v>649036</v>
       </c>
       <c r="R18" t="n">
-        <v>6995954</v>
+        <v>6995660</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,11 +2357,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2386,7 +2386,7 @@
         <v>130350868</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>130350863</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>130350847</v>
       </c>
       <c r="B21" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>130351124</v>
       </c>
       <c r="B22" t="n">
-        <v>92180</v>
+        <v>92193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>130350838</v>
       </c>
       <c r="B23" t="n">
-        <v>91725</v>
+        <v>91737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350900</v>
+        <v>130350878</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>92233</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>649027</v>
+        <v>649038</v>
       </c>
       <c r="R24" t="n">
-        <v>6995592</v>
+        <v>6995626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350905</v>
+        <v>130350877</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>92233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>649120</v>
+        <v>648991</v>
       </c>
       <c r="R25" t="n">
-        <v>6995740</v>
+        <v>6995659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130350878</v>
+        <v>130350900</v>
       </c>
       <c r="B26" t="n">
-        <v>92220</v>
+        <v>79219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>649038</v>
+        <v>649027</v>
       </c>
       <c r="R26" t="n">
-        <v>6995626</v>
+        <v>6995592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,32 +3174,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130350877</v>
+        <v>130350905</v>
       </c>
       <c r="B27" t="n">
-        <v>92220</v>
+        <v>79219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>648991</v>
+        <v>649120</v>
       </c>
       <c r="R27" t="n">
-        <v>6995659</v>
+        <v>6995740</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130350849</v>
+        <v>130350850</v>
       </c>
       <c r="B28" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>649171</v>
+        <v>649130</v>
       </c>
       <c r="R28" t="n">
-        <v>6995600</v>
+        <v>6995565</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130350850</v>
+        <v>130350849</v>
       </c>
       <c r="B29" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>649130</v>
+        <v>649171</v>
       </c>
       <c r="R29" t="n">
-        <v>6995565</v>
+        <v>6995600</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3478,7 +3478,7 @@
         <v>130350898</v>
       </c>
       <c r="B30" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130350846</v>
+        <v>130350858</v>
       </c>
       <c r="B31" t="n">
-        <v>91761</v>
+        <v>57862</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3579,21 +3579,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>649063</v>
+        <v>648826</v>
       </c>
       <c r="R31" t="n">
-        <v>6995635</v>
+        <v>6995403</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3639,6 +3639,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3665,32 +3670,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350858</v>
+        <v>130350891</v>
       </c>
       <c r="B32" t="n">
-        <v>57854</v>
+        <v>80284</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3700,10 +3705,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>648826</v>
+        <v>649044</v>
       </c>
       <c r="R32" t="n">
-        <v>6995403</v>
+        <v>6995628</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,11 +3741,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3767,32 +3767,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130350891</v>
+        <v>130350846</v>
       </c>
       <c r="B33" t="n">
-        <v>80276</v>
+        <v>91774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>649044</v>
+        <v>649063</v>
       </c>
       <c r="R33" t="n">
-        <v>6995628</v>
+        <v>6995635</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3867,7 +3867,7 @@
         <v>130350852</v>
       </c>
       <c r="B34" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>130350869</v>
       </c>
       <c r="B35" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>130350855</v>
       </c>
       <c r="B36" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>130350911</v>
       </c>
       <c r="B37" t="n">
-        <v>89155</v>
+        <v>89167</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>130350872</v>
       </c>
       <c r="B38" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4369,10 +4369,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130350840</v>
+        <v>130350897</v>
       </c>
       <c r="B39" t="n">
-        <v>91761</v>
+        <v>91794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4380,23 +4380,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4404,10 +4400,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>649262</v>
+        <v>648848</v>
       </c>
       <c r="R39" t="n">
-        <v>6995647</v>
+        <v>6995528</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4466,10 +4462,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130350897</v>
+        <v>130350840</v>
       </c>
       <c r="B40" t="n">
-        <v>91781</v>
+        <v>91774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4477,19 +4473,23 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>648848</v>
+        <v>649262</v>
       </c>
       <c r="R40" t="n">
-        <v>6995528</v>
+        <v>6995647</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4562,7 +4562,7 @@
         <v>130350871</v>
       </c>
       <c r="B41" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>130350845</v>
       </c>
       <c r="B42" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350892</v>
+        <v>130350886</v>
       </c>
       <c r="B43" t="n">
-        <v>57035</v>
+        <v>80324</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>649126</v>
+        <v>648997</v>
       </c>
       <c r="R43" t="n">
-        <v>6995764</v>
+        <v>6995649</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4829,11 +4829,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4860,10 +4855,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350886</v>
+        <v>130350859</v>
       </c>
       <c r="B44" t="n">
-        <v>80316</v>
+        <v>57862</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,21 +4866,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4895,10 +4890,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648997</v>
+        <v>648771</v>
       </c>
       <c r="R44" t="n">
-        <v>6995649</v>
+        <v>6995688</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4931,6 +4926,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4957,10 +4957,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350837</v>
+        <v>130350856</v>
       </c>
       <c r="B45" t="n">
-        <v>91948</v>
+        <v>57862</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,21 +4968,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>649254</v>
+        <v>648835</v>
       </c>
       <c r="R45" t="n">
-        <v>6995609</v>
+        <v>6995397</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5028,6 +5028,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5054,10 +5059,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350896</v>
+        <v>130350854</v>
       </c>
       <c r="B46" t="n">
-        <v>91781</v>
+        <v>57862</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,19 +5070,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5085,10 +5094,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648854</v>
+        <v>648853</v>
       </c>
       <c r="R46" t="n">
-        <v>6995532</v>
+        <v>6995420</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5121,6 +5130,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5147,10 +5161,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350859</v>
+        <v>130350896</v>
       </c>
       <c r="B47" t="n">
-        <v>57854</v>
+        <v>91794</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,23 +5172,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5182,10 +5192,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648771</v>
+        <v>648854</v>
       </c>
       <c r="R47" t="n">
-        <v>6995688</v>
+        <v>6995532</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5218,11 +5228,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5249,10 +5254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350856</v>
+        <v>130350837</v>
       </c>
       <c r="B48" t="n">
-        <v>57854</v>
+        <v>91961</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5260,21 +5265,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5284,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648835</v>
+        <v>649254</v>
       </c>
       <c r="R48" t="n">
-        <v>6995397</v>
+        <v>6995609</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5320,11 +5325,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5351,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350854</v>
+        <v>130350892</v>
       </c>
       <c r="B49" t="n">
-        <v>57854</v>
+        <v>57043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>648853</v>
+        <v>649126</v>
       </c>
       <c r="R49" t="n">
-        <v>6995420</v>
+        <v>6995764</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5456,7 +5456,7 @@
         <v>130350839</v>
       </c>
       <c r="B50" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>130350909</v>
       </c>
       <c r="B51" t="n">
-        <v>89155</v>
+        <v>89167</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>130350883</v>
       </c>
       <c r="B52" t="n">
-        <v>80344</v>
+        <v>80352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5744,32 +5744,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350890</v>
+        <v>130350841</v>
       </c>
       <c r="B53" t="n">
-        <v>80276</v>
+        <v>91774</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649374</v>
+        <v>649195</v>
       </c>
       <c r="R53" t="n">
-        <v>6995542</v>
+        <v>6995694</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350841</v>
+        <v>130350879</v>
       </c>
       <c r="B54" t="n">
-        <v>91761</v>
+        <v>92072</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>649195</v>
+        <v>649062</v>
       </c>
       <c r="R54" t="n">
-        <v>6995694</v>
+        <v>6995641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130350879</v>
+        <v>130350864</v>
       </c>
       <c r="B55" t="n">
-        <v>92059</v>
+        <v>57862</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>649062</v>
+        <v>648993</v>
       </c>
       <c r="R55" t="n">
-        <v>6995641</v>
+        <v>6995756</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6009,6 +6009,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6035,10 +6040,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130350864</v>
+        <v>130350867</v>
       </c>
       <c r="B56" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>648993</v>
+        <v>649095</v>
       </c>
       <c r="R56" t="n">
-        <v>6995756</v>
+        <v>6995637</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6110,7 +6115,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6137,32 +6142,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130350867</v>
+        <v>130350890</v>
       </c>
       <c r="B57" t="n">
-        <v>57854</v>
+        <v>80284</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6172,10 +6177,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>649095</v>
+        <v>649374</v>
       </c>
       <c r="R57" t="n">
-        <v>6995637</v>
+        <v>6995542</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6208,11 +6213,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350901</v>
+        <v>130350874</v>
       </c>
       <c r="B58" t="n">
-        <v>79211</v>
+        <v>57859</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648771</v>
+        <v>648811</v>
       </c>
       <c r="R58" t="n">
-        <v>6995702</v>
+        <v>6995477</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,6 +6310,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6336,10 +6341,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350874</v>
+        <v>130350876</v>
       </c>
       <c r="B59" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6371,10 +6376,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>648811</v>
+        <v>649127</v>
       </c>
       <c r="R59" t="n">
-        <v>6995477</v>
+        <v>6995704</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,7 +6416,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6438,10 +6443,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350876</v>
+        <v>130350901</v>
       </c>
       <c r="B60" t="n">
-        <v>57851</v>
+        <v>79219</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6449,21 +6454,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6473,10 +6478,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>649127</v>
+        <v>648771</v>
       </c>
       <c r="R60" t="n">
-        <v>6995704</v>
+        <v>6995702</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6509,11 +6514,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6543,7 +6543,7 @@
         <v>130350910</v>
       </c>
       <c r="B61" t="n">
-        <v>89155</v>
+        <v>89167</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>130350842</v>
       </c>
       <c r="B62" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350893</v>
+        <v>130350875</v>
       </c>
       <c r="B63" t="n">
-        <v>57035</v>
+        <v>57859</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,16 +6745,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649144</v>
+        <v>648755</v>
       </c>
       <c r="R63" t="n">
-        <v>6995799</v>
+        <v>6995792</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6839,7 +6839,7 @@
         <v>130350862</v>
       </c>
       <c r="B64" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6938,10 +6938,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350875</v>
+        <v>130350893</v>
       </c>
       <c r="B65" t="n">
-        <v>57851</v>
+        <v>57043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6949,16 +6949,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>648755</v>
+        <v>649144</v>
       </c>
       <c r="R65" t="n">
-        <v>6995792</v>
+        <v>6995799</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7043,7 +7043,7 @@
         <v>130350881</v>
       </c>
       <c r="B66" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>130350889</v>
       </c>
       <c r="B67" t="n">
-        <v>80276</v>
+        <v>80284</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>130350848</v>
       </c>
       <c r="B68" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>130350884</v>
       </c>
       <c r="B69" t="n">
-        <v>96183</v>
+        <v>96196</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130350885</v>
       </c>
       <c r="B3" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>130350902</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>130350908</v>
       </c>
       <c r="B5" t="n">
-        <v>89167</v>
+        <v>89168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>130350873</v>
       </c>
       <c r="B6" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>130350865</v>
       </c>
       <c r="B7" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130350866</v>
+        <v>130350904</v>
       </c>
       <c r="B8" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649049</v>
+        <v>649056</v>
       </c>
       <c r="R8" t="n">
-        <v>6995652</v>
+        <v>6995686</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130350870</v>
+        <v>130350866</v>
       </c>
       <c r="B9" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1427,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649039</v>
+        <v>649049</v>
       </c>
       <c r="R9" t="n">
-        <v>6995705</v>
+        <v>6995652</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,7 +1462,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,10 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130350860</v>
+        <v>130350870</v>
       </c>
       <c r="B10" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1529,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>648687</v>
+        <v>649039</v>
       </c>
       <c r="R10" t="n">
-        <v>6995932</v>
+        <v>6995705</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130350904</v>
+        <v>130350860</v>
       </c>
       <c r="B11" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,21 +1602,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1631,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649056</v>
+        <v>648687</v>
       </c>
       <c r="R11" t="n">
-        <v>6995686</v>
+        <v>6995932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,6 +1662,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,10 +1693,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130350853</v>
+        <v>130350857</v>
       </c>
       <c r="B12" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648941</v>
+        <v>648826</v>
       </c>
       <c r="R12" t="n">
-        <v>6995608</v>
+        <v>6995407</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130350857</v>
+        <v>130350853</v>
       </c>
       <c r="B13" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648826</v>
+        <v>648941</v>
       </c>
       <c r="R13" t="n">
-        <v>6995407</v>
+        <v>6995608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350903</v>
+        <v>130350899</v>
       </c>
       <c r="B14" t="n">
-        <v>79219</v>
+        <v>91795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,23 +1908,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1932,10 +1928,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>648792</v>
+        <v>648996</v>
       </c>
       <c r="R14" t="n">
-        <v>6995927</v>
+        <v>6995647</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1990,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130351125</v>
+        <v>130350861</v>
       </c>
       <c r="B15" t="n">
-        <v>92193</v>
+        <v>57863</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,21 +2001,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2029,10 +2025,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648877</v>
+        <v>648707</v>
       </c>
       <c r="R15" t="n">
-        <v>6995565</v>
+        <v>6995954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2065,6 +2061,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2091,10 +2092,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130350861</v>
+        <v>130350903</v>
       </c>
       <c r="B16" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,21 +2103,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2126,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648707</v>
+        <v>648792</v>
       </c>
       <c r="R16" t="n">
-        <v>6995954</v>
+        <v>6995927</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2162,11 +2163,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130350899</v>
+        <v>130350844</v>
       </c>
       <c r="B17" t="n">
-        <v>91794</v>
+        <v>91775</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2204,19 +2200,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648996</v>
+        <v>649036</v>
       </c>
       <c r="R17" t="n">
-        <v>6995647</v>
+        <v>6995660</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,10 +2286,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130350844</v>
+        <v>130351125</v>
       </c>
       <c r="B18" t="n">
-        <v>91774</v>
+        <v>92194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,21 +2297,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6040186</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>649036</v>
+        <v>648877</v>
       </c>
       <c r="R18" t="n">
-        <v>6995660</v>
+        <v>6995565</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130350868</v>
+        <v>130351124</v>
       </c>
       <c r="B19" t="n">
-        <v>57862</v>
+        <v>92194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2394,21 +2394,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649093</v>
+        <v>649116</v>
       </c>
       <c r="R19" t="n">
-        <v>6995638</v>
+        <v>6995496</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,11 +2454,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2485,32 +2480,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130350863</v>
+        <v>130350838</v>
       </c>
       <c r="B20" t="n">
-        <v>57862</v>
+        <v>91738</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2520,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649031</v>
+        <v>649074</v>
       </c>
       <c r="R20" t="n">
-        <v>6995803</v>
+        <v>6995652</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,11 +2551,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2587,10 +2577,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130350847</v>
+        <v>130350868</v>
       </c>
       <c r="B21" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2622,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>649222</v>
+        <v>649093</v>
       </c>
       <c r="R21" t="n">
-        <v>6995657</v>
+        <v>6995638</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2662,7 +2652,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2689,10 +2679,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130351124</v>
+        <v>130350863</v>
       </c>
       <c r="B22" t="n">
-        <v>92193</v>
+        <v>57863</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2700,21 +2690,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2724,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>649116</v>
+        <v>649031</v>
       </c>
       <c r="R22" t="n">
-        <v>6995496</v>
+        <v>6995803</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2760,6 +2750,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2786,32 +2781,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130350838</v>
+        <v>130350847</v>
       </c>
       <c r="B23" t="n">
-        <v>91737</v>
+        <v>57863</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2821,10 +2816,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649074</v>
+        <v>649222</v>
       </c>
       <c r="R23" t="n">
-        <v>6995652</v>
+        <v>6995657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2857,6 +2852,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2883,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350878</v>
+        <v>130350900</v>
       </c>
       <c r="B24" t="n">
-        <v>92233</v>
+        <v>79220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>649038</v>
+        <v>649027</v>
       </c>
       <c r="R24" t="n">
-        <v>6995626</v>
+        <v>6995592</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350877</v>
+        <v>130350905</v>
       </c>
       <c r="B25" t="n">
-        <v>92233</v>
+        <v>79220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>648991</v>
+        <v>649120</v>
       </c>
       <c r="R25" t="n">
-        <v>6995659</v>
+        <v>6995740</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130350900</v>
+        <v>130350878</v>
       </c>
       <c r="B26" t="n">
-        <v>79219</v>
+        <v>92234</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>649027</v>
+        <v>649038</v>
       </c>
       <c r="R26" t="n">
-        <v>6995592</v>
+        <v>6995626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,32 +3174,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130350905</v>
+        <v>130350877</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>92234</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>649120</v>
+        <v>648991</v>
       </c>
       <c r="R27" t="n">
-        <v>6995740</v>
+        <v>6995659</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3274,7 +3274,7 @@
         <v>130350850</v>
       </c>
       <c r="B28" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>130350849</v>
       </c>
       <c r="B29" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350898</v>
+        <v>130350846</v>
       </c>
       <c r="B30" t="n">
-        <v>91794</v>
+        <v>91775</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3486,19 +3486,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3506,10 +3510,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>648849</v>
+        <v>649063</v>
       </c>
       <c r="R30" t="n">
-        <v>6995437</v>
+        <v>6995635</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3571,7 +3575,7 @@
         <v>130350858</v>
       </c>
       <c r="B31" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3670,34 +3674,30 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350891</v>
+        <v>130350898</v>
       </c>
       <c r="B32" t="n">
-        <v>80284</v>
+        <v>91795</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>649044</v>
+        <v>648849</v>
       </c>
       <c r="R32" t="n">
-        <v>6995628</v>
+        <v>6995437</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3767,32 +3767,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130350846</v>
+        <v>130350891</v>
       </c>
       <c r="B33" t="n">
-        <v>91774</v>
+        <v>80285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>649063</v>
+        <v>649044</v>
       </c>
       <c r="R33" t="n">
-        <v>6995635</v>
+        <v>6995628</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3867,7 +3867,7 @@
         <v>130350852</v>
       </c>
       <c r="B34" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>130350869</v>
       </c>
       <c r="B35" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>130350855</v>
       </c>
       <c r="B36" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>130350911</v>
       </c>
       <c r="B37" t="n">
-        <v>89167</v>
+        <v>89168</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>130350872</v>
       </c>
       <c r="B38" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>130350897</v>
       </c>
       <c r="B39" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>130350840</v>
       </c>
       <c r="B40" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>130350871</v>
       </c>
       <c r="B41" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>130350845</v>
       </c>
       <c r="B42" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350886</v>
+        <v>130350896</v>
       </c>
       <c r="B43" t="n">
-        <v>80324</v>
+        <v>91795</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,23 +4769,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4793,10 +4789,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>648997</v>
+        <v>648854</v>
       </c>
       <c r="R43" t="n">
-        <v>6995649</v>
+        <v>6995532</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4855,10 +4851,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350859</v>
+        <v>130350886</v>
       </c>
       <c r="B44" t="n">
-        <v>57862</v>
+        <v>80325</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,21 +4862,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4890,10 +4886,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648771</v>
+        <v>648997</v>
       </c>
       <c r="R44" t="n">
-        <v>6995688</v>
+        <v>6995649</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4926,11 +4922,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4957,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350856</v>
+        <v>130350837</v>
       </c>
       <c r="B45" t="n">
-        <v>57862</v>
+        <v>91962</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,21 +4959,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4992,10 +4983,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648835</v>
+        <v>649254</v>
       </c>
       <c r="R45" t="n">
-        <v>6995397</v>
+        <v>6995609</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5028,11 +5019,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5059,10 +5045,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350854</v>
+        <v>130350859</v>
       </c>
       <c r="B46" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5094,10 +5080,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648853</v>
+        <v>648771</v>
       </c>
       <c r="R46" t="n">
-        <v>6995420</v>
+        <v>6995688</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5134,7 +5120,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5161,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350896</v>
+        <v>130350856</v>
       </c>
       <c r="B47" t="n">
-        <v>91794</v>
+        <v>57863</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5172,19 +5158,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5192,10 +5182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648854</v>
+        <v>648835</v>
       </c>
       <c r="R47" t="n">
-        <v>6995532</v>
+        <v>6995397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5228,6 +5218,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5254,10 +5249,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350837</v>
+        <v>130350854</v>
       </c>
       <c r="B48" t="n">
-        <v>91961</v>
+        <v>57863</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,21 +5260,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5289,10 +5284,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>649254</v>
+        <v>648853</v>
       </c>
       <c r="R48" t="n">
-        <v>6995609</v>
+        <v>6995420</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,6 +5320,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5354,7 +5354,7 @@
         <v>130350892</v>
       </c>
       <c r="B49" t="n">
-        <v>57043</v>
+        <v>57044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5453,32 +5453,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130350839</v>
+        <v>130350883</v>
       </c>
       <c r="B50" t="n">
-        <v>91774</v>
+        <v>80353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>649369</v>
+        <v>649094</v>
       </c>
       <c r="R50" t="n">
-        <v>6995531</v>
+        <v>6995519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130350909</v>
+        <v>130350839</v>
       </c>
       <c r="B51" t="n">
-        <v>89167</v>
+        <v>91775</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>648957</v>
+        <v>649369</v>
       </c>
       <c r="R51" t="n">
-        <v>6995579</v>
+        <v>6995531</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,32 +5647,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350883</v>
+        <v>130350909</v>
       </c>
       <c r="B52" t="n">
-        <v>80352</v>
+        <v>89168</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>649094</v>
+        <v>648957</v>
       </c>
       <c r="R52" t="n">
-        <v>6995519</v>
+        <v>6995579</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5747,7 +5747,7 @@
         <v>130350841</v>
       </c>
       <c r="B53" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>130350879</v>
       </c>
       <c r="B54" t="n">
-        <v>92072</v>
+        <v>92073</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>130350864</v>
       </c>
       <c r="B55" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>130350867</v>
       </c>
       <c r="B56" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>130350890</v>
       </c>
       <c r="B57" t="n">
-        <v>80284</v>
+        <v>80285</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350874</v>
+        <v>130350901</v>
       </c>
       <c r="B58" t="n">
-        <v>57859</v>
+        <v>79220</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648811</v>
+        <v>648771</v>
       </c>
       <c r="R58" t="n">
-        <v>6995477</v>
+        <v>6995702</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,11 +6310,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6341,10 +6336,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350876</v>
+        <v>130350874</v>
       </c>
       <c r="B59" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6376,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>649127</v>
+        <v>648811</v>
       </c>
       <c r="R59" t="n">
-        <v>6995704</v>
+        <v>6995477</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6416,7 +6411,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6443,10 +6438,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350901</v>
+        <v>130350876</v>
       </c>
       <c r="B60" t="n">
-        <v>79219</v>
+        <v>57860</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6454,21 +6449,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6478,10 +6473,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>648771</v>
+        <v>649127</v>
       </c>
       <c r="R60" t="n">
-        <v>6995702</v>
+        <v>6995704</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6514,6 +6509,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6543,7 +6543,7 @@
         <v>130350910</v>
       </c>
       <c r="B61" t="n">
-        <v>89167</v>
+        <v>89168</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>130350842</v>
       </c>
       <c r="B62" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350875</v>
+        <v>130350893</v>
       </c>
       <c r="B63" t="n">
-        <v>57859</v>
+        <v>57044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,16 +6745,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>648755</v>
+        <v>649144</v>
       </c>
       <c r="R63" t="n">
-        <v>6995792</v>
+        <v>6995799</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6836,10 +6836,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350862</v>
+        <v>130350875</v>
       </c>
       <c r="B64" t="n">
-        <v>57862</v>
+        <v>57860</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6847,16 +6847,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>648830</v>
+        <v>648755</v>
       </c>
       <c r="R64" t="n">
-        <v>6995874</v>
+        <v>6995792</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6938,32 +6938,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350893</v>
+        <v>130350889</v>
       </c>
       <c r="B65" t="n">
-        <v>57043</v>
+        <v>80285</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102612</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>649144</v>
+        <v>649384</v>
       </c>
       <c r="R65" t="n">
-        <v>6995799</v>
+        <v>6995514</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7009,11 +7009,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7043,7 +7038,7 @@
         <v>130350881</v>
       </c>
       <c r="B66" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7137,32 +7132,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130350889</v>
+        <v>130350862</v>
       </c>
       <c r="B67" t="n">
-        <v>80284</v>
+        <v>57863</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7172,10 +7167,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649384</v>
+        <v>648830</v>
       </c>
       <c r="R67" t="n">
-        <v>6995514</v>
+        <v>6995874</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7208,6 +7203,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7237,7 +7237,7 @@
         <v>130350848</v>
       </c>
       <c r="B68" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>130350884</v>
       </c>
       <c r="B69" t="n">
-        <v>96196</v>
+        <v>96197</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130350885</v>
       </c>
       <c r="B3" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350902</v>
+        <v>130350873</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>57053</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648702</v>
+        <v>649139</v>
       </c>
       <c r="R4" t="n">
-        <v>6995939</v>
+        <v>6995673</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,7 +997,7 @@
         <v>130350908</v>
       </c>
       <c r="B5" t="n">
-        <v>89168</v>
+        <v>89169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,32 +1091,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130350873</v>
+        <v>130350902</v>
       </c>
       <c r="B6" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>649139</v>
+        <v>648702</v>
       </c>
       <c r="R6" t="n">
-        <v>6995673</v>
+        <v>6995939</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,11 +1162,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,7 +1191,7 @@
         <v>130350865</v>
       </c>
       <c r="B7" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>130350904</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>130350866</v>
       </c>
       <c r="B9" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>130350870</v>
       </c>
       <c r="B10" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>130350860</v>
       </c>
       <c r="B11" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,10 +1693,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130350857</v>
+        <v>130350853</v>
       </c>
       <c r="B12" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>648826</v>
+        <v>648941</v>
       </c>
       <c r="R12" t="n">
-        <v>6995407</v>
+        <v>6995608</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130350853</v>
+        <v>130350857</v>
       </c>
       <c r="B13" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>648941</v>
+        <v>648826</v>
       </c>
       <c r="R13" t="n">
-        <v>6995608</v>
+        <v>6995407</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350899</v>
+        <v>130350844</v>
       </c>
       <c r="B14" t="n">
-        <v>91795</v>
+        <v>91776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,19 +1908,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1928,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>648996</v>
+        <v>649036</v>
       </c>
       <c r="R14" t="n">
-        <v>6995647</v>
+        <v>6995660</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130350861</v>
+        <v>130350903</v>
       </c>
       <c r="B15" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2001,21 +2005,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2025,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648707</v>
+        <v>648792</v>
       </c>
       <c r="R15" t="n">
-        <v>6995954</v>
+        <v>6995927</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,11 +2065,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2092,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130350903</v>
+        <v>130350899</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>91796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,23 +2102,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2127,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648792</v>
+        <v>648996</v>
       </c>
       <c r="R16" t="n">
-        <v>6995927</v>
+        <v>6995647</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130350844</v>
+        <v>130350861</v>
       </c>
       <c r="B17" t="n">
-        <v>91775</v>
+        <v>57864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2195,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>649036</v>
+        <v>648707</v>
       </c>
       <c r="R17" t="n">
-        <v>6995660</v>
+        <v>6995954</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,6 +2255,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2289,7 +2289,7 @@
         <v>130351125</v>
       </c>
       <c r="B18" t="n">
-        <v>92194</v>
+        <v>92195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130351124</v>
+        <v>130350838</v>
       </c>
       <c r="B19" t="n">
-        <v>92194</v>
+        <v>91739</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040186</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649116</v>
+        <v>649074</v>
       </c>
       <c r="R19" t="n">
-        <v>6995496</v>
+        <v>6995652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,32 +2480,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130350838</v>
+        <v>130351124</v>
       </c>
       <c r="B20" t="n">
-        <v>91738</v>
+        <v>92195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6040186</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649074</v>
+        <v>649116</v>
       </c>
       <c r="R20" t="n">
-        <v>6995652</v>
+        <v>6995496</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
         <v>130350868</v>
       </c>
       <c r="B21" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>130350863</v>
       </c>
       <c r="B22" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>130350847</v>
       </c>
       <c r="B23" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350900</v>
+        <v>130350878</v>
       </c>
       <c r="B24" t="n">
-        <v>79220</v>
+        <v>92235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>649027</v>
+        <v>649038</v>
       </c>
       <c r="R24" t="n">
-        <v>6995592</v>
+        <v>6995626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350905</v>
+        <v>130350877</v>
       </c>
       <c r="B25" t="n">
-        <v>79220</v>
+        <v>92235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>649120</v>
+        <v>648991</v>
       </c>
       <c r="R25" t="n">
-        <v>6995740</v>
+        <v>6995659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130350878</v>
+        <v>130350900</v>
       </c>
       <c r="B26" t="n">
-        <v>92234</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>649038</v>
+        <v>649027</v>
       </c>
       <c r="R26" t="n">
-        <v>6995626</v>
+        <v>6995592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,32 +3174,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130350877</v>
+        <v>130350905</v>
       </c>
       <c r="B27" t="n">
-        <v>92234</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>648991</v>
+        <v>649120</v>
       </c>
       <c r="R27" t="n">
-        <v>6995659</v>
+        <v>6995740</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130350850</v>
+        <v>130350849</v>
       </c>
       <c r="B28" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>649130</v>
+        <v>649171</v>
       </c>
       <c r="R28" t="n">
-        <v>6995565</v>
+        <v>6995600</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130350849</v>
+        <v>130350850</v>
       </c>
       <c r="B29" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>649171</v>
+        <v>649130</v>
       </c>
       <c r="R29" t="n">
-        <v>6995600</v>
+        <v>6995565</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3475,32 +3475,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350846</v>
+        <v>130350891</v>
       </c>
       <c r="B30" t="n">
-        <v>91775</v>
+        <v>80286</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>649063</v>
+        <v>649044</v>
       </c>
       <c r="R30" t="n">
-        <v>6995635</v>
+        <v>6995628</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130350858</v>
+        <v>130350846</v>
       </c>
       <c r="B31" t="n">
-        <v>57863</v>
+        <v>91776</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3583,21 +3583,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>648826</v>
+        <v>649063</v>
       </c>
       <c r="R31" t="n">
-        <v>6995403</v>
+        <v>6995635</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3643,11 +3643,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3677,7 +3672,7 @@
         <v>130350898</v>
       </c>
       <c r="B32" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3767,32 +3762,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130350891</v>
+        <v>130350858</v>
       </c>
       <c r="B33" t="n">
-        <v>80285</v>
+        <v>57864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3802,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>649044</v>
+        <v>648826</v>
       </c>
       <c r="R33" t="n">
-        <v>6995628</v>
+        <v>6995403</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,6 +3833,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3867,7 +3867,7 @@
         <v>130350852</v>
       </c>
       <c r="B34" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>130350869</v>
       </c>
       <c r="B35" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>130350855</v>
       </c>
       <c r="B36" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>130350911</v>
       </c>
       <c r="B37" t="n">
-        <v>89168</v>
+        <v>89169</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>130350872</v>
       </c>
       <c r="B38" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4369,10 +4369,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130350897</v>
+        <v>130350840</v>
       </c>
       <c r="B39" t="n">
-        <v>91795</v>
+        <v>91776</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4380,19 +4380,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4400,10 +4404,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>648848</v>
+        <v>649262</v>
       </c>
       <c r="R39" t="n">
-        <v>6995528</v>
+        <v>6995647</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4462,10 +4466,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130350840</v>
+        <v>130350897</v>
       </c>
       <c r="B40" t="n">
-        <v>91775</v>
+        <v>91796</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4473,23 +4477,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>649262</v>
+        <v>648848</v>
       </c>
       <c r="R40" t="n">
-        <v>6995647</v>
+        <v>6995528</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4562,7 +4562,7 @@
         <v>130350871</v>
       </c>
       <c r="B41" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>130350845</v>
       </c>
       <c r="B42" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350896</v>
+        <v>130350837</v>
       </c>
       <c r="B43" t="n">
-        <v>91795</v>
+        <v>91963</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,19 +4769,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>1588</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4789,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>648854</v>
+        <v>649254</v>
       </c>
       <c r="R43" t="n">
-        <v>6995532</v>
+        <v>6995609</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4851,10 +4855,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350886</v>
+        <v>130350896</v>
       </c>
       <c r="B44" t="n">
-        <v>80325</v>
+        <v>91796</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4862,23 +4866,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648997</v>
+        <v>648854</v>
       </c>
       <c r="R44" t="n">
-        <v>6995649</v>
+        <v>6995532</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350837</v>
+        <v>130350892</v>
       </c>
       <c r="B45" t="n">
-        <v>91962</v>
+        <v>57044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1588</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>649254</v>
+        <v>649126</v>
       </c>
       <c r="R45" t="n">
-        <v>6995609</v>
+        <v>6995764</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5019,6 +5019,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5045,10 +5050,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350859</v>
+        <v>130350886</v>
       </c>
       <c r="B46" t="n">
-        <v>57863</v>
+        <v>80326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5056,21 +5061,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5080,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648771</v>
+        <v>648997</v>
       </c>
       <c r="R46" t="n">
-        <v>6995688</v>
+        <v>6995649</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5116,11 +5121,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5147,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350856</v>
+        <v>130350859</v>
       </c>
       <c r="B47" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648835</v>
+        <v>648771</v>
       </c>
       <c r="R47" t="n">
-        <v>6995397</v>
+        <v>6995688</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5249,10 +5249,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350854</v>
+        <v>130350856</v>
       </c>
       <c r="B48" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648853</v>
+        <v>648835</v>
       </c>
       <c r="R48" t="n">
-        <v>6995420</v>
+        <v>6995397</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350892</v>
+        <v>130350854</v>
       </c>
       <c r="B49" t="n">
-        <v>57044</v>
+        <v>57864</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>649126</v>
+        <v>648853</v>
       </c>
       <c r="R49" t="n">
-        <v>6995764</v>
+        <v>6995420</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5456,7 +5456,7 @@
         <v>130350883</v>
       </c>
       <c r="B50" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130350839</v>
+        <v>130350909</v>
       </c>
       <c r="B51" t="n">
-        <v>91775</v>
+        <v>89169</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>649369</v>
+        <v>648957</v>
       </c>
       <c r="R51" t="n">
-        <v>6995531</v>
+        <v>6995579</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,10 +5647,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350909</v>
+        <v>130350839</v>
       </c>
       <c r="B52" t="n">
-        <v>89168</v>
+        <v>91776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5658,21 +5658,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>648957</v>
+        <v>649369</v>
       </c>
       <c r="R52" t="n">
-        <v>6995579</v>
+        <v>6995531</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350841</v>
+        <v>130350879</v>
       </c>
       <c r="B53" t="n">
-        <v>91775</v>
+        <v>92074</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5755,21 +5755,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649195</v>
+        <v>649062</v>
       </c>
       <c r="R53" t="n">
-        <v>6995694</v>
+        <v>6995641</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5841,32 +5841,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350879</v>
+        <v>130350890</v>
       </c>
       <c r="B54" t="n">
-        <v>92073</v>
+        <v>80286</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>649062</v>
+        <v>649374</v>
       </c>
       <c r="R54" t="n">
-        <v>6995641</v>
+        <v>6995542</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130350864</v>
+        <v>130350841</v>
       </c>
       <c r="B55" t="n">
-        <v>57863</v>
+        <v>91776</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>648993</v>
+        <v>649195</v>
       </c>
       <c r="R55" t="n">
-        <v>6995756</v>
+        <v>6995694</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6009,11 +6009,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6040,10 +6035,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130350867</v>
+        <v>130350864</v>
       </c>
       <c r="B56" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6075,10 +6070,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>649095</v>
+        <v>648993</v>
       </c>
       <c r="R56" t="n">
-        <v>6995637</v>
+        <v>6995756</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6115,7 +6110,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6142,32 +6137,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130350890</v>
+        <v>130350867</v>
       </c>
       <c r="B57" t="n">
-        <v>80285</v>
+        <v>57864</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6177,10 +6172,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>649374</v>
+        <v>649095</v>
       </c>
       <c r="R57" t="n">
-        <v>6995542</v>
+        <v>6995637</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6213,6 +6208,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350901</v>
+        <v>130350874</v>
       </c>
       <c r="B58" t="n">
-        <v>79220</v>
+        <v>57861</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648771</v>
+        <v>648811</v>
       </c>
       <c r="R58" t="n">
-        <v>6995702</v>
+        <v>6995477</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,6 +6310,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6336,10 +6341,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350874</v>
+        <v>130350876</v>
       </c>
       <c r="B59" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6371,10 +6376,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>648811</v>
+        <v>649127</v>
       </c>
       <c r="R59" t="n">
-        <v>6995477</v>
+        <v>6995704</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,7 +6416,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6438,10 +6443,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350876</v>
+        <v>130350901</v>
       </c>
       <c r="B60" t="n">
-        <v>57860</v>
+        <v>79221</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6449,21 +6454,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6473,10 +6478,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>649127</v>
+        <v>648771</v>
       </c>
       <c r="R60" t="n">
-        <v>6995704</v>
+        <v>6995702</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6509,11 +6514,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6543,7 +6543,7 @@
         <v>130350910</v>
       </c>
       <c r="B61" t="n">
-        <v>89168</v>
+        <v>89169</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>130350842</v>
       </c>
       <c r="B62" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350893</v>
+        <v>130350875</v>
       </c>
       <c r="B63" t="n">
-        <v>57044</v>
+        <v>57861</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,16 +6745,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649144</v>
+        <v>648755</v>
       </c>
       <c r="R63" t="n">
-        <v>6995799</v>
+        <v>6995792</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6836,10 +6836,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350875</v>
+        <v>130350862</v>
       </c>
       <c r="B64" t="n">
-        <v>57860</v>
+        <v>57864</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6847,16 +6847,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>648755</v>
+        <v>648830</v>
       </c>
       <c r="R64" t="n">
-        <v>6995792</v>
+        <v>6995874</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6938,32 +6938,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350889</v>
+        <v>130350893</v>
       </c>
       <c r="B65" t="n">
-        <v>80285</v>
+        <v>57044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>102612</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>649384</v>
+        <v>649144</v>
       </c>
       <c r="R65" t="n">
-        <v>6995514</v>
+        <v>6995799</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7009,6 +7009,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7038,7 +7043,7 @@
         <v>130350881</v>
       </c>
       <c r="B66" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7132,32 +7137,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130350862</v>
+        <v>130350889</v>
       </c>
       <c r="B67" t="n">
-        <v>57863</v>
+        <v>80286</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7167,10 +7172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>648830</v>
+        <v>649384</v>
       </c>
       <c r="R67" t="n">
-        <v>6995874</v>
+        <v>6995514</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7203,11 +7208,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7237,7 +7237,7 @@
         <v>130350848</v>
       </c>
       <c r="B68" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>130350884</v>
       </c>
       <c r="B69" t="n">
-        <v>96197</v>
+        <v>96200</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -892,32 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350873</v>
+        <v>130350908</v>
       </c>
       <c r="B4" t="n">
-        <v>57053</v>
+        <v>89169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649139</v>
+        <v>649250</v>
       </c>
       <c r="R4" t="n">
-        <v>6995673</v>
+        <v>6995605</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,32 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350908</v>
+        <v>130350873</v>
       </c>
       <c r="B5" t="n">
-        <v>89169</v>
+        <v>57053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649250</v>
+        <v>649139</v>
       </c>
       <c r="R5" t="n">
-        <v>6995605</v>
+        <v>6995673</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1060,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130350904</v>
+        <v>130350866</v>
       </c>
       <c r="B8" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649056</v>
+        <v>649049</v>
       </c>
       <c r="R8" t="n">
-        <v>6995686</v>
+        <v>6995652</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,6 +1361,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,7 +1392,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130350866</v>
+        <v>130350870</v>
       </c>
       <c r="B9" t="n">
         <v>57864</v>
@@ -1422,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649049</v>
+        <v>649039</v>
       </c>
       <c r="R9" t="n">
-        <v>6995652</v>
+        <v>6995705</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1462,7 +1467,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,7 +1494,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130350870</v>
+        <v>130350860</v>
       </c>
       <c r="B10" t="n">
         <v>57864</v>
@@ -1524,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649039</v>
+        <v>648687</v>
       </c>
       <c r="R10" t="n">
-        <v>6995705</v>
+        <v>6995932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130350860</v>
+        <v>130350904</v>
       </c>
       <c r="B11" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,21 +1607,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1626,10 +1631,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>648687</v>
+        <v>649056</v>
       </c>
       <c r="R11" t="n">
-        <v>6995932</v>
+        <v>6995686</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,11 +1667,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130350903</v>
+        <v>130350899</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>91796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2005,23 +2005,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2029,10 +2025,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>648792</v>
+        <v>648996</v>
       </c>
       <c r="R15" t="n">
-        <v>6995927</v>
+        <v>6995647</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,10 +2087,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130350899</v>
+        <v>130350903</v>
       </c>
       <c r="B16" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2102,19 +2098,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>648996</v>
+        <v>648792</v>
       </c>
       <c r="R16" t="n">
-        <v>6995647</v>
+        <v>6995927</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130351124</v>
+        <v>130350847</v>
       </c>
       <c r="B20" t="n">
-        <v>92195</v>
+        <v>57864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2491,21 +2491,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649116</v>
+        <v>649222</v>
       </c>
       <c r="R20" t="n">
-        <v>6995496</v>
+        <v>6995657</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,6 +2551,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2577,10 +2582,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130350868</v>
+        <v>130351124</v>
       </c>
       <c r="B21" t="n">
-        <v>57864</v>
+        <v>92195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2588,21 +2593,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>649093</v>
+        <v>649116</v>
       </c>
       <c r="R21" t="n">
-        <v>6995638</v>
+        <v>6995496</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2648,11 +2653,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2679,7 +2679,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130350863</v>
+        <v>130350868</v>
       </c>
       <c r="B22" t="n">
         <v>57864</v>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>649031</v>
+        <v>649093</v>
       </c>
       <c r="R22" t="n">
-        <v>6995803</v>
+        <v>6995638</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130350847</v>
+        <v>130350863</v>
       </c>
       <c r="B23" t="n">
         <v>57864</v>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649222</v>
+        <v>649031</v>
       </c>
       <c r="R23" t="n">
-        <v>6995657</v>
+        <v>6995803</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2883,7 +2883,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350878</v>
+        <v>130350877</v>
       </c>
       <c r="B24" t="n">
         <v>92235</v>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>649038</v>
+        <v>648991</v>
       </c>
       <c r="R24" t="n">
-        <v>6995626</v>
+        <v>6995659</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350877</v>
+        <v>130350878</v>
       </c>
       <c r="B25" t="n">
         <v>92235</v>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>648991</v>
+        <v>649038</v>
       </c>
       <c r="R25" t="n">
-        <v>6995659</v>
+        <v>6995626</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3475,32 +3475,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350891</v>
+        <v>130350846</v>
       </c>
       <c r="B30" t="n">
-        <v>80286</v>
+        <v>91776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>649044</v>
+        <v>649063</v>
       </c>
       <c r="R30" t="n">
-        <v>6995628</v>
+        <v>6995635</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130350846</v>
+        <v>130350898</v>
       </c>
       <c r="B31" t="n">
-        <v>91776</v>
+        <v>91796</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3583,23 +3583,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3607,10 +3603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>649063</v>
+        <v>648849</v>
       </c>
       <c r="R31" t="n">
-        <v>6995635</v>
+        <v>6995437</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3669,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350898</v>
+        <v>130350858</v>
       </c>
       <c r="B32" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3680,19 +3676,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>648849</v>
+        <v>648826</v>
       </c>
       <c r="R32" t="n">
-        <v>6995437</v>
+        <v>6995403</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,6 +3736,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3762,32 +3767,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130350858</v>
+        <v>130350891</v>
       </c>
       <c r="B33" t="n">
-        <v>57864</v>
+        <v>80286</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3797,10 +3802,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>648826</v>
+        <v>649044</v>
       </c>
       <c r="R33" t="n">
-        <v>6995403</v>
+        <v>6995628</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3833,11 +3838,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350837</v>
+        <v>130350859</v>
       </c>
       <c r="B43" t="n">
-        <v>91963</v>
+        <v>57864</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>649254</v>
+        <v>648771</v>
       </c>
       <c r="R43" t="n">
-        <v>6995609</v>
+        <v>6995688</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4829,6 +4829,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4855,10 +4860,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350896</v>
+        <v>130350856</v>
       </c>
       <c r="B44" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,19 +4871,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4886,10 +4895,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648854</v>
+        <v>648835</v>
       </c>
       <c r="R44" t="n">
-        <v>6995532</v>
+        <v>6995397</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4922,6 +4931,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4948,10 +4962,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350892</v>
+        <v>130350854</v>
       </c>
       <c r="B45" t="n">
-        <v>57044</v>
+        <v>57864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4959,16 +4973,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4983,10 +4997,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>649126</v>
+        <v>648853</v>
       </c>
       <c r="R45" t="n">
-        <v>6995764</v>
+        <v>6995420</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5023,7 +5037,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5050,10 +5064,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350886</v>
+        <v>130350892</v>
       </c>
       <c r="B46" t="n">
-        <v>80326</v>
+        <v>57044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5061,21 +5075,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5085,10 +5099,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648997</v>
+        <v>649126</v>
       </c>
       <c r="R46" t="n">
-        <v>6995649</v>
+        <v>6995764</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5121,6 +5135,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5147,10 +5166,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350859</v>
+        <v>130350837</v>
       </c>
       <c r="B47" t="n">
-        <v>57864</v>
+        <v>91963</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,21 +5177,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5182,10 +5201,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648771</v>
+        <v>649254</v>
       </c>
       <c r="R47" t="n">
-        <v>6995688</v>
+        <v>6995609</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5218,11 +5237,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5249,10 +5263,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350856</v>
+        <v>130350896</v>
       </c>
       <c r="B48" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5260,23 +5274,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5284,10 +5294,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648835</v>
+        <v>648854</v>
       </c>
       <c r="R48" t="n">
-        <v>6995397</v>
+        <v>6995532</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5320,11 +5330,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5351,10 +5356,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350854</v>
+        <v>130350886</v>
       </c>
       <c r="B49" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,21 +5367,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5386,10 +5391,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>648853</v>
+        <v>648997</v>
       </c>
       <c r="R49" t="n">
-        <v>6995420</v>
+        <v>6995649</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5422,11 +5427,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5453,32 +5453,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130350883</v>
+        <v>130350909</v>
       </c>
       <c r="B50" t="n">
-        <v>80354</v>
+        <v>89169</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>649094</v>
+        <v>648957</v>
       </c>
       <c r="R50" t="n">
-        <v>6995519</v>
+        <v>6995579</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130350909</v>
+        <v>130350839</v>
       </c>
       <c r="B51" t="n">
-        <v>89169</v>
+        <v>91776</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>648957</v>
+        <v>649369</v>
       </c>
       <c r="R51" t="n">
-        <v>6995579</v>
+        <v>6995531</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,32 +5647,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350839</v>
+        <v>130350883</v>
       </c>
       <c r="B52" t="n">
-        <v>91776</v>
+        <v>80354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>649369</v>
+        <v>649094</v>
       </c>
       <c r="R52" t="n">
-        <v>6995531</v>
+        <v>6995519</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5744,32 +5744,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350879</v>
+        <v>130350890</v>
       </c>
       <c r="B53" t="n">
-        <v>92074</v>
+        <v>80286</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649062</v>
+        <v>649374</v>
       </c>
       <c r="R53" t="n">
-        <v>6995641</v>
+        <v>6995542</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5841,32 +5841,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350890</v>
+        <v>130350879</v>
       </c>
       <c r="B54" t="n">
-        <v>80286</v>
+        <v>92074</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>649374</v>
+        <v>649062</v>
       </c>
       <c r="R54" t="n">
-        <v>6995542</v>
+        <v>6995641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350874</v>
+        <v>130350901</v>
       </c>
       <c r="B58" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648811</v>
+        <v>648771</v>
       </c>
       <c r="R58" t="n">
-        <v>6995477</v>
+        <v>6995702</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,11 +6310,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6341,7 +6336,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350876</v>
+        <v>130350874</v>
       </c>
       <c r="B59" t="n">
         <v>57861</v>
@@ -6376,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>649127</v>
+        <v>648811</v>
       </c>
       <c r="R59" t="n">
-        <v>6995704</v>
+        <v>6995477</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6416,7 +6411,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6443,10 +6438,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350901</v>
+        <v>130350876</v>
       </c>
       <c r="B60" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6454,21 +6449,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6478,10 +6473,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>648771</v>
+        <v>649127</v>
       </c>
       <c r="R60" t="n">
-        <v>6995702</v>
+        <v>6995704</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6514,6 +6509,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6540,10 +6540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130350910</v>
+        <v>130350842</v>
       </c>
       <c r="B61" t="n">
-        <v>89169</v>
+        <v>91776</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>648873</v>
+        <v>649096</v>
       </c>
       <c r="R61" t="n">
-        <v>6995569</v>
+        <v>6995501</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6637,10 +6637,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130350842</v>
+        <v>130350910</v>
       </c>
       <c r="B62" t="n">
-        <v>91776</v>
+        <v>89169</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6648,21 +6648,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>649096</v>
+        <v>648873</v>
       </c>
       <c r="R62" t="n">
-        <v>6995501</v>
+        <v>6995569</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350875</v>
+        <v>130350862</v>
       </c>
       <c r="B63" t="n">
-        <v>57861</v>
+        <v>57864</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,16 +6745,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>648755</v>
+        <v>648830</v>
       </c>
       <c r="R63" t="n">
-        <v>6995792</v>
+        <v>6995874</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6836,10 +6836,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350862</v>
+        <v>130350893</v>
       </c>
       <c r="B64" t="n">
-        <v>57864</v>
+        <v>57044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6847,16 +6847,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>648830</v>
+        <v>649144</v>
       </c>
       <c r="R64" t="n">
-        <v>6995874</v>
+        <v>6995799</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6938,10 +6938,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350893</v>
+        <v>130350875</v>
       </c>
       <c r="B65" t="n">
-        <v>57044</v>
+        <v>57861</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6949,16 +6949,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>649144</v>
+        <v>648755</v>
       </c>
       <c r="R65" t="n">
-        <v>6995799</v>
+        <v>6995792</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350908</v>
+        <v>130350902</v>
       </c>
       <c r="B4" t="n">
-        <v>89169</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649250</v>
+        <v>648702</v>
       </c>
       <c r="R4" t="n">
-        <v>6995605</v>
+        <v>6995939</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,32 +989,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350873</v>
+        <v>130350908</v>
       </c>
       <c r="B5" t="n">
-        <v>57053</v>
+        <v>89169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649139</v>
+        <v>649250</v>
       </c>
       <c r="R5" t="n">
-        <v>6995673</v>
+        <v>6995605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,11 +1060,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1091,32 +1086,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130350902</v>
+        <v>130350873</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>57053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>648702</v>
+        <v>649139</v>
       </c>
       <c r="R6" t="n">
-        <v>6995939</v>
+        <v>6995673</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,6 +1157,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,7 +1290,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130350866</v>
+        <v>130350860</v>
       </c>
       <c r="B8" t="n">
         <v>57864</v>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649049</v>
+        <v>648687</v>
       </c>
       <c r="R8" t="n">
-        <v>6995652</v>
+        <v>6995932</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130350870</v>
+        <v>130350904</v>
       </c>
       <c r="B9" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,21 +1403,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649039</v>
+        <v>649056</v>
       </c>
       <c r="R9" t="n">
-        <v>6995705</v>
+        <v>6995686</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,11 +1463,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,7 +1489,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130350860</v>
+        <v>130350866</v>
       </c>
       <c r="B10" t="n">
         <v>57864</v>
@@ -1529,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>648687</v>
+        <v>649049</v>
       </c>
       <c r="R10" t="n">
-        <v>6995932</v>
+        <v>6995652</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,7 +1564,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130350904</v>
+        <v>130350870</v>
       </c>
       <c r="B11" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,21 +1602,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1631,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649056</v>
+        <v>649039</v>
       </c>
       <c r="R11" t="n">
-        <v>6995686</v>
+        <v>6995705</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,6 +1662,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350844</v>
+        <v>130350861</v>
       </c>
       <c r="B14" t="n">
-        <v>91776</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>649036</v>
+        <v>648707</v>
       </c>
       <c r="R14" t="n">
-        <v>6995660</v>
+        <v>6995954</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,6 +1968,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130350861</v>
+        <v>130350844</v>
       </c>
       <c r="B17" t="n">
-        <v>57864</v>
+        <v>91776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2195,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2219,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>648707</v>
+        <v>649036</v>
       </c>
       <c r="R17" t="n">
-        <v>6995954</v>
+        <v>6995660</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2255,11 +2260,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130350838</v>
+        <v>130351124</v>
       </c>
       <c r="B19" t="n">
-        <v>91739</v>
+        <v>92195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6040186</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649074</v>
+        <v>649116</v>
       </c>
       <c r="R19" t="n">
-        <v>6995652</v>
+        <v>6995496</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,32 +2480,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130350847</v>
+        <v>130350838</v>
       </c>
       <c r="B20" t="n">
-        <v>57864</v>
+        <v>91739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649222</v>
+        <v>649074</v>
       </c>
       <c r="R20" t="n">
-        <v>6995657</v>
+        <v>6995652</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,11 +2551,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2582,10 +2577,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130351124</v>
+        <v>130350868</v>
       </c>
       <c r="B21" t="n">
-        <v>92195</v>
+        <v>57864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,21 +2588,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2617,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>649116</v>
+        <v>649093</v>
       </c>
       <c r="R21" t="n">
-        <v>6995496</v>
+        <v>6995638</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2653,6 +2648,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2679,7 +2679,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130350868</v>
+        <v>130350863</v>
       </c>
       <c r="B22" t="n">
         <v>57864</v>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>649093</v>
+        <v>649031</v>
       </c>
       <c r="R22" t="n">
-        <v>6995638</v>
+        <v>6995803</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130350863</v>
+        <v>130350847</v>
       </c>
       <c r="B23" t="n">
         <v>57864</v>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649031</v>
+        <v>649222</v>
       </c>
       <c r="R23" t="n">
-        <v>6995803</v>
+        <v>6995657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3475,10 +3475,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350846</v>
+        <v>130350898</v>
       </c>
       <c r="B30" t="n">
-        <v>91776</v>
+        <v>91796</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3486,23 +3486,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3510,10 +3506,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>649063</v>
+        <v>648849</v>
       </c>
       <c r="R30" t="n">
-        <v>6995635</v>
+        <v>6995437</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,10 +3568,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130350898</v>
+        <v>130350858</v>
       </c>
       <c r="B31" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3583,19 +3579,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>648849</v>
+        <v>648826</v>
       </c>
       <c r="R31" t="n">
-        <v>6995437</v>
+        <v>6995403</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3639,6 +3639,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3665,10 +3670,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350858</v>
+        <v>130350846</v>
       </c>
       <c r="B32" t="n">
-        <v>57864</v>
+        <v>91776</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,21 +3681,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3700,10 +3705,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>648826</v>
+        <v>649063</v>
       </c>
       <c r="R32" t="n">
-        <v>6995403</v>
+        <v>6995635</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3736,11 +3741,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3864,7 +3864,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130350852</v>
+        <v>130350869</v>
       </c>
       <c r="B34" t="n">
         <v>57864</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>649032</v>
+        <v>649090</v>
       </c>
       <c r="R34" t="n">
-        <v>6995530</v>
+        <v>6995641</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130350869</v>
+        <v>130350852</v>
       </c>
       <c r="B35" t="n">
         <v>57864</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>649090</v>
+        <v>649032</v>
       </c>
       <c r="R35" t="n">
-        <v>6995641</v>
+        <v>6995530</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130350911</v>
+        <v>130350872</v>
       </c>
       <c r="B37" t="n">
-        <v>89169</v>
+        <v>57864</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4181,21 +4181,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>648698</v>
+        <v>649146</v>
       </c>
       <c r="R37" t="n">
-        <v>6995926</v>
+        <v>6995662</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4241,6 +4241,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4267,10 +4272,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130350872</v>
+        <v>130350911</v>
       </c>
       <c r="B38" t="n">
-        <v>57864</v>
+        <v>89169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4278,21 +4283,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4302,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>649146</v>
+        <v>648698</v>
       </c>
       <c r="R38" t="n">
-        <v>6995662</v>
+        <v>6995926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4338,11 +4343,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4369,10 +4369,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130350840</v>
+        <v>130350897</v>
       </c>
       <c r="B39" t="n">
-        <v>91776</v>
+        <v>91796</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4380,23 +4380,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4404,10 +4400,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>649262</v>
+        <v>648848</v>
       </c>
       <c r="R39" t="n">
-        <v>6995647</v>
+        <v>6995528</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4466,10 +4462,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130350897</v>
+        <v>130350840</v>
       </c>
       <c r="B40" t="n">
-        <v>91796</v>
+        <v>91776</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4477,19 +4473,23 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>648848</v>
+        <v>649262</v>
       </c>
       <c r="R40" t="n">
-        <v>6995528</v>
+        <v>6995647</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350859</v>
+        <v>130350886</v>
       </c>
       <c r="B43" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>648771</v>
+        <v>648997</v>
       </c>
       <c r="R43" t="n">
-        <v>6995688</v>
+        <v>6995649</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4829,11 +4829,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4860,10 +4855,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130350856</v>
+        <v>130350896</v>
       </c>
       <c r="B44" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,23 +4866,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -4895,10 +4886,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>648835</v>
+        <v>648854</v>
       </c>
       <c r="R44" t="n">
-        <v>6995397</v>
+        <v>6995532</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4931,11 +4922,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4962,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350854</v>
+        <v>130350837</v>
       </c>
       <c r="B45" t="n">
-        <v>57864</v>
+        <v>91963</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4973,21 +4959,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4997,10 +4983,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648853</v>
+        <v>649254</v>
       </c>
       <c r="R45" t="n">
-        <v>6995420</v>
+        <v>6995609</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5033,11 +5019,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5064,10 +5045,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350892</v>
+        <v>130350854</v>
       </c>
       <c r="B46" t="n">
-        <v>57044</v>
+        <v>57864</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5075,16 +5056,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5099,10 +5080,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>649126</v>
+        <v>648853</v>
       </c>
       <c r="R46" t="n">
-        <v>6995764</v>
+        <v>6995420</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5139,7 +5120,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5166,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350837</v>
+        <v>130350892</v>
       </c>
       <c r="B47" t="n">
-        <v>91963</v>
+        <v>57044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5177,21 +5158,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1588</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5201,10 +5182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>649254</v>
+        <v>649126</v>
       </c>
       <c r="R47" t="n">
-        <v>6995609</v>
+        <v>6995764</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5237,6 +5218,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5263,10 +5249,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350896</v>
+        <v>130350859</v>
       </c>
       <c r="B48" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5274,19 +5260,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5294,10 +5284,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648854</v>
+        <v>648771</v>
       </c>
       <c r="R48" t="n">
-        <v>6995532</v>
+        <v>6995688</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5330,6 +5320,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5356,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350886</v>
+        <v>130350856</v>
       </c>
       <c r="B49" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,21 +5362,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5391,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>648997</v>
+        <v>648835</v>
       </c>
       <c r="R49" t="n">
-        <v>6995649</v>
+        <v>6995397</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5427,6 +5422,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5453,32 +5453,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130350909</v>
+        <v>130350883</v>
       </c>
       <c r="B50" t="n">
-        <v>89169</v>
+        <v>80354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>648957</v>
+        <v>649094</v>
       </c>
       <c r="R50" t="n">
-        <v>6995579</v>
+        <v>6995519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130350839</v>
+        <v>130350909</v>
       </c>
       <c r="B51" t="n">
-        <v>91776</v>
+        <v>89169</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>649369</v>
+        <v>648957</v>
       </c>
       <c r="R51" t="n">
-        <v>6995531</v>
+        <v>6995579</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,32 +5647,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350883</v>
+        <v>130350839</v>
       </c>
       <c r="B52" t="n">
-        <v>80354</v>
+        <v>91776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>649094</v>
+        <v>649369</v>
       </c>
       <c r="R52" t="n">
-        <v>6995519</v>
+        <v>6995531</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350901</v>
+        <v>130350874</v>
       </c>
       <c r="B58" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648771</v>
+        <v>648811</v>
       </c>
       <c r="R58" t="n">
-        <v>6995702</v>
+        <v>6995477</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,6 +6310,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6336,7 +6341,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350874</v>
+        <v>130350876</v>
       </c>
       <c r="B59" t="n">
         <v>57861</v>
@@ -6371,10 +6376,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>648811</v>
+        <v>649127</v>
       </c>
       <c r="R59" t="n">
-        <v>6995477</v>
+        <v>6995704</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,7 +6416,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6438,10 +6443,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350876</v>
+        <v>130350901</v>
       </c>
       <c r="B60" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6449,21 +6454,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6473,10 +6478,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>649127</v>
+        <v>648771</v>
       </c>
       <c r="R60" t="n">
-        <v>6995704</v>
+        <v>6995702</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6509,11 +6514,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350862</v>
+        <v>130350875</v>
       </c>
       <c r="B63" t="n">
-        <v>57864</v>
+        <v>57861</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,16 +6745,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>648830</v>
+        <v>648755</v>
       </c>
       <c r="R63" t="n">
-        <v>6995874</v>
+        <v>6995792</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6938,32 +6938,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350875</v>
+        <v>130350881</v>
       </c>
       <c r="B65" t="n">
-        <v>57861</v>
+        <v>97845</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>648755</v>
+        <v>649111</v>
       </c>
       <c r="R65" t="n">
-        <v>6995792</v>
+        <v>6995725</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7009,11 +7009,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7040,32 +7035,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130350881</v>
+        <v>130350862</v>
       </c>
       <c r="B66" t="n">
-        <v>97845</v>
+        <v>57864</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7075,10 +7070,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>649111</v>
+        <v>648830</v>
       </c>
       <c r="R66" t="n">
-        <v>6995725</v>
+        <v>6995874</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7111,6 +7106,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130350860</v>
+        <v>130350866</v>
       </c>
       <c r="B8" t="n">
         <v>57864</v>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>648687</v>
+        <v>649049</v>
       </c>
       <c r="R8" t="n">
-        <v>6995932</v>
+        <v>6995652</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130350904</v>
+        <v>130350870</v>
       </c>
       <c r="B9" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,21 +1403,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649056</v>
+        <v>649039</v>
       </c>
       <c r="R9" t="n">
-        <v>6995686</v>
+        <v>6995705</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130350866</v>
+        <v>130350904</v>
       </c>
       <c r="B10" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1500,21 +1505,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1524,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649049</v>
+        <v>649056</v>
       </c>
       <c r="R10" t="n">
-        <v>6995652</v>
+        <v>6995686</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,11 +1565,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,7 +1591,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130350870</v>
+        <v>130350860</v>
       </c>
       <c r="B11" t="n">
         <v>57864</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>649039</v>
+        <v>648687</v>
       </c>
       <c r="R11" t="n">
-        <v>6995705</v>
+        <v>6995932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2883,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350877</v>
+        <v>130350900</v>
       </c>
       <c r="B24" t="n">
-        <v>92235</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>648991</v>
+        <v>649027</v>
       </c>
       <c r="R24" t="n">
-        <v>6995659</v>
+        <v>6995592</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350878</v>
+        <v>130350905</v>
       </c>
       <c r="B25" t="n">
-        <v>92235</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>649038</v>
+        <v>649120</v>
       </c>
       <c r="R25" t="n">
-        <v>6995626</v>
+        <v>6995740</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130350900</v>
+        <v>130350877</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>92235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>649027</v>
+        <v>648991</v>
       </c>
       <c r="R26" t="n">
-        <v>6995592</v>
+        <v>6995659</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,32 +3174,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130350905</v>
+        <v>130350878</v>
       </c>
       <c r="B27" t="n">
-        <v>79221</v>
+        <v>92235</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>649120</v>
+        <v>649038</v>
       </c>
       <c r="R27" t="n">
-        <v>6995740</v>
+        <v>6995626</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350837</v>
+        <v>130350854</v>
       </c>
       <c r="B45" t="n">
-        <v>91963</v>
+        <v>57864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>649254</v>
+        <v>648853</v>
       </c>
       <c r="R45" t="n">
-        <v>6995609</v>
+        <v>6995420</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5019,6 +5019,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5045,10 +5050,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350854</v>
+        <v>130350837</v>
       </c>
       <c r="B46" t="n">
-        <v>57864</v>
+        <v>91963</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5056,21 +5061,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5080,10 +5085,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>648853</v>
+        <v>649254</v>
       </c>
       <c r="R46" t="n">
-        <v>6995420</v>
+        <v>6995609</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5116,11 +5121,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5147,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350892</v>
+        <v>130350859</v>
       </c>
       <c r="B47" t="n">
-        <v>57044</v>
+        <v>57864</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,16 +5158,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>649126</v>
+        <v>648771</v>
       </c>
       <c r="R47" t="n">
-        <v>6995764</v>
+        <v>6995688</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5249,7 +5249,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350859</v>
+        <v>130350856</v>
       </c>
       <c r="B48" t="n">
         <v>57864</v>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648771</v>
+        <v>648835</v>
       </c>
       <c r="R48" t="n">
-        <v>6995688</v>
+        <v>6995397</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5351,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130350856</v>
+        <v>130350892</v>
       </c>
       <c r="B49" t="n">
-        <v>57864</v>
+        <v>57044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>648835</v>
+        <v>649126</v>
       </c>
       <c r="R49" t="n">
-        <v>6995397</v>
+        <v>6995764</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5744,32 +5744,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350890</v>
+        <v>130350879</v>
       </c>
       <c r="B53" t="n">
-        <v>80286</v>
+        <v>92074</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649374</v>
+        <v>649062</v>
       </c>
       <c r="R53" t="n">
-        <v>6995542</v>
+        <v>6995641</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350879</v>
+        <v>130350841</v>
       </c>
       <c r="B54" t="n">
-        <v>92074</v>
+        <v>91776</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>649062</v>
+        <v>649195</v>
       </c>
       <c r="R54" t="n">
-        <v>6995641</v>
+        <v>6995694</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5938,10 +5938,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130350841</v>
+        <v>130350864</v>
       </c>
       <c r="B55" t="n">
-        <v>91776</v>
+        <v>57864</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5949,21 +5949,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>649195</v>
+        <v>648993</v>
       </c>
       <c r="R55" t="n">
-        <v>6995694</v>
+        <v>6995756</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6009,6 +6009,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6035,7 +6040,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130350864</v>
+        <v>130350867</v>
       </c>
       <c r="B56" t="n">
         <v>57864</v>
@@ -6070,10 +6075,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>648993</v>
+        <v>649095</v>
       </c>
       <c r="R56" t="n">
-        <v>6995756</v>
+        <v>6995637</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6110,7 +6115,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6137,32 +6142,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130350867</v>
+        <v>130350890</v>
       </c>
       <c r="B57" t="n">
-        <v>57864</v>
+        <v>80286</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6172,10 +6177,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>649095</v>
+        <v>649374</v>
       </c>
       <c r="R57" t="n">
-        <v>6995637</v>
+        <v>6995542</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6208,11 +6213,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350874</v>
+        <v>130350901</v>
       </c>
       <c r="B58" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648811</v>
+        <v>648771</v>
       </c>
       <c r="R58" t="n">
-        <v>6995477</v>
+        <v>6995702</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,11 +6310,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6341,7 +6336,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130350876</v>
+        <v>130350874</v>
       </c>
       <c r="B59" t="n">
         <v>57861</v>
@@ -6376,10 +6371,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>649127</v>
+        <v>648811</v>
       </c>
       <c r="R59" t="n">
-        <v>6995704</v>
+        <v>6995477</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6416,7 +6411,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6443,10 +6438,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350901</v>
+        <v>130350876</v>
       </c>
       <c r="B60" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6454,21 +6449,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6478,10 +6473,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>648771</v>
+        <v>649127</v>
       </c>
       <c r="R60" t="n">
-        <v>6995702</v>
+        <v>6995704</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6514,6 +6509,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350875</v>
+        <v>130350893</v>
       </c>
       <c r="B63" t="n">
-        <v>57861</v>
+        <v>57044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,16 +6745,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>648755</v>
+        <v>649144</v>
       </c>
       <c r="R63" t="n">
-        <v>6995792</v>
+        <v>6995799</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6836,32 +6836,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130350893</v>
+        <v>130350881</v>
       </c>
       <c r="B64" t="n">
-        <v>57044</v>
+        <v>97845</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>649144</v>
+        <v>649111</v>
       </c>
       <c r="R64" t="n">
-        <v>6995799</v>
+        <v>6995725</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6907,11 +6907,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6938,10 +6933,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350881</v>
+        <v>130350889</v>
       </c>
       <c r="B65" t="n">
-        <v>97845</v>
+        <v>80286</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6949,21 +6944,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6973,10 +6968,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>649111</v>
+        <v>649384</v>
       </c>
       <c r="R65" t="n">
-        <v>6995725</v>
+        <v>6995514</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7035,10 +7030,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130350862</v>
+        <v>130350875</v>
       </c>
       <c r="B66" t="n">
-        <v>57864</v>
+        <v>57861</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7046,16 +7041,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7070,10 +7065,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>648830</v>
+        <v>648755</v>
       </c>
       <c r="R66" t="n">
-        <v>6995874</v>
+        <v>6995792</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7110,7 +7105,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7137,32 +7132,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130350889</v>
+        <v>130350862</v>
       </c>
       <c r="B67" t="n">
-        <v>80286</v>
+        <v>57864</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7172,10 +7167,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>649384</v>
+        <v>648830</v>
       </c>
       <c r="R67" t="n">
-        <v>6995514</v>
+        <v>6995874</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7208,6 +7203,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350902</v>
+        <v>130350908</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>89169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648702</v>
+        <v>649250</v>
       </c>
       <c r="R4" t="n">
-        <v>6995939</v>
+        <v>6995605</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350908</v>
+        <v>130350902</v>
       </c>
       <c r="B5" t="n">
-        <v>89169</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>649250</v>
+        <v>648702</v>
       </c>
       <c r="R5" t="n">
-        <v>6995605</v>
+        <v>6995939</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130350866</v>
+        <v>130350904</v>
       </c>
       <c r="B8" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>649049</v>
+        <v>649056</v>
       </c>
       <c r="R8" t="n">
-        <v>6995652</v>
+        <v>6995686</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,7 +1387,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130350870</v>
+        <v>130350866</v>
       </c>
       <c r="B9" t="n">
         <v>57864</v>
@@ -1427,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>649039</v>
+        <v>649049</v>
       </c>
       <c r="R9" t="n">
-        <v>6995705</v>
+        <v>6995652</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,7 +1462,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,10 +1489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130350904</v>
+        <v>130350870</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,21 +1500,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1529,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>649056</v>
+        <v>649039</v>
       </c>
       <c r="R10" t="n">
-        <v>6995686</v>
+        <v>6995705</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,6 +1560,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130350861</v>
+        <v>130350844</v>
       </c>
       <c r="B14" t="n">
-        <v>57864</v>
+        <v>91776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>648707</v>
+        <v>649036</v>
       </c>
       <c r="R14" t="n">
-        <v>6995954</v>
+        <v>6995660</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,11 +1968,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,10 +2184,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130350844</v>
+        <v>130351125</v>
       </c>
       <c r="B17" t="n">
-        <v>91776</v>
+        <v>92195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2195,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6040186</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2219,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>649036</v>
+        <v>648877</v>
       </c>
       <c r="R17" t="n">
-        <v>6995660</v>
+        <v>6995565</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,10 +2281,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130351125</v>
+        <v>130350861</v>
       </c>
       <c r="B18" t="n">
-        <v>92195</v>
+        <v>57864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,21 +2292,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2321,10 +2316,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>648877</v>
+        <v>648707</v>
       </c>
       <c r="R18" t="n">
-        <v>6995565</v>
+        <v>6995954</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,6 +2352,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2383,32 +2383,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130351124</v>
+        <v>130350838</v>
       </c>
       <c r="B19" t="n">
-        <v>92195</v>
+        <v>91739</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040186</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>649116</v>
+        <v>649074</v>
       </c>
       <c r="R19" t="n">
-        <v>6995496</v>
+        <v>6995652</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,32 +2480,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130350838</v>
+        <v>130350868</v>
       </c>
       <c r="B20" t="n">
-        <v>91739</v>
+        <v>57864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>649074</v>
+        <v>649093</v>
       </c>
       <c r="R20" t="n">
-        <v>6995652</v>
+        <v>6995638</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,6 +2551,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2577,7 +2582,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130350868</v>
+        <v>130350863</v>
       </c>
       <c r="B21" t="n">
         <v>57864</v>
@@ -2612,10 +2617,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>649093</v>
+        <v>649031</v>
       </c>
       <c r="R21" t="n">
-        <v>6995638</v>
+        <v>6995803</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,7 +2684,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130350863</v>
+        <v>130350847</v>
       </c>
       <c r="B22" t="n">
         <v>57864</v>
@@ -2714,10 +2719,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>649031</v>
+        <v>649222</v>
       </c>
       <c r="R22" t="n">
-        <v>6995803</v>
+        <v>6995657</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2754,7 +2759,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2781,10 +2786,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130350847</v>
+        <v>130351124</v>
       </c>
       <c r="B23" t="n">
-        <v>57864</v>
+        <v>92195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2792,21 +2797,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2816,10 +2821,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>649222</v>
+        <v>649116</v>
       </c>
       <c r="R23" t="n">
-        <v>6995657</v>
+        <v>6995496</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,11 +2857,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2883,32 +2883,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130350900</v>
+        <v>130350878</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>92235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>649027</v>
+        <v>649038</v>
       </c>
       <c r="R24" t="n">
-        <v>6995592</v>
+        <v>6995626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2980,32 +2980,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130350905</v>
+        <v>130350877</v>
       </c>
       <c r="B25" t="n">
-        <v>79221</v>
+        <v>92235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>649120</v>
+        <v>648991</v>
       </c>
       <c r="R25" t="n">
-        <v>6995740</v>
+        <v>6995659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,32 +3077,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130350877</v>
+        <v>130350900</v>
       </c>
       <c r="B26" t="n">
-        <v>92235</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>648991</v>
+        <v>649027</v>
       </c>
       <c r="R26" t="n">
-        <v>6995659</v>
+        <v>6995592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,32 +3174,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130350878</v>
+        <v>130350905</v>
       </c>
       <c r="B27" t="n">
-        <v>92235</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>649038</v>
+        <v>649120</v>
       </c>
       <c r="R27" t="n">
-        <v>6995626</v>
+        <v>6995740</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130350898</v>
+        <v>130350846</v>
       </c>
       <c r="B30" t="n">
-        <v>91796</v>
+        <v>91776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3486,19 +3486,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3506,10 +3510,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>648849</v>
+        <v>649063</v>
       </c>
       <c r="R30" t="n">
-        <v>6995437</v>
+        <v>6995635</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3568,32 +3572,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130350858</v>
+        <v>130350891</v>
       </c>
       <c r="B31" t="n">
-        <v>57864</v>
+        <v>80286</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3603,10 +3607,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>648826</v>
+        <v>649044</v>
       </c>
       <c r="R31" t="n">
-        <v>6995403</v>
+        <v>6995628</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3639,11 +3643,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3670,10 +3669,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130350846</v>
+        <v>130350898</v>
       </c>
       <c r="B32" t="n">
-        <v>91776</v>
+        <v>91796</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3681,23 +3680,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3705,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>649063</v>
+        <v>648849</v>
       </c>
       <c r="R32" t="n">
-        <v>6995635</v>
+        <v>6995437</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3767,32 +3762,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130350891</v>
+        <v>130350858</v>
       </c>
       <c r="B33" t="n">
-        <v>80286</v>
+        <v>57864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3802,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>649044</v>
+        <v>648826</v>
       </c>
       <c r="R33" t="n">
-        <v>6995628</v>
+        <v>6995403</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3838,6 +3833,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3864,7 +3864,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130350869</v>
+        <v>130350852</v>
       </c>
       <c r="B34" t="n">
         <v>57864</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>649090</v>
+        <v>649032</v>
       </c>
       <c r="R34" t="n">
-        <v>6995641</v>
+        <v>6995530</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130350852</v>
+        <v>130350869</v>
       </c>
       <c r="B35" t="n">
         <v>57864</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>649032</v>
+        <v>649090</v>
       </c>
       <c r="R35" t="n">
-        <v>6995530</v>
+        <v>6995641</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4369,10 +4369,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130350897</v>
+        <v>130350871</v>
       </c>
       <c r="B39" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4380,19 +4380,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4400,10 +4404,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>648848</v>
+        <v>649048</v>
       </c>
       <c r="R39" t="n">
-        <v>6995528</v>
+        <v>6995714</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4436,6 +4440,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4559,10 +4568,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130350871</v>
+        <v>130350897</v>
       </c>
       <c r="B41" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4570,23 +4579,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4594,10 +4599,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>649048</v>
+        <v>648848</v>
       </c>
       <c r="R41" t="n">
-        <v>6995714</v>
+        <v>6995528</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4630,11 +4635,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4758,10 +4758,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130350886</v>
+        <v>130350837</v>
       </c>
       <c r="B43" t="n">
-        <v>80326</v>
+        <v>91963</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,21 +4769,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>648997</v>
+        <v>649254</v>
       </c>
       <c r="R43" t="n">
-        <v>6995649</v>
+        <v>6995609</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130350854</v>
+        <v>130350886</v>
       </c>
       <c r="B45" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>648853</v>
+        <v>648997</v>
       </c>
       <c r="R45" t="n">
-        <v>6995420</v>
+        <v>6995649</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5019,11 +5019,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5050,10 +5045,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130350837</v>
+        <v>130350859</v>
       </c>
       <c r="B46" t="n">
-        <v>91963</v>
+        <v>57864</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5061,21 +5056,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5085,10 +5080,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>649254</v>
+        <v>648771</v>
       </c>
       <c r="R46" t="n">
-        <v>6995609</v>
+        <v>6995688</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5121,6 +5116,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5147,7 +5147,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130350859</v>
+        <v>130350856</v>
       </c>
       <c r="B47" t="n">
         <v>57864</v>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>648771</v>
+        <v>648835</v>
       </c>
       <c r="R47" t="n">
-        <v>6995688</v>
+        <v>6995397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5249,7 +5249,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130350856</v>
+        <v>130350854</v>
       </c>
       <c r="B48" t="n">
         <v>57864</v>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>648835</v>
+        <v>648853</v>
       </c>
       <c r="R48" t="n">
-        <v>6995397</v>
+        <v>6995420</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5453,32 +5453,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130350883</v>
+        <v>130350839</v>
       </c>
       <c r="B50" t="n">
-        <v>80354</v>
+        <v>91776</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>649094</v>
+        <v>649369</v>
       </c>
       <c r="R50" t="n">
-        <v>6995519</v>
+        <v>6995531</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5647,32 +5647,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130350839</v>
+        <v>130350883</v>
       </c>
       <c r="B52" t="n">
-        <v>91776</v>
+        <v>80354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>649369</v>
+        <v>649094</v>
       </c>
       <c r="R52" t="n">
-        <v>6995531</v>
+        <v>6995519</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130350879</v>
+        <v>130350841</v>
       </c>
       <c r="B53" t="n">
-        <v>92074</v>
+        <v>91776</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5755,21 +5755,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>649062</v>
+        <v>649195</v>
       </c>
       <c r="R53" t="n">
-        <v>6995641</v>
+        <v>6995694</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130350841</v>
+        <v>130350879</v>
       </c>
       <c r="B54" t="n">
-        <v>91776</v>
+        <v>92074</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,21 +5852,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>649195</v>
+        <v>649062</v>
       </c>
       <c r="R54" t="n">
-        <v>6995694</v>
+        <v>6995641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130350901</v>
+        <v>130350876</v>
       </c>
       <c r="B58" t="n">
-        <v>79221</v>
+        <v>57861</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>648771</v>
+        <v>649127</v>
       </c>
       <c r="R58" t="n">
-        <v>6995702</v>
+        <v>6995704</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,6 +6310,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6438,10 +6443,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130350876</v>
+        <v>130350901</v>
       </c>
       <c r="B60" t="n">
-        <v>57861</v>
+        <v>79221</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6449,21 +6454,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6473,10 +6478,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>649127</v>
+        <v>648771</v>
       </c>
       <c r="R60" t="n">
-        <v>6995704</v>
+        <v>6995702</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6509,11 +6514,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6540,10 +6540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130350842</v>
+        <v>130350862</v>
       </c>
       <c r="B61" t="n">
-        <v>91776</v>
+        <v>57864</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6551,21 +6551,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>649096</v>
+        <v>648830</v>
       </c>
       <c r="R61" t="n">
-        <v>6995501</v>
+        <v>6995874</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6611,6 +6611,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6637,10 +6642,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130350910</v>
+        <v>130350893</v>
       </c>
       <c r="B62" t="n">
-        <v>89169</v>
+        <v>57044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6648,21 +6653,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>510</v>
+        <v>102612</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>648873</v>
+        <v>649144</v>
       </c>
       <c r="R62" t="n">
-        <v>6995569</v>
+        <v>6995799</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6708,6 +6713,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6734,10 +6744,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130350893</v>
+        <v>130350875</v>
       </c>
       <c r="B63" t="n">
-        <v>57044</v>
+        <v>57861</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,16 +6755,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6769,10 +6779,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>649144</v>
+        <v>648755</v>
       </c>
       <c r="R63" t="n">
-        <v>6995799</v>
+        <v>6995792</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,7 +6819,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6933,32 +6943,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130350889</v>
+        <v>130350910</v>
       </c>
       <c r="B65" t="n">
-        <v>80286</v>
+        <v>89169</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>510</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6968,10 +6978,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>649384</v>
+        <v>648873</v>
       </c>
       <c r="R65" t="n">
-        <v>6995514</v>
+        <v>6995569</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7030,10 +7040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130350875</v>
+        <v>130350842</v>
       </c>
       <c r="B66" t="n">
-        <v>57861</v>
+        <v>91776</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7041,21 +7051,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7065,10 +7075,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>648755</v>
+        <v>649096</v>
       </c>
       <c r="R66" t="n">
-        <v>6995792</v>
+        <v>6995501</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7101,11 +7111,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7132,32 +7137,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130350862</v>
+        <v>130350889</v>
       </c>
       <c r="B67" t="n">
-        <v>57864</v>
+        <v>80286</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7167,10 +7172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>648830</v>
+        <v>649384</v>
       </c>
       <c r="R67" t="n">
-        <v>6995874</v>
+        <v>6995514</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7203,11 +7208,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-30</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 61873-2025 artfynd.xlsx
+++ b/artfynd/A 61873-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350908</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350909</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350910</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350911</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350879</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350839</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350840</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350841</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350842</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350843</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350844</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350845</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350846</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350877</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350878</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350837</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350884</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350838</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350900</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350901</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350902</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350903</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350904</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350905</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350885</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350886</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350883</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350874</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3495,6 +3640,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350875</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3597,6 +3747,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350876</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3717,6 +3872,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128491040</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3819,6 +3979,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350847</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3921,6 +4086,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350848</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4023,6 +4193,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350849</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4125,6 +4300,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350850</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4227,6 +4407,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350852</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4329,6 +4514,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350853</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4431,6 +4621,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350854</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4533,6 +4728,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350855</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4635,6 +4835,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350856</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4737,6 +4942,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350857</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4839,6 +5049,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350858</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4941,6 +5156,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350859</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5043,6 +5263,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350860</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5145,6 +5370,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350861</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5247,6 +5477,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350862</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5349,6 +5584,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350863</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5451,6 +5691,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350864</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5553,6 +5798,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350865</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5655,6 +5905,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350866</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5757,6 +6012,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350867</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5859,6 +6119,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350868</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5961,6 +6226,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350869</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6063,6 +6333,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350870</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6165,6 +6440,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350871</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6267,6 +6547,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350872</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6369,6 +6654,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350873</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6471,6 +6761,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350892</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6573,6 +6868,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350893</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6675,6 +6975,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350895</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6772,6 +7077,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350881</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6869,6 +7179,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350889</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6966,6 +7281,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350890</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7063,6 +7383,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130350891</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7160,6 +7485,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351124</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7257,8 +7587,81 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130351125</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>